--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="885" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0C3B1E4-595C-406C-A73B-581CD4205C02}"/>
+  <xr:revisionPtr revIDLastSave="896" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{103FB33C-17CF-464B-83A4-53A71B44D5C7}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-11235" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="665">
   <si>
     <t>Job</t>
   </si>
@@ -1980,6 +1980,60 @@
   </si>
   <si>
     <t>1688 Turakina Valley Road, Marton</t>
+  </si>
+  <si>
+    <t>1087566 - 00070520 - DG Label</t>
+  </si>
+  <si>
+    <t>26 Kent Street, Carterton</t>
+  </si>
+  <si>
+    <t>1087565 - 00063216 - DG Label</t>
+  </si>
+  <si>
+    <t>245 Millricks Line, Linton</t>
+  </si>
+  <si>
+    <t>1087563 - 00065474 - DG Label</t>
+  </si>
+  <si>
+    <t>11 The Oaks, Awapuni</t>
+  </si>
+  <si>
+    <t>1087561 - 00051746 - DG Label</t>
+  </si>
+  <si>
+    <t>25 Weka Street, Pohangina</t>
+  </si>
+  <si>
+    <t>1087623 - 00071450 - DG Label</t>
+  </si>
+  <si>
+    <t>1087622 - 00068633 - DG Label</t>
+  </si>
+  <si>
+    <t>1087621 - 00065427 - DG Label</t>
+  </si>
+  <si>
+    <t>1087620 - 00015005 - DG Label</t>
+  </si>
+  <si>
+    <t>1087619 - 00060420 - DG Label</t>
+  </si>
+  <si>
+    <t>286 Hewitts Road, Linton</t>
+  </si>
+  <si>
+    <t>25 Montgomery Terrace</t>
+  </si>
+  <si>
+    <t>25 Elmira Avenue, Hokowhitu</t>
+  </si>
+  <si>
+    <t>94 Amberley Avenue, Highbury</t>
+  </si>
+  <si>
+    <t>11 Tūere Place, Hokowhitu</t>
   </si>
 </sst>
 </file>
@@ -2352,7 +2406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C324"/>
+  <dimension ref="A1:C333"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -5924,6 +5978,102 @@
         <v>211</v>
       </c>
     </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>647</v>
+      </c>
+      <c r="B325" t="s">
+        <v>648</v>
+      </c>
+      <c r="C325" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>649</v>
+      </c>
+      <c r="B326" t="s">
+        <v>650</v>
+      </c>
+      <c r="C326" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>651</v>
+      </c>
+      <c r="B327" t="s">
+        <v>652</v>
+      </c>
+      <c r="C327" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>653</v>
+      </c>
+      <c r="B328" t="s">
+        <v>654</v>
+      </c>
+      <c r="C328" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>655</v>
+      </c>
+      <c r="B329" t="s">
+        <v>660</v>
+      </c>
+      <c r="C329" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>656</v>
+      </c>
+      <c r="B330" t="s">
+        <v>661</v>
+      </c>
+      <c r="C330" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>657</v>
+      </c>
+      <c r="B331" t="s">
+        <v>662</v>
+      </c>
+      <c r="C331" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>658</v>
+      </c>
+      <c r="B332" t="s">
+        <v>663</v>
+      </c>
+      <c r="C332" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>659</v>
+      </c>
+      <c r="B333" t="s">
+        <v>664</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="896" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{103FB33C-17CF-464B-83A4-53A71B44D5C7}"/>
+  <xr:revisionPtr revIDLastSave="976" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{375B7B98-5CFF-4E53-B9E9-E693E2EA3BC8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-11235" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
+    <workbookView xWindow="54495" yWindow="-7665" windowWidth="26010" windowHeight="20985" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="658">
   <si>
     <t>Job</t>
   </si>
@@ -353,9 +353,6 @@
     <t>722 Upper Plain Road, Masterton</t>
   </si>
   <si>
-    <t>1083023 - 00022620 - DG Label</t>
-  </si>
-  <si>
     <t>124 Works Road, Longburn</t>
   </si>
   <si>
@@ -419,9 +416,6 @@
     <t>1082679 - 00027851 - DG Label</t>
   </si>
   <si>
-    <t>18 Ataahua Place, Featherston</t>
-  </si>
-  <si>
     <t>1082671 - 00016526 - DG Label</t>
   </si>
   <si>
@@ -506,12 +500,6 @@
     <t>68 London Street, Kimbolton</t>
   </si>
   <si>
-    <t>1082148 - 00049360 - DG Label</t>
-  </si>
-  <si>
-    <t>11 Moore Street, Featherston</t>
-  </si>
-  <si>
     <t>1081142 - 00042583 - DG Label</t>
   </si>
   <si>
@@ -572,12 +560,6 @@
     <t>11 Te Ore Ore Bideford Road , Te Ore Ore, Masterton, 5886</t>
   </si>
   <si>
-    <t>1082608 - 00037238  - DG Label - 1000605901PC3C4</t>
-  </si>
-  <si>
-    <t>32 TAMA ROAD , RIVERSDALE BEACH, MASTERTON, 5872</t>
-  </si>
-  <si>
     <t>1082604 - 00037235 - DG Label - 1000583813PC6B9</t>
   </si>
   <si>
@@ -782,12 +764,6 @@
     <t>1084779 - 00048369 - DG Label</t>
   </si>
   <si>
-    <t>5 Pukeko Place, Riversdale Beach</t>
-  </si>
-  <si>
-    <t>1084781 - 00059954 - DG Label</t>
-  </si>
-  <si>
     <t>1244A Rangitikei Line, Kauwhata</t>
   </si>
   <si>
@@ -986,12 +962,6 @@
     <t>1085625 - 00059698 - DG Label</t>
   </si>
   <si>
-    <t>19 Bengston Street, Eketahuna</t>
-  </si>
-  <si>
-    <t>1085623 - 00035552 - DG Label</t>
-  </si>
-  <si>
     <t>15 Tangimoana Road, Ohakea</t>
   </si>
   <si>
@@ -1100,9 +1070,6 @@
     <t>1085718 - 00025360 - DG Label</t>
   </si>
   <si>
-    <t>65 Hartwell Drive, Bunnythorpe</t>
-  </si>
-  <si>
     <t>1085717 - 00057960 - DG Label</t>
   </si>
   <si>
@@ -1118,9 +1085,6 @@
     <t>1085715 - 00030535 - DG Label</t>
   </si>
   <si>
-    <t>2/31 Moore Street, Tawhero</t>
-  </si>
-  <si>
     <t>1085714 - 00048298 - DG Label</t>
   </si>
   <si>
@@ -1175,21 +1139,12 @@
     <t>1085915 - 00061776 - DG Label</t>
   </si>
   <si>
-    <t>62 Hartwell Drive, Bunnythorpe</t>
-  </si>
-  <si>
     <t>1085914 - 00062074 - DG Label</t>
   </si>
   <si>
     <t>12 Edenmore Terrace, Fitzherbert</t>
   </si>
   <si>
-    <t>1085912 - 00061647 - DG Label</t>
-  </si>
-  <si>
-    <t>427C Ruahine Street, Terrace End</t>
-  </si>
-  <si>
     <t>1132 Pohangina Valley East Road, Pohangina</t>
   </si>
   <si>
@@ -1250,9 +1205,6 @@
     <t>1086021 - 00056665 - DG Label</t>
   </si>
   <si>
-    <t>1086114 - 00058005 - DG Label</t>
-  </si>
-  <si>
     <t>329 Kahuterawa Road, Linton</t>
   </si>
   <si>
@@ -1262,9 +1214,6 @@
     <t>93 Chester Road, Clareville</t>
   </si>
   <si>
-    <t>51 Southdown Drive, Martinborough</t>
-  </si>
-  <si>
     <t>41 Kowhai Street, Castelcliff, Whanganui, 4501</t>
   </si>
   <si>
@@ -1361,18 +1310,9 @@
     <t>1085965 - 00039615 - DG Label</t>
   </si>
   <si>
-    <t>1085964 - 00038228 - DG Label</t>
-  </si>
-  <si>
-    <t>1078484 - DG Labelling request - 00022542</t>
-  </si>
-  <si>
     <t>1078481 - DG Labelling request - 00037578</t>
   </si>
   <si>
-    <t xml:space="preserve">1085967 - 00038230 - DG Label </t>
-  </si>
-  <si>
     <t>258 High Street South, Carterton</t>
   </si>
   <si>
@@ -1385,9 +1325,6 @@
     <t>260 High Street South, Carterton</t>
   </si>
   <si>
-    <t>613 Lake Ferry Road</t>
-  </si>
-  <si>
     <t>574 Masterton Castlepoint Road, Masterton</t>
   </si>
   <si>
@@ -1403,18 +1340,6 @@
     <t>377 Gillespies Line, Kairanga</t>
   </si>
   <si>
-    <t>1086423 - 00065064 - DG Label</t>
-  </si>
-  <si>
-    <t>1 Cleveland Heights, Kelvin Grove</t>
-  </si>
-  <si>
-    <t>1086422 - 00065066 - DG Label</t>
-  </si>
-  <si>
-    <t>49 Parnell Heights Drive, Kelvin Grove</t>
-  </si>
-  <si>
     <t>33 Harvest Lane, Newbury</t>
   </si>
   <si>
@@ -1466,15 +1391,9 @@
     <t>283 Cambridge Avenue, Ashhurst</t>
   </si>
   <si>
-    <t>43 Tennyson Avenue, Kelvin Grove</t>
-  </si>
-  <si>
     <t xml:space="preserve">4a wellesley st </t>
   </si>
   <si>
-    <t>1085892 - 00053352 - DG Label</t>
-  </si>
-  <si>
     <t>1078322 - DG Labelling request - 00038395</t>
   </si>
   <si>
@@ -1508,12 +1427,6 @@
     <t>3 Tutakarae Road, Kelvin Grove</t>
   </si>
   <si>
-    <t>1086650 - 00063059 - DG Label</t>
-  </si>
-  <si>
-    <t>35 Horseshoe Lane, Pahiatua</t>
-  </si>
-  <si>
     <t>1086649 - 00056472 - DG Label</t>
   </si>
   <si>
@@ -1544,18 +1457,6 @@
     <t>146 Mill Road, Rongotea</t>
   </si>
   <si>
-    <t>1086642 - 00057023 - DG Label</t>
-  </si>
-  <si>
-    <t>23 Liberty Grove, Kelvin Grove</t>
-  </si>
-  <si>
-    <t>1086641 - 00057011 - DG Label</t>
-  </si>
-  <si>
-    <t>18 La Lena Grove, Fitzherbert</t>
-  </si>
-  <si>
     <t>1086639 - 00056782 - DG Label</t>
   </si>
   <si>
@@ -1568,18 +1469,6 @@
     <t>1580 State Highway 3, Awahuri</t>
   </si>
   <si>
-    <t>1086635 - 00056022 - DG Label</t>
-  </si>
-  <si>
-    <t>992 Tremaine Avenue, Roslyn</t>
-  </si>
-  <si>
-    <t>1086634 - 00056019 - DG Label</t>
-  </si>
-  <si>
-    <t>9 Sharon Place, Awapuni</t>
-  </si>
-  <si>
     <t>1086631 - 00050566 - DG Label</t>
   </si>
   <si>
@@ -1616,12 +1505,6 @@
     <t>1086967 - 00057376 - DG Label</t>
   </si>
   <si>
-    <t>2738 Masterton Castlepoint Road, Mangapakeha</t>
-  </si>
-  <si>
-    <t>1086968 - 00064506 - DG Label</t>
-  </si>
-  <si>
     <t>110 Fitzroy Street, Terrace End</t>
   </si>
   <si>
@@ -1652,24 +1535,6 @@
     <t>4A Cedar Crescent, Feilding</t>
   </si>
   <si>
-    <t>1087122 - 00056485 - DG Label</t>
-  </si>
-  <si>
-    <t>102 Rosina Road, Tangimoana</t>
-  </si>
-  <si>
-    <t>1087121 - 00062073 - DG Label</t>
-  </si>
-  <si>
-    <t>86 Pacific Drive, Fitzherbert</t>
-  </si>
-  <si>
-    <t>1087120 - 00061616 - DG Label</t>
-  </si>
-  <si>
-    <t>5 Tower Place, Fitzherbert</t>
-  </si>
-  <si>
     <t>1087119 - 00057022 - DG Label</t>
   </si>
   <si>
@@ -1766,24 +1631,6 @@
     <t>1087148 - 00053854 - DG Label</t>
   </si>
   <si>
-    <t>81 Hillcrest Drive, Kelvin Grove</t>
-  </si>
-  <si>
-    <t>1087149 - 00062522 - DG Label</t>
-  </si>
-  <si>
-    <t>9 Logan Place, Kelvin Grove</t>
-  </si>
-  <si>
-    <t>1087150 - 00029185 - DG Label</t>
-  </si>
-  <si>
-    <t>60 Ihaka Street, Hokowhitu</t>
-  </si>
-  <si>
-    <t>1087151 - 00053065 - DG Label</t>
-  </si>
-  <si>
     <t>1087281 - 00067739 - DG Label</t>
   </si>
   <si>
@@ -1805,9 +1652,6 @@
     <t>1087274 - 00055245 - DG Label</t>
   </si>
   <si>
-    <t>219a Hinekura Road, Hinakura</t>
-  </si>
-  <si>
     <t>1087269 - 00052068 - DG Label</t>
   </si>
   <si>
@@ -1826,12 +1670,6 @@
     <t>42 Harrison Street, Whanganui</t>
   </si>
   <si>
-    <t>1087300 - 00055403 - DG Label</t>
-  </si>
-  <si>
-    <t>15 Florin Lane, Rongotea</t>
-  </si>
-  <si>
     <t>1087299 - 00065802 - DG Label</t>
   </si>
   <si>
@@ -1868,12 +1706,6 @@
     <t>40 Parkland Crescent, Terrace End</t>
   </si>
   <si>
-    <t>1087362 - 00056559 - DG Label</t>
-  </si>
-  <si>
-    <t>256 Manaia Road, Solway</t>
-  </si>
-  <si>
     <t>1087361 - 00053770 - DG Label</t>
   </si>
   <si>
@@ -1928,12 +1760,6 @@
     <t>69 Meridian Grove, Kelvin Grove</t>
   </si>
   <si>
-    <t>1087493 - 00055288 - DG Label</t>
-  </si>
-  <si>
-    <t>63 Tangimoana Beach Road, Tangimoana</t>
-  </si>
-  <si>
     <t>1087492 - 00059113 - DG Label</t>
   </si>
   <si>
@@ -2034,6 +1860,159 @@
   </si>
   <si>
     <t>11 Tūere Place, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1087798 - 00062077 - DG Label</t>
+  </si>
+  <si>
+    <t>7 Caffray Avenue, Aramoho</t>
+  </si>
+  <si>
+    <t>1087797 - 00060025 - DG Label</t>
+  </si>
+  <si>
+    <t>20 Dickens Lane, Otamatea</t>
+  </si>
+  <si>
+    <t>1087796 - 00056888 - DG Label</t>
+  </si>
+  <si>
+    <t>210 Heads Road, Gonville</t>
+  </si>
+  <si>
+    <t>1087795 - 00014068 - DG Label</t>
+  </si>
+  <si>
+    <t>77 Wikitoria Road, Whanganui Airport</t>
+  </si>
+  <si>
+    <t>1087794 - 00062249 - DG Label</t>
+  </si>
+  <si>
+    <t>11 McGregor Crescent, Masterton</t>
+  </si>
+  <si>
+    <t>1087793 - 00064585 - DG Label</t>
+  </si>
+  <si>
+    <t>46 Romina Way, Martinborough</t>
+  </si>
+  <si>
+    <t>1087792 - 00065145 - DG Label</t>
+  </si>
+  <si>
+    <t>4 Mana Place, Awapuni</t>
+  </si>
+  <si>
+    <t>1087790 - 00065126 - DG Label</t>
+  </si>
+  <si>
+    <t>533 Kelvin Grove Road, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1087789 - 00056263 - DG Label</t>
+  </si>
+  <si>
+    <t>20 Abby Road, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1087788 - 00061007 - DG Label</t>
+  </si>
+  <si>
+    <t>57A Manuka Street, Lansdowne</t>
+  </si>
+  <si>
+    <t>1087787 - 00067838 - DG Label</t>
+  </si>
+  <si>
+    <t>56 Kopane Road, Rongotea</t>
+  </si>
+  <si>
+    <t>1087786 - 00062201 - DG Label</t>
+  </si>
+  <si>
+    <t>330 Aokautere Drive, Aokautere</t>
+  </si>
+  <si>
+    <t>1087785 - 00070481 - DG Label</t>
+  </si>
+  <si>
+    <t>15 Union Street, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1087784 - 00063340 - DG Label</t>
+  </si>
+  <si>
+    <t>3 Kākāriki Crescent, Carterton</t>
+  </si>
+  <si>
+    <t>1087783 - 00064721 - DG Label</t>
+  </si>
+  <si>
+    <t>22 Galea Grove, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1087782 - 00062531 - DG Label</t>
+  </si>
+  <si>
+    <t>291 Grey Street, Palmerston North</t>
+  </si>
+  <si>
+    <t>1087781 - 00064110 - DG Label</t>
+  </si>
+  <si>
+    <t>103 Freedom Drive, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1087780 - 00065105 - DG Label</t>
+  </si>
+  <si>
+    <t>9E Satori Way, Feilding</t>
+  </si>
+  <si>
+    <t>1087779 - 00067876 - DG Label</t>
+  </si>
+  <si>
+    <t>1185C Halcombe Road, Halcombe</t>
+  </si>
+  <si>
+    <t>1087778 - 00062453 - DG Label</t>
+  </si>
+  <si>
+    <t>41 Roberts Avenue, Aramoho</t>
+  </si>
+  <si>
+    <t>1087426 - 00070331 - DG Label</t>
+  </si>
+  <si>
+    <t>1085967 - 00038230 - DG Label</t>
+  </si>
+  <si>
+    <t>1085964 - 00042172 - DG Label</t>
+  </si>
+  <si>
+    <t>65 Tennants Road, Bulls</t>
+  </si>
+  <si>
+    <t>18 Ataahua Place, Featherston, 5710</t>
+  </si>
+  <si>
+    <t>51 Southdown Drive, Martinborough, Hillside, Martinborough</t>
+  </si>
+  <si>
+    <t>19 Bengston Street, Eketāhuna 4900</t>
+  </si>
+  <si>
+    <t>65 Hartwell Drive, Kelvin Grove, Palmerston North 4470</t>
+  </si>
+  <si>
+    <t>62 Hartwell Drive, Kelvin Grove, Palmerston North 4470</t>
+  </si>
+  <si>
+    <t>2/31 Moore Avenue, Tawhero, Whanganui 4501</t>
+  </si>
+  <si>
+    <t>219A Hinakura Road, Martinborough 5784</t>
   </si>
 </sst>
 </file>
@@ -2076,7 +2055,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2406,7 +2406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C333"/>
+  <dimension ref="A1:C328"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -2422,216 +2422,216 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C7" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C9" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B11" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C11" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C12" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B13" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B14" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C14" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C15" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C17" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C18" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>209</v>
+        <v>113</v>
       </c>
       <c r="B20" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C20" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -2639,65 +2639,65 @@
         <v>114</v>
       </c>
       <c r="B21" t="s">
-        <v>225</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C22" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>651</v>
       </c>
       <c r="C26" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -2708,7 +2708,7 @@
         <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -2719,7 +2719,7 @@
         <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -2730,7 +2730,7 @@
         <v>130</v>
       </c>
       <c r="C29" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -2741,7 +2741,7 @@
         <v>132</v>
       </c>
       <c r="C30" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -2749,21 +2749,21 @@
         <v>133</v>
       </c>
       <c r="B31" t="s">
-        <v>134</v>
+        <v>218</v>
       </c>
       <c r="C31" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" t="s">
         <v>135</v>
       </c>
-      <c r="B32" t="s">
-        <v>224</v>
-      </c>
       <c r="C32" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -2774,7 +2774,7 @@
         <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -2785,7 +2785,7 @@
         <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -2793,21 +2793,21 @@
         <v>140</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>141</v>
+      </c>
+      <c r="B36" t="s">
         <v>142</v>
       </c>
-      <c r="B36" t="s">
-        <v>141</v>
-      </c>
       <c r="C36" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -2818,7 +2818,7 @@
         <v>144</v>
       </c>
       <c r="C37" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
@@ -2829,7 +2829,7 @@
         <v>146</v>
       </c>
       <c r="C38" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
@@ -2840,7 +2840,7 @@
         <v>148</v>
       </c>
       <c r="C39" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
@@ -2851,7 +2851,7 @@
         <v>150</v>
       </c>
       <c r="C40" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
@@ -2862,7 +2862,7 @@
         <v>152</v>
       </c>
       <c r="C41" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -2873,7 +2873,7 @@
         <v>154</v>
       </c>
       <c r="C42" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
@@ -2884,7 +2884,7 @@
         <v>156</v>
       </c>
       <c r="C43" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
@@ -2895,7 +2895,7 @@
         <v>158</v>
       </c>
       <c r="C44" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
@@ -2906,7 +2906,7 @@
         <v>160</v>
       </c>
       <c r="C45" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
@@ -2917,7 +2917,7 @@
         <v>162</v>
       </c>
       <c r="C46" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -2928,7 +2928,7 @@
         <v>164</v>
       </c>
       <c r="C47" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
@@ -2939,7 +2939,7 @@
         <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
@@ -2950,964 +2950,964 @@
         <v>168</v>
       </c>
       <c r="C49" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>169</v>
+        <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="C50" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>171</v>
+        <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="C51" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C52" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B53" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C53" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C54" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>217</v>
-      </c>
-      <c r="C55" t="s">
-        <v>211</v>
+        <v>213</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B56" t="s">
-        <v>218</v>
+        <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>212</v>
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>216</v>
       </c>
       <c r="C59" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>217</v>
       </c>
       <c r="C60" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>222</v>
+        <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B62" t="s">
-        <v>223</v>
+        <v>19</v>
       </c>
       <c r="C62" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C63" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B64" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B65" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C67" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C68" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B69" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C69" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B70" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C70" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C71" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B72" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C72" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B73" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C73" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B74" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C74" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B75" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C75" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C76" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B78" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C78" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B79" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C79" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B80" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C80" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B81" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C81" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C82" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C83" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B84" t="s">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="C84" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B85" t="s">
-        <v>61</v>
+        <v>215</v>
       </c>
       <c r="C85" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B86" t="s">
-        <v>220</v>
+        <v>65</v>
       </c>
       <c r="C86" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B87" t="s">
-        <v>221</v>
+        <v>67</v>
       </c>
       <c r="C87" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B88" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C88" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B89" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C89" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B90" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C90" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C91" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B92" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C92" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B93" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C93" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B94" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C94" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C95" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B96" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C96" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B97" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C97" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B98" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C98" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B99" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C99" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B100" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C100" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B101" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C101" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B102" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C102" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B103" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C103" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C104" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C106" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C107" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C108" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C109" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>108</v>
+        <v>234</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>110</v>
+        <v>233</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="C111" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>112</v>
+        <v>231</v>
       </c>
       <c r="B112" t="s">
-        <v>113</v>
+        <v>230</v>
       </c>
       <c r="C112" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="B113" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
       <c r="C113" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B114" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="C114" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B115" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C115" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B116" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="C116" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B117" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C117" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B118" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C118" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B119" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C119" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B120" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C120" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B121" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C121" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B122" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C122" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B123" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C123" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B124" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C124" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="B125" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="C125" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="B126" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="C126" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="B127" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="C127" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="B128" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C128" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B129" t="s">
-        <v>255</v>
+        <v>652</v>
       </c>
       <c r="C129" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B130" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B131" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="C131" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B132" t="s">
-        <v>249</v>
+        <v>391</v>
       </c>
       <c r="C132" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B133" t="s">
-        <v>407</v>
+        <v>264</v>
       </c>
       <c r="C133" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
+        <v>265</v>
+      </c>
+      <c r="B134" t="s">
         <v>266</v>
       </c>
-      <c r="B134" t="s">
-        <v>267</v>
-      </c>
       <c r="C134" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
+        <v>267</v>
+      </c>
+      <c r="B135" t="s">
         <v>268</v>
       </c>
-      <c r="B135" t="s">
-        <v>269</v>
-      </c>
       <c r="C135" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
+        <v>269</v>
+      </c>
+      <c r="B136" t="s">
         <v>270</v>
       </c>
-      <c r="B136" t="s">
-        <v>408</v>
-      </c>
       <c r="C136" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
@@ -3918,7 +3918,7 @@
         <v>272</v>
       </c>
       <c r="C137" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
@@ -3926,54 +3926,54 @@
         <v>273</v>
       </c>
       <c r="B138" t="s">
-        <v>274</v>
+        <v>559</v>
       </c>
       <c r="C138" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
+        <v>274</v>
+      </c>
+      <c r="B139" t="s">
         <v>275</v>
       </c>
-      <c r="B139" t="s">
-        <v>276</v>
-      </c>
       <c r="C139" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
+        <v>276</v>
+      </c>
+      <c r="B140" t="s">
         <v>277</v>
       </c>
-      <c r="B140" t="s">
-        <v>278</v>
-      </c>
       <c r="C140" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
+        <v>278</v>
+      </c>
+      <c r="B141" t="s">
         <v>279</v>
       </c>
-      <c r="B141" t="s">
-        <v>280</v>
-      </c>
       <c r="C141" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
+        <v>280</v>
+      </c>
+      <c r="B142" t="s">
         <v>281</v>
       </c>
-      <c r="B142" t="s">
-        <v>615</v>
-      </c>
       <c r="C142" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
@@ -3984,7 +3984,7 @@
         <v>283</v>
       </c>
       <c r="C143" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
@@ -3995,7 +3995,7 @@
         <v>285</v>
       </c>
       <c r="C144" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
@@ -4006,7 +4006,7 @@
         <v>287</v>
       </c>
       <c r="C145" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
@@ -4017,7 +4017,7 @@
         <v>289</v>
       </c>
       <c r="C146" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
@@ -4028,7 +4028,7 @@
         <v>291</v>
       </c>
       <c r="C147" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
@@ -4039,7 +4039,7 @@
         <v>293</v>
       </c>
       <c r="C148" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
@@ -4050,7 +4050,7 @@
         <v>295</v>
       </c>
       <c r="C149" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -4061,7 +4061,7 @@
         <v>297</v>
       </c>
       <c r="C150" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -4072,7 +4072,7 @@
         <v>299</v>
       </c>
       <c r="C151" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
@@ -4083,7 +4083,7 @@
         <v>301</v>
       </c>
       <c r="C152" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
@@ -4094,7 +4094,7 @@
         <v>303</v>
       </c>
       <c r="C153" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
@@ -4105,7 +4105,7 @@
         <v>305</v>
       </c>
       <c r="C154" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
@@ -4113,10 +4113,10 @@
         <v>306</v>
       </c>
       <c r="B155" t="s">
-        <v>307</v>
+        <v>653</v>
       </c>
       <c r="C155" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
@@ -4127,7 +4127,7 @@
         <v>309</v>
       </c>
       <c r="C156" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
@@ -4138,7 +4138,7 @@
         <v>311</v>
       </c>
       <c r="C157" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
@@ -4149,7 +4149,7 @@
         <v>313</v>
       </c>
       <c r="C158" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
@@ -4160,7 +4160,7 @@
         <v>315</v>
       </c>
       <c r="C159" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
@@ -4171,7 +4171,7 @@
         <v>317</v>
       </c>
       <c r="C160" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
@@ -4182,7 +4182,7 @@
         <v>319</v>
       </c>
       <c r="C161" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
@@ -4193,7 +4193,7 @@
         <v>321</v>
       </c>
       <c r="C162" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
@@ -4204,7 +4204,7 @@
         <v>323</v>
       </c>
       <c r="C163" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
@@ -4215,7 +4215,7 @@
         <v>325</v>
       </c>
       <c r="C164" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
@@ -4226,7 +4226,7 @@
         <v>327</v>
       </c>
       <c r="C165" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
@@ -4237,7 +4237,7 @@
         <v>329</v>
       </c>
       <c r="C166" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
@@ -4248,7 +4248,7 @@
         <v>331</v>
       </c>
       <c r="C167" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
@@ -4259,7 +4259,7 @@
         <v>333</v>
       </c>
       <c r="C168" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
@@ -4270,7 +4270,7 @@
         <v>335</v>
       </c>
       <c r="C169" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
@@ -4281,7 +4281,7 @@
         <v>337</v>
       </c>
       <c r="C170" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
@@ -4292,7 +4292,7 @@
         <v>339</v>
       </c>
       <c r="C171" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
@@ -4303,7 +4303,7 @@
         <v>341</v>
       </c>
       <c r="C172" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
@@ -4311,208 +4311,208 @@
         <v>342</v>
       </c>
       <c r="B173" t="s">
-        <v>343</v>
+        <v>654</v>
       </c>
       <c r="C173" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
+        <v>343</v>
+      </c>
+      <c r="B174" t="s">
         <v>344</v>
       </c>
-      <c r="B174" t="s">
-        <v>345</v>
-      </c>
       <c r="C174" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
+        <v>345</v>
+      </c>
+      <c r="B175" t="s">
         <v>346</v>
       </c>
-      <c r="B175" t="s">
-        <v>347</v>
-      </c>
       <c r="C175" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B176" t="s">
-        <v>349</v>
+        <v>656</v>
       </c>
       <c r="C176" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B177" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C177" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B178" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C178" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B179" t="s">
-        <v>355</v>
+        <v>307</v>
       </c>
       <c r="C179" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B180" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C180" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B181" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C181" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B182" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C182" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B183" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C183" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B184" t="s">
-        <v>317</v>
+        <v>362</v>
       </c>
       <c r="C184" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B185" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C185" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B186" t="s">
-        <v>368</v>
+        <v>655</v>
       </c>
       <c r="C186" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B187" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C187" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B188" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="C188" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="B189" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C189" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B190" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C190" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B191" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C191" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
@@ -4520,76 +4520,76 @@
         <v>379</v>
       </c>
       <c r="B192" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C192" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B193" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C193" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>402</v>
+        <v>375</v>
       </c>
       <c r="B194" t="s">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="C194" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="B195" t="s">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="C195" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="B196" t="s">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="C196" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="B197" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="C197" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B198" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C198" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
@@ -4597,692 +4597,692 @@
         <v>392</v>
       </c>
       <c r="B199" t="s">
-        <v>391</v>
+        <v>449</v>
       </c>
       <c r="C199" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B200" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C200" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B201" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C201" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="B202" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="C202" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="B203" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C203" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B204" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C204" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B205" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C205" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B206" t="s">
-        <v>474</v>
+        <v>406</v>
       </c>
       <c r="C206" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B207" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C207" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B208" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C208" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B209" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C209" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B210" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C210" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B211" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C211" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B212" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C212" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B213" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C213" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
+        <v>648</v>
+      </c>
+      <c r="B214" t="s">
         <v>424</v>
       </c>
-      <c r="B214" t="s">
-        <v>425</v>
-      </c>
       <c r="C214" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B215" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C215" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B216" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C216" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>430</v>
+        <v>649</v>
       </c>
       <c r="B217" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C217" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="B218" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C218" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B219" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C219" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B220" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C220" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B221" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C221" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B222" t="s">
         <v>445</v>
       </c>
       <c r="C222" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B223" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C223" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B224" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C224" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B225" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="C225" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B226" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="C226" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="B227" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="C227" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="B228" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="C228" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B229" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C229" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B230" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C230" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="B231" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="C231" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="B232" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="C232" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="B233" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="C233" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="B234" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C234" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B235" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C235" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B236" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C236" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B237" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C237" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="B238" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C238" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B239" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C239" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B240" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C240" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B241" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C241" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B242" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C242" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B243" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C243" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B244" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C244" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B245" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C245" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B246" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C246" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B247" t="s">
         <v>492</v>
       </c>
       <c r="C247" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B248" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C248" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B249" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C249" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="B250" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="C250" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B251" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C251" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B252" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C252" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B253" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C253" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B254" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C254" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B255" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C255" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B256" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C256" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B257" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C257" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="B258" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="C258" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="B259" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="C259" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B260" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C260" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B261" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C261" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
@@ -5290,791 +5290,745 @@
         <v>521</v>
       </c>
       <c r="B262" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C262" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="B263" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="C263" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="B264" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="C264" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="B265" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="C265" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="B266" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="C266" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="B267" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="C267" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>533</v>
+        <v>509</v>
       </c>
       <c r="B268" t="s">
-        <v>534</v>
+        <v>508</v>
       </c>
       <c r="C268" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B269" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C269" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B270" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C270" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B271" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="C271" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="B272" t="s">
-        <v>542</v>
+        <v>657</v>
       </c>
       <c r="C272" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B273" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C273" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B274" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="C274" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B275" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="C275" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B276" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C276" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B277" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C277" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>580</v>
+        <v>547</v>
       </c>
       <c r="B278" t="s">
-        <v>579</v>
+        <v>548</v>
       </c>
       <c r="C278" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>578</v>
+        <v>549</v>
       </c>
       <c r="B279" t="s">
-        <v>577</v>
+        <v>550</v>
       </c>
       <c r="C279" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>576</v>
+        <v>551</v>
       </c>
       <c r="B280" t="s">
-        <v>575</v>
+        <v>552</v>
       </c>
       <c r="C280" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="B281" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
       <c r="C281" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>572</v>
+        <v>555</v>
       </c>
       <c r="B282" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="C282" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="B283" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="C283" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="B284" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="C284" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B285" t="s">
-        <v>565</v>
+        <v>388</v>
       </c>
       <c r="C285" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
+        <v>563</v>
+      </c>
+      <c r="B286" t="s">
         <v>564</v>
       </c>
-      <c r="B286" t="s">
-        <v>563</v>
-      </c>
       <c r="C286" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B287" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C287" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B288" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="C288" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="B289" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="C289" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="B290" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="C290" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="B291" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="C291" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B292" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C292" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="B293" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C293" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B294" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="C294" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B295" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="C295" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B296" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="C296" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B297" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C297" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B298" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C298" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B299" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C299" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="B300" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C300" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B301" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C301" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B302" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C302" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="B303" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C303" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="B304" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C304" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="B305" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C305" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="B306" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C306" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="B307" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="C307" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B308" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C308" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="B309" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="C309" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="B310" t="s">
-        <v>404</v>
+        <v>612</v>
       </c>
       <c r="C310" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B311" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C311" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B312" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="C312" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B313" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C313" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B314" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C314" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B315" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C315" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B316" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C316" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="B317" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="C317" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="B318" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C318" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="B319" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C319" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="B320" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C320" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="B321" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C321" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="B322" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="C322" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="B323" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="C323" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="B324" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C324" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="B325" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C325" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="B326" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C326" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B327" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C327" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="B328" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C328" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A329" t="s">
-        <v>655</v>
-      </c>
-      <c r="B329" t="s">
-        <v>660</v>
-      </c>
-      <c r="C329" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A330" t="s">
-        <v>656</v>
-      </c>
-      <c r="B330" t="s">
-        <v>661</v>
-      </c>
-      <c r="C330" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A331" t="s">
-        <v>657</v>
-      </c>
-      <c r="B331" t="s">
-        <v>662</v>
-      </c>
-      <c r="C331" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A332" t="s">
-        <v>658</v>
-      </c>
-      <c r="B332" t="s">
-        <v>663</v>
-      </c>
-      <c r="C332" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A333" t="s">
-        <v>659</v>
-      </c>
-      <c r="B333" t="s">
-        <v>664</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1048576 B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="976" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{375B7B98-5CFF-4E53-B9E9-E693E2EA3BC8}"/>
+  <xr:revisionPtr revIDLastSave="1121" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37B70C33-3AED-4CC2-A60A-320CE49B3DAC}"/>
   <bookViews>
-    <workbookView xWindow="54495" yWindow="-7665" windowWidth="26010" windowHeight="20985" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
+    <workbookView xWindow="28695" yWindow="-7665" windowWidth="25995" windowHeight="20985" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="711">
   <si>
     <t>Job</t>
   </si>
@@ -56,9 +56,6 @@
     <t>1084464 - 00050442 - DG Label</t>
   </si>
   <si>
-    <t>1084462 - 00048230 - DG Label</t>
-  </si>
-  <si>
     <t>1084461 - 00050984 - DG Label</t>
   </si>
   <si>
@@ -101,12 +98,6 @@
     <t>10 Malcolm Street, Martinborough</t>
   </si>
   <si>
-    <t>1083905 - 00046581 - DG Label</t>
-  </si>
-  <si>
-    <t>43 Taranaki Street, Masterton</t>
-  </si>
-  <si>
     <t>1083903 - 00049965 - DG Label</t>
   </si>
   <si>
@@ -161,12 +152,6 @@
     <t>24 Ardsley Lane, Lansdowne</t>
   </si>
   <si>
-    <t>1083705 - 00031383 - DG Label</t>
-  </si>
-  <si>
-    <t>10 Alton Grove, Masterton</t>
-  </si>
-  <si>
     <t>1083699 - 00059938 - DG Label</t>
   </si>
   <si>
@@ -191,12 +176,6 @@
     <t>329 Chester Road, Carterton</t>
   </si>
   <si>
-    <t>1083537 - 00051885 - DG Label</t>
-  </si>
-  <si>
-    <t>5 Mervyn Brown Place, Solway</t>
-  </si>
-  <si>
     <t>1083536 - 00051887 - DG Label</t>
   </si>
   <si>
@@ -341,12 +320,6 @@
     <t>22 South Street, Feilding</t>
   </si>
   <si>
-    <t>1083037 - 00042253 - DG Label</t>
-  </si>
-  <si>
-    <t>2 Kaka Street, Masterton</t>
-  </si>
-  <si>
     <t>1083036 - 00050431 - DG Label</t>
   </si>
   <si>
@@ -608,12 +581,6 @@
     <t>70B DUBLIN STREET , MARTINBOROUGH, 5711</t>
   </si>
   <si>
-    <t>1082574 - 00014488  - DG Label -0037559000WRE8B</t>
-  </si>
-  <si>
-    <t>64 CORNWALL STREET , MASTERTON, 5810</t>
-  </si>
-  <si>
     <t>1082527 - 00052277 - DG Label - 0000065056CP68A</t>
   </si>
   <si>
@@ -626,12 +593,6 @@
     <t>1 Cotterville Crescent, Greytown, 5712</t>
   </si>
   <si>
-    <t>1082525 - 00042914 - DG Label - 1000574372PC7FE</t>
-  </si>
-  <si>
-    <t>13 MERVYN BROWN PLACE, SOLWAY, MASTERTON, 5810</t>
-  </si>
-  <si>
     <t>1082489 - 00042252 - DG Label - 0666001531PCF45</t>
   </si>
   <si>
@@ -674,9 +635,6 @@
     <t>99A Lees Pakaraka Road, Masterton</t>
   </si>
   <si>
-    <t>67A Perry Street, Masterton</t>
-  </si>
-  <si>
     <t>80 West Street, Greytown</t>
   </si>
   <si>
@@ -800,12 +758,6 @@
     <t>1085285 - 00054784 - DG Label</t>
   </si>
   <si>
-    <t>4 Barracks Avenue, Solway</t>
-  </si>
-  <si>
-    <t>1085290 - 00059953 - DG Label</t>
-  </si>
-  <si>
     <t>1965B State Highway 2, Greytown</t>
   </si>
   <si>
@@ -815,21 +767,12 @@
     <t>1085378 - 00050724 - DG Label</t>
   </si>
   <si>
-    <t>1085377 - 00052076 - DG Label</t>
-  </si>
-  <si>
-    <t>8C Michael Street, Masterton</t>
-  </si>
-  <si>
     <t>1085376 - 00064756 - DG Label</t>
   </si>
   <si>
     <t>6A Garrity Lane, Greytown</t>
   </si>
   <si>
-    <t>1085373 - 00037564 - DG Label</t>
-  </si>
-  <si>
     <t>1085371 - 00053149 - DG Label</t>
   </si>
   <si>
@@ -959,9 +902,6 @@
     <t>154 Watershed Road, Bunnythorpe</t>
   </si>
   <si>
-    <t>1085625 - 00059698 - DG Label</t>
-  </si>
-  <si>
     <t>15 Tangimoana Road, Ohakea</t>
   </si>
   <si>
@@ -983,12 +923,6 @@
     <t>295 Dalefield Road, Dalefield</t>
   </si>
   <si>
-    <t>1085619 - 00054760 - DG Label</t>
-  </si>
-  <si>
-    <t>42 Johnstone Drive, Fitzherbert</t>
-  </si>
-  <si>
     <t>1085737 - 00064071 - DG Label</t>
   </si>
   <si>
@@ -1007,12 +941,6 @@
     <t>9 Fox Road, Springvale</t>
   </si>
   <si>
-    <t>1085732 - 00030245 - DG Label</t>
-  </si>
-  <si>
-    <t>47 Kowhai Street, Castlecliff</t>
-  </si>
-  <si>
     <t>1085731 - 00029753 - DG Label</t>
   </si>
   <si>
@@ -1049,12 +977,6 @@
     <t>2187 State Highway 3, Sanson</t>
   </si>
   <si>
-    <t>1085722 - 00047186 - DG Label</t>
-  </si>
-  <si>
-    <t>36 Cloverlea Road, Westbrook</t>
-  </si>
-  <si>
     <t>1085721 - 00054363 - DG Label</t>
   </si>
   <si>
@@ -1082,9 +1004,6 @@
     <t>52 Surrey Road, Springvale</t>
   </si>
   <si>
-    <t>1085715 - 00030535 - DG Label</t>
-  </si>
-  <si>
     <t>1085714 - 00048298 - DG Label</t>
   </si>
   <si>
@@ -1106,45 +1025,18 @@
     <t>13 Fantail Avenue, Carterton</t>
   </si>
   <si>
-    <t>1085842 - 00059955 - DG Label</t>
-  </si>
-  <si>
-    <t>572 Kelvin Grove Road, Kelvin Grove</t>
-  </si>
-  <si>
     <t>1085841 - 00060910 - DG Label</t>
   </si>
   <si>
     <t>20B Donovans Road, Masterton</t>
   </si>
   <si>
-    <t>1085840 - 00062204 - DG Label</t>
-  </si>
-  <si>
-    <t>24 Pokerekere Crescent, Kelvin Grove</t>
-  </si>
-  <si>
-    <t>1085838 - 00058379 - DG Label</t>
-  </si>
-  <si>
-    <t>2E Hogg Crescent, Masterton</t>
-  </si>
-  <si>
     <t>1085917 - 00056807 - DG Label</t>
   </si>
   <si>
     <t>33 Hughes Line, Clareville</t>
   </si>
   <si>
-    <t>1085915 - 00061776 - DG Label</t>
-  </si>
-  <si>
-    <t>1085914 - 00062074 - DG Label</t>
-  </si>
-  <si>
-    <t>12 Edenmore Terrace, Fitzherbert</t>
-  </si>
-  <si>
     <t>1132 Pohangina Valley East Road, Pohangina</t>
   </si>
   <si>
@@ -1193,30 +1085,12 @@
     <t>1086019 - 00051506 - DG Label</t>
   </si>
   <si>
-    <t>22 Tukere Crescent, Kelvin Grove</t>
-  </si>
-  <si>
-    <t>1086020 - 00052189 - DG Label</t>
-  </si>
-  <si>
-    <t>21 Sandown Avenue, Himatangi Beach</t>
-  </si>
-  <si>
-    <t>1086021 - 00056665 - DG Label</t>
-  </si>
-  <si>
-    <t>329 Kahuterawa Road, Linton</t>
-  </si>
-  <si>
     <t>1086116 - 00052128 - DG Label</t>
   </si>
   <si>
     <t>93 Chester Road, Clareville</t>
   </si>
   <si>
-    <t>41 Kowhai Street, Castelcliff, Whanganui, 4501</t>
-  </si>
-  <si>
     <t>1086155 - 00059130 - DG Label</t>
   </si>
   <si>
@@ -1256,24 +1130,12 @@
     <t>88 Oxford Street, Ashhurst</t>
   </si>
   <si>
-    <t>1086195 - 00062723 - DG Label</t>
-  </si>
-  <si>
-    <t>44b James Line, Kelvin Grove</t>
-  </si>
-  <si>
     <t>1086288 - 00059442 - DG Label</t>
   </si>
   <si>
     <t>38 Marybank Road, Marybank</t>
   </si>
   <si>
-    <t>1086286 - 00054776 - DG Label</t>
-  </si>
-  <si>
-    <t>10 Browning Place, Roslyn</t>
-  </si>
-  <si>
     <t>1086285 - 00067399 - DG Label</t>
   </si>
   <si>
@@ -1334,36 +1196,18 @@
     <t>49 Mt Biggs Road, Halcombe</t>
   </si>
   <si>
-    <t>1086424 - 00065363 - DG Label</t>
-  </si>
-  <si>
-    <t>377 Gillespies Line, Kairanga</t>
-  </si>
-  <si>
     <t>33 Harvest Lane, Newbury</t>
   </si>
   <si>
     <t>1086475 - 00064074 - DG Label</t>
   </si>
   <si>
-    <t>29 Balmoral Drive, Terrace End</t>
-  </si>
-  <si>
-    <t>1086476 - 00062189 - DG Label</t>
-  </si>
-  <si>
     <t>91 Managhs Road, Halcombe</t>
   </si>
   <si>
     <t>1086478 - 00060479 - DG Label</t>
   </si>
   <si>
-    <t>60 Purnell Street, College Estate</t>
-  </si>
-  <si>
-    <t>1086482 - 00061638 - DG Label</t>
-  </si>
-  <si>
     <t>1065 Rongotea Road, Rongotea</t>
   </si>
   <si>
@@ -1415,18 +1259,6 @@
     <t>1119A Camerons Line, Aorangi</t>
   </si>
   <si>
-    <t>1086652 - 00059021 - DG Label</t>
-  </si>
-  <si>
-    <t>5 Pastoral Lane, Hokowhitu</t>
-  </si>
-  <si>
-    <t>1086651 - 00058544 - DG Label</t>
-  </si>
-  <si>
-    <t>3 Tutakarae Road, Kelvin Grove</t>
-  </si>
-  <si>
     <t>1086649 - 00056472 - DG Label</t>
   </si>
   <si>
@@ -1457,12 +1289,6 @@
     <t>146 Mill Road, Rongotea</t>
   </si>
   <si>
-    <t>1086639 - 00056782 - DG Label</t>
-  </si>
-  <si>
-    <t>173 Valley Views, Fitzherbert</t>
-  </si>
-  <si>
     <t>1086637 - 00056454 - DG Label</t>
   </si>
   <si>
@@ -1475,12 +1301,6 @@
     <t>4 Whio Avenue, Feilding</t>
   </si>
   <si>
-    <t>1086618 - 00053389 - DG Label</t>
-  </si>
-  <si>
-    <t>58B London Street, Kimbolton</t>
-  </si>
-  <si>
     <t>1086616 - 00061593 - DG Label</t>
   </si>
   <si>
@@ -1505,30 +1325,12 @@
     <t>1086967 - 00057376 - DG Label</t>
   </si>
   <si>
-    <t>110 Fitzroy Street, Terrace End</t>
-  </si>
-  <si>
-    <t>1086969 - 00045408 - DG Label</t>
-  </si>
-  <si>
-    <t>1 Bunny Street, Masterton</t>
-  </si>
-  <si>
-    <t>1086970 - 00057969 - DG Label</t>
-  </si>
-  <si>
     <t>271 Scotts Road, Linton</t>
   </si>
   <si>
     <t>1086971 - 00048813 - DG Label</t>
   </si>
   <si>
-    <t>1087125 - 00063134 - DG Label</t>
-  </si>
-  <si>
-    <t>34 Caroline Crescent, Highbury</t>
-  </si>
-  <si>
     <t>1087124 - 00060146 - DG Label</t>
   </si>
   <si>
@@ -1547,12 +1349,6 @@
     <t>27 Mahoney Street, Whanganui East</t>
   </si>
   <si>
-    <t>1087116 - 00052080 - DG Label</t>
-  </si>
-  <si>
-    <t>23 Renall Street, Masterton</t>
-  </si>
-  <si>
     <t>1087115 - 00056539 - DG Label</t>
   </si>
   <si>
@@ -1577,60 +1373,18 @@
     <t>1087139 - 00064745 - DG Label</t>
   </si>
   <si>
-    <t>257 Victoria Avenue, Hokowhitu</t>
-  </si>
-  <si>
-    <t>1087140 - 00065085 - DG Label</t>
-  </si>
-  <si>
     <t>163 Nannestads Line, Bunnythorpe</t>
   </si>
   <si>
     <t>1087141 - 00065202 - DG Label</t>
   </si>
   <si>
-    <t>6 Goodwyn Crescent, Hokowhitu</t>
-  </si>
-  <si>
-    <t>1087142 - 00065225 - DG Label</t>
-  </si>
-  <si>
-    <t>47 Collingwood Street, Hokowhitu</t>
-  </si>
-  <si>
-    <t>1087143 - 00065762 - DG Label</t>
-  </si>
-  <si>
-    <t>1 Sunshine Place, Kelvin Grove</t>
-  </si>
-  <si>
-    <t>1087144 - 00067318 - DG Label</t>
-  </si>
-  <si>
-    <t>65 Stanley Avenue, Palmerston North</t>
-  </si>
-  <si>
-    <t>1087145 - 00027716 - DG Label</t>
-  </si>
-  <si>
-    <t>84 Waicola Drive, Fitzherbert</t>
-  </si>
-  <si>
-    <t>1087146 - 00028635 - DG Label</t>
-  </si>
-  <si>
     <t>208 John F Kennedy Drive, Milson</t>
   </si>
   <si>
     <t>1087147 - 00040396 - DG Label</t>
   </si>
   <si>
-    <t>32 Lincoln Terrace, Hokowhitu</t>
-  </si>
-  <si>
-    <t>1087148 - 00053854 - DG Label</t>
-  </si>
-  <si>
     <t>1087281 - 00067739 - DG Label</t>
   </si>
   <si>
@@ -1670,24 +1424,6 @@
     <t>42 Harrison Street, Whanganui</t>
   </si>
   <si>
-    <t>1087299 - 00065802 - DG Label</t>
-  </si>
-  <si>
-    <t>69 Marne Street, Hokowhitu</t>
-  </si>
-  <si>
-    <t>1087298 - 00065746 - DG Label</t>
-  </si>
-  <si>
-    <t>25 Highbury Avenue, Highbury</t>
-  </si>
-  <si>
-    <t>1087297 - 00065704 - DG Label</t>
-  </si>
-  <si>
-    <t>32 Armagh Terrace, Marton</t>
-  </si>
-  <si>
     <t>1087365 - 00065152 - DG Label</t>
   </si>
   <si>
@@ -1700,12 +1436,6 @@
     <t>25C Stonebridge Heights, Feilding</t>
   </si>
   <si>
-    <t>1087363 - 00066901 - DG Label</t>
-  </si>
-  <si>
-    <t>40 Parkland Crescent, Terrace End</t>
-  </si>
-  <si>
     <t>1087361 - 00053770 - DG Label</t>
   </si>
   <si>
@@ -1727,15 +1457,6 @@
     <t>220 Kahuterawa Road, Linton</t>
   </si>
   <si>
-    <t>1087503 - 00058006 - DG Label</t>
-  </si>
-  <si>
-    <t>1087501 - 00056422 - DG Label</t>
-  </si>
-  <si>
-    <t>104 Clifton Terrace, Fitzherbert</t>
-  </si>
-  <si>
     <t>1087499 - 00062081 - DG Label</t>
   </si>
   <si>
@@ -1748,30 +1469,12 @@
     <t>18 Pukeko Road, Bunnythorpe</t>
   </si>
   <si>
-    <t>1087497 - 00057207 - DG Label</t>
-  </si>
-  <si>
-    <t>104 Slacks Road, Awapuni</t>
-  </si>
-  <si>
-    <t>1087495 - 00065119 - DG Label</t>
-  </si>
-  <si>
-    <t>69 Meridian Grove, Kelvin Grove</t>
-  </si>
-  <si>
     <t>1087492 - 00059113 - DG Label</t>
   </si>
   <si>
     <t>577 Hughes Line, East Taratahi</t>
   </si>
   <si>
-    <t>1087547 - 00063691 - DG Label</t>
-  </si>
-  <si>
-    <t>30 Nicholson Drive, Kaitoke</t>
-  </si>
-  <si>
     <t>1087546 - 00066181 - DG Label</t>
   </si>
   <si>
@@ -1796,12 +1499,6 @@
     <t>601 Oroua Valley Road, Apiti</t>
   </si>
   <si>
-    <t>1087542 - 00059047 - DG Label</t>
-  </si>
-  <si>
-    <t>58 Skerman Street, Marton</t>
-  </si>
-  <si>
     <t>1087541 - 00057987 - DG Label</t>
   </si>
   <si>
@@ -1820,12 +1517,6 @@
     <t>245 Millricks Line, Linton</t>
   </si>
   <si>
-    <t>1087563 - 00065474 - DG Label</t>
-  </si>
-  <si>
-    <t>11 The Oaks, Awapuni</t>
-  </si>
-  <si>
     <t>1087561 - 00051746 - DG Label</t>
   </si>
   <si>
@@ -1835,63 +1526,27 @@
     <t>1087623 - 00071450 - DG Label</t>
   </si>
   <si>
-    <t>1087622 - 00068633 - DG Label</t>
-  </si>
-  <si>
-    <t>1087621 - 00065427 - DG Label</t>
-  </si>
-  <si>
-    <t>1087620 - 00015005 - DG Label</t>
-  </si>
-  <si>
     <t>1087619 - 00060420 - DG Label</t>
   </si>
   <si>
     <t>286 Hewitts Road, Linton</t>
   </si>
   <si>
-    <t>25 Montgomery Terrace</t>
-  </si>
-  <si>
-    <t>25 Elmira Avenue, Hokowhitu</t>
-  </si>
-  <si>
-    <t>94 Amberley Avenue, Highbury</t>
-  </si>
-  <si>
     <t>11 Tūere Place, Hokowhitu</t>
   </si>
   <si>
-    <t>1087798 - 00062077 - DG Label</t>
-  </si>
-  <si>
-    <t>7 Caffray Avenue, Aramoho</t>
-  </si>
-  <si>
     <t>1087797 - 00060025 - DG Label</t>
   </si>
   <si>
     <t>20 Dickens Lane, Otamatea</t>
   </si>
   <si>
-    <t>1087796 - 00056888 - DG Label</t>
-  </si>
-  <si>
-    <t>210 Heads Road, Gonville</t>
-  </si>
-  <si>
     <t>1087795 - 00014068 - DG Label</t>
   </si>
   <si>
     <t>77 Wikitoria Road, Whanganui Airport</t>
   </si>
   <si>
-    <t>1087794 - 00062249 - DG Label</t>
-  </si>
-  <si>
-    <t>11 McGregor Crescent, Masterton</t>
-  </si>
-  <si>
     <t>1087793 - 00064585 - DG Label</t>
   </si>
   <si>
@@ -1904,24 +1559,6 @@
     <t>4 Mana Place, Awapuni</t>
   </si>
   <si>
-    <t>1087790 - 00065126 - DG Label</t>
-  </si>
-  <si>
-    <t>533 Kelvin Grove Road, Kelvin Grove</t>
-  </si>
-  <si>
-    <t>1087789 - 00056263 - DG Label</t>
-  </si>
-  <si>
-    <t>20 Abby Road, Fitzherbert</t>
-  </si>
-  <si>
-    <t>1087788 - 00061007 - DG Label</t>
-  </si>
-  <si>
-    <t>57A Manuka Street, Lansdowne</t>
-  </si>
-  <si>
     <t>1087787 - 00067838 - DG Label</t>
   </si>
   <si>
@@ -1934,12 +1571,6 @@
     <t>330 Aokautere Drive, Aokautere</t>
   </si>
   <si>
-    <t>1087785 - 00070481 - DG Label</t>
-  </si>
-  <si>
-    <t>15 Union Street, Hokowhitu</t>
-  </si>
-  <si>
     <t>1087784 - 00063340 - DG Label</t>
   </si>
   <si>
@@ -1976,12 +1607,6 @@
     <t>1185C Halcombe Road, Halcombe</t>
   </si>
   <si>
-    <t>1087778 - 00062453 - DG Label</t>
-  </si>
-  <si>
-    <t>41 Roberts Avenue, Aramoho</t>
-  </si>
-  <si>
     <t>1087426 - 00070331 - DG Label</t>
   </si>
   <si>
@@ -2000,19 +1625,553 @@
     <t>51 Southdown Drive, Martinborough, Hillside, Martinborough</t>
   </si>
   <si>
-    <t>19 Bengston Street, Eketāhuna 4900</t>
-  </si>
-  <si>
     <t>65 Hartwell Drive, Kelvin Grove, Palmerston North 4470</t>
   </si>
   <si>
-    <t>62 Hartwell Drive, Kelvin Grove, Palmerston North 4470</t>
-  </si>
-  <si>
-    <t>2/31 Moore Avenue, Tawhero, Whanganui 4501</t>
-  </si>
-  <si>
     <t>219A Hinakura Road, Martinborough 5784</t>
+  </si>
+  <si>
+    <t>1088887 - 00026051 - DG Label</t>
+  </si>
+  <si>
+    <t>1088886 - 00053928 - DG Label</t>
+  </si>
+  <si>
+    <t>1088885 - 00066896 - DG Label</t>
+  </si>
+  <si>
+    <t>1088884 - 00065773 - DG Label</t>
+  </si>
+  <si>
+    <t>1088883 - 00065780 - DG Label</t>
+  </si>
+  <si>
+    <t>1088882 - 00065753 - DG Label</t>
+  </si>
+  <si>
+    <t>1088881 - 00061641 - DG Label</t>
+  </si>
+  <si>
+    <t>1088880 - 00070508 - DG Label</t>
+  </si>
+  <si>
+    <t>1088879 - 00072240 - DG Label</t>
+  </si>
+  <si>
+    <t>1088878 - 00063302 - DG Label</t>
+  </si>
+  <si>
+    <t>1088877 - 00052160 - DG Label</t>
+  </si>
+  <si>
+    <t>1088876 - 00067028 - DG Label</t>
+  </si>
+  <si>
+    <t>1088875 - 00072583 - DG Label</t>
+  </si>
+  <si>
+    <t>1088874 - 00057954 - DG Label</t>
+  </si>
+  <si>
+    <t>1088820 - 00025077 - DG Label</t>
+  </si>
+  <si>
+    <t>1088819 - 00053582 - DG Label</t>
+  </si>
+  <si>
+    <t>1088817 - 00064077 - DG Label</t>
+  </si>
+  <si>
+    <t>1088816 - 00072235 - DG Label</t>
+  </si>
+  <si>
+    <t>1088815 - 00063313 - DG Label</t>
+  </si>
+  <si>
+    <t>1088809 - 00025169 - DG Label</t>
+  </si>
+  <si>
+    <t>1088808 - 00032041 - DG Label</t>
+  </si>
+  <si>
+    <t>1088807 - 00032682 - DG Label</t>
+  </si>
+  <si>
+    <t>1088806 - 00053919 - DG Label</t>
+  </si>
+  <si>
+    <t>1088782 - 00057571 - DG Label</t>
+  </si>
+  <si>
+    <t>1088779 - 00059485 - DG Label</t>
+  </si>
+  <si>
+    <t>1088778 - 00059487 - DG Label</t>
+  </si>
+  <si>
+    <t>1088776 - 00064091 - DG Label</t>
+  </si>
+  <si>
+    <t>1088773 - 00066333 - DG Label</t>
+  </si>
+  <si>
+    <t>1088771 - 00066336 - DG Label</t>
+  </si>
+  <si>
+    <t>1088770 - 00061872 - DG Label</t>
+  </si>
+  <si>
+    <t>1088769 - 00065767 - DG Label</t>
+  </si>
+  <si>
+    <t>1088768 - 00067149 - DG Label</t>
+  </si>
+  <si>
+    <t>1088766 - 00065178 - DG Label</t>
+  </si>
+  <si>
+    <t>1088764 - 00067788 - DG Label</t>
+  </si>
+  <si>
+    <t>1088740 - 00067491 - DG Label</t>
+  </si>
+  <si>
+    <t>1088737 - 00067725 - DG Label</t>
+  </si>
+  <si>
+    <t>1088734 - 00067456 - DG Label</t>
+  </si>
+  <si>
+    <t>1088729 - 00068423 - DG Label</t>
+  </si>
+  <si>
+    <t>1088727 - 00038775 - DG Label</t>
+  </si>
+  <si>
+    <t>1088725 - 00070510 - DG Label</t>
+  </si>
+  <si>
+    <t>1088724 - 00064099 - DG Label</t>
+  </si>
+  <si>
+    <t>1088723 - 00064106 - DG Label</t>
+  </si>
+  <si>
+    <t>1088721 - 00057186 - DG Label</t>
+  </si>
+  <si>
+    <t>1088681 - 00071920 - DG Label</t>
+  </si>
+  <si>
+    <t>1088598 - 00071744 - DG Label</t>
+  </si>
+  <si>
+    <t>1088595 - 00065195 - DG Label</t>
+  </si>
+  <si>
+    <t>1088592 - 00066903 - DG Label</t>
+  </si>
+  <si>
+    <t>1088590 - 00063407 - DG Label</t>
+  </si>
+  <si>
+    <t>1088588 - 00026057 - DG Label</t>
+  </si>
+  <si>
+    <t>1088584 - 00053238 - DG Label</t>
+  </si>
+  <si>
+    <t>1088583 - 00066503 - DG Label</t>
+  </si>
+  <si>
+    <t>1088579 - 00028107 - DG Label</t>
+  </si>
+  <si>
+    <t>1088577 - 00062943 - DG Label</t>
+  </si>
+  <si>
+    <t>1088575 - 00063305 - DG Label</t>
+  </si>
+  <si>
+    <t>1088574 - 00068534 - DG Label </t>
+  </si>
+  <si>
+    <t>1088571 - 00068782 - DG Label</t>
+  </si>
+  <si>
+    <t>1088570 - 00054294 - DG Label</t>
+  </si>
+  <si>
+    <t>1088421 - 00057272 - DG Label</t>
+  </si>
+  <si>
+    <t>1088415 - 00055248 - DG Label</t>
+  </si>
+  <si>
+    <t>1088409 - 00063303 - DG Label</t>
+  </si>
+  <si>
+    <t>1088406 - 00053648 - DG Label</t>
+  </si>
+  <si>
+    <t>1088404 - 00064339 - DG Label</t>
+  </si>
+  <si>
+    <t>1088400 - 00064087 - DG Label</t>
+  </si>
+  <si>
+    <t>1088393 - 00066868 - DG Label</t>
+  </si>
+  <si>
+    <t>1088342 - 00062220 - DG Label</t>
+  </si>
+  <si>
+    <t>1088341 - 00056617 - DG Label</t>
+  </si>
+  <si>
+    <t>1088340 - 00062870 - DG Label</t>
+  </si>
+  <si>
+    <t>1088339 - 00059700 - DG Label</t>
+  </si>
+  <si>
+    <t>1088338 - 00048651 - DG Label</t>
+  </si>
+  <si>
+    <t>1088334 - 00065862 - DG Label</t>
+  </si>
+  <si>
+    <t>1088333 - 00066000 - DG Label</t>
+  </si>
+  <si>
+    <t>1088332 - 00065610 - DG Label</t>
+  </si>
+  <si>
+    <t>1088330 - 00049791 - DG Label</t>
+  </si>
+  <si>
+    <t>1088322 - 00053961 - DG Label</t>
+  </si>
+  <si>
+    <t>1088321 - 00053962 - DG Label</t>
+  </si>
+  <si>
+    <t>1088320 - 00070509 - DG Label</t>
+  </si>
+  <si>
+    <t>1088317 - 00056952 - DG Label</t>
+  </si>
+  <si>
+    <t>1088315 - 00072243 - DG Label</t>
+  </si>
+  <si>
+    <t>1088314 - 00068632 - DG Label</t>
+  </si>
+  <si>
+    <t>1088312 - 00063585 - DG Label</t>
+  </si>
+  <si>
+    <t>1088311 - 00063050 - DG Label</t>
+  </si>
+  <si>
+    <t>1088307 - 00036744 - DG Label</t>
+  </si>
+  <si>
+    <t>1088306 - 00062076 - DG Label</t>
+  </si>
+  <si>
+    <t>1088304 - 00057103 - DG Label</t>
+  </si>
+  <si>
+    <t>1088303 - 00062284 - DG Label</t>
+  </si>
+  <si>
+    <t>1088302 - 00071638 - DG Label</t>
+  </si>
+  <si>
+    <t>1088252 - 00024700 - DG Label</t>
+  </si>
+  <si>
+    <t>1088250 - 00026437 - DG Label</t>
+  </si>
+  <si>
+    <t>1088240 - 00048022 - DG Label</t>
+  </si>
+  <si>
+    <t>1088239 - 00050670 - DG Label</t>
+  </si>
+  <si>
+    <t>1088226 - 00067692 - DG Label</t>
+  </si>
+  <si>
+    <t>52 Willow Park Drive, Opaki</t>
+  </si>
+  <si>
+    <t>150 Hinekura Road, Martinborough</t>
+  </si>
+  <si>
+    <t>34 Ngatarua Road, Whanganui</t>
+  </si>
+  <si>
+    <t>42 Benmore Avenue, Palmerston North</t>
+  </si>
+  <si>
+    <t>26 Fallow Avenue, Feilding</t>
+  </si>
+  <si>
+    <t>1 The Oaks, Awapuni</t>
+  </si>
+  <si>
+    <t>2A Dundas Road, Sanson</t>
+  </si>
+  <si>
+    <t>24 Coralie Place, Masterton</t>
+  </si>
+  <si>
+    <t>61 Evans Road, Masterton</t>
+  </si>
+  <si>
+    <t>16 Naples Street, Martinborough</t>
+  </si>
+  <si>
+    <t>131 Caveland Road, Carterton</t>
+  </si>
+  <si>
+    <t>45 Koputara Road, Foxton</t>
+  </si>
+  <si>
+    <t>138 Reid Line West, Feilding</t>
+  </si>
+  <si>
+    <t>57 Exeter Crescent, Whanganui</t>
+  </si>
+  <si>
+    <t>953C Kaiwhata Road, Carterton</t>
+  </si>
+  <si>
+    <t>30 Pickwick Road, Otamatea</t>
+  </si>
+  <si>
+    <t>150 Hansens Line, Newbury</t>
+  </si>
+  <si>
+    <t>160 Eyre Road, Linton</t>
+  </si>
+  <si>
+    <t>2 Craigmillar Street, Masterton</t>
+  </si>
+  <si>
+    <t>399A Lake Ferry Road, Dyerville</t>
+  </si>
+  <si>
+    <t>98 Titoki Street, Landsdowne</t>
+  </si>
+  <si>
+    <t>40 Feist Street, Carterton</t>
+  </si>
+  <si>
+    <t>6 South Featherston Road</t>
+  </si>
+  <si>
+    <t>885 State Highway 2</t>
+  </si>
+  <si>
+    <t>79 Cologne Street</t>
+  </si>
+  <si>
+    <t>808 State Highway 53</t>
+  </si>
+  <si>
+    <t>768A State Highway 2</t>
+  </si>
+  <si>
+    <t>24 Westwood Avenue, Greytown</t>
+  </si>
+  <si>
+    <t>97 Lincoln Road, Carterton</t>
+  </si>
+  <si>
+    <t>3931 Matahiwi Track</t>
+  </si>
+  <si>
+    <t>38 Cracroft Drive, Putiki</t>
+  </si>
+  <si>
+    <t>15 Oaklea Avenue, Marton</t>
+  </si>
+  <si>
+    <t>193 Fitzherbert Avenue</t>
+  </si>
+  <si>
+    <t>906C Reid Line East, Bunnythorpe</t>
+  </si>
+  <si>
+    <t>774 Kimbolton Road</t>
+  </si>
+  <si>
+    <t>344 Blueskin Road</t>
+  </si>
+  <si>
+    <t>85 Havelock Avenue</t>
+  </si>
+  <si>
+    <t>90D Paierau Road</t>
+  </si>
+  <si>
+    <t>14 Carlisle Street, Milson</t>
+  </si>
+  <si>
+    <t>52 Featherston Street</t>
+  </si>
+  <si>
+    <t>240C Blueskin Road</t>
+  </si>
+  <si>
+    <t>53 North Street, Greytown</t>
+  </si>
+  <si>
+    <t>143 West Street, Greytown</t>
+  </si>
+  <si>
+    <t>26 Henderson Street, Kimbolton</t>
+  </si>
+  <si>
+    <t>4 Mitre Way, Masterton</t>
+  </si>
+  <si>
+    <t>2 Barlow Road, Martinborough</t>
+  </si>
+  <si>
+    <t>45B Seafield Road, Whanganui</t>
+  </si>
+  <si>
+    <t>11 Poutini Street, Whanganui</t>
+  </si>
+  <si>
+    <t>69 Wood Street, Takaro</t>
+  </si>
+  <si>
+    <t>203 Ulysses Road, Ashhurst</t>
+  </si>
+  <si>
+    <t>9 Coralie Place, Masterton</t>
+  </si>
+  <si>
+    <t>1A Carrington Drive, Carterton</t>
+  </si>
+  <si>
+    <t>45 Pokerekere Crescent, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>5 Waltons Avenue, Carterton</t>
+  </si>
+  <si>
+    <t>17C Madison Street, Carterton</t>
+  </si>
+  <si>
+    <t>268 Mikimiki Road, Masterton</t>
+  </si>
+  <si>
+    <t>2A Cologne Street, Martinborough</t>
+  </si>
+  <si>
+    <t>835 State Highway 2, Masterton</t>
+  </si>
+  <si>
+    <t>6 Weld Street, Martinborough</t>
+  </si>
+  <si>
+    <t>37 Hereford Street, West End</t>
+  </si>
+  <si>
+    <t>333 Brandon Hall Road, Bulls</t>
+  </si>
+  <si>
+    <t>16 Cotter Street, Greytown</t>
+  </si>
+  <si>
+    <t>2 Garrity Lane</t>
+  </si>
+  <si>
+    <t>27 Hartwell Drive</t>
+  </si>
+  <si>
+    <t>4 Monaco Grove</t>
+  </si>
+  <si>
+    <t>80 Hamua Rongomai Road</t>
+  </si>
+  <si>
+    <t>136 Southdown Drive</t>
+  </si>
+  <si>
+    <t>1427 Whanganui River Road</t>
+  </si>
+  <si>
+    <t>Takahuri Block (aka #1021), Kaiwhaiki Road</t>
+  </si>
+  <si>
+    <t>96 Costley Street, Carterton</t>
+  </si>
+  <si>
+    <t>323 Bainesse Road</t>
+  </si>
+  <si>
+    <t>33 Ashford Avenue, Hokowhitu</t>
+  </si>
+  <si>
+    <t>7 Gill Lane, Rongotea</t>
+  </si>
+  <si>
+    <t>32 Armstrong Avenue, Carterton</t>
+  </si>
+  <si>
+    <t>49 Balfour Cresent</t>
+  </si>
+  <si>
+    <t>214A Dry River Road</t>
+  </si>
+  <si>
+    <t>58 Wall Road</t>
+  </si>
+  <si>
+    <t>397 Kairanga Bunnythorpe Road</t>
+  </si>
+  <si>
+    <t>1 Tarata Grove</t>
+  </si>
+  <si>
+    <t>117 Bridge Road</t>
+  </si>
+  <si>
+    <t>41 Almadale Road</t>
+  </si>
+  <si>
+    <t>24 Ameku Road, Raetihi</t>
+  </si>
+  <si>
+    <t>77 Watt Livingstone Road, Westmere</t>
+  </si>
+  <si>
+    <t>81 Western Line, Whanganui</t>
+  </si>
+  <si>
+    <t>1 196 Taupō Quay, Gonville</t>
+  </si>
+  <si>
+    <t>75a Marybank Road, Putiki</t>
+  </si>
+  <si>
+    <t>264 High Street South, Carterton</t>
+  </si>
+  <si>
+    <t>19 Woodland Grove, Feilding</t>
+  </si>
+  <si>
+    <t>264 Victoria Avenue, Whanganui</t>
+  </si>
+  <si>
+    <t>103 Warwick Street,</t>
   </si>
 </sst>
 </file>
@@ -2406,7 +2565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C328"/>
+  <dimension ref="A1:C355"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -2422,1360 +2581,1360 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B5" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C9" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C10" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C11" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C12" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C13" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B14" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C14" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C15" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C16" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C17" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>201</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C18" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>203</v>
+        <v>105</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B20" t="s">
-        <v>219</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C23" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>526</v>
       </c>
       <c r="C24" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B26" t="s">
-        <v>651</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="C29" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B31" t="s">
-        <v>218</v>
+        <v>128</v>
       </c>
       <c r="C31" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B33" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C33" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C35" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B36" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C36" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B37" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C37" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B38" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C38" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C39" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C40" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B43" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B44" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C45" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B46" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C46" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B47" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C47" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>165</v>
+        <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="C48" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C50" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B51" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C51" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>210</v>
-      </c>
-      <c r="C52" t="s">
-        <v>205</v>
+        <v>199</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>211</v>
+        <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>212</v>
+        <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>213</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>206</v>
+        <v>12</v>
+      </c>
+      <c r="C55" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="C56" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>203</v>
       </c>
       <c r="C57" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>216</v>
+        <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B60" t="s">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C64" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C65" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C66" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C67" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C68" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C69" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B70" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C71" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B72" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C72" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C73" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B74" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C74" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B75" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B76" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C76" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B77" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C77" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B78" t="s">
-        <v>51</v>
+        <v>200</v>
       </c>
       <c r="C78" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B79" t="s">
-        <v>53</v>
+        <v>201</v>
       </c>
       <c r="C79" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B80" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C80" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B82" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C82" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B83" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C83" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>214</v>
+        <v>66</v>
       </c>
       <c r="C84" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B85" t="s">
-        <v>215</v>
+        <v>68</v>
       </c>
       <c r="C85" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B86" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C86" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B87" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C87" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B88" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C88" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C89" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B90" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C90" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B91" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C92" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C93" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B94" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C94" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B95" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C95" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B96" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C96" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B97" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B98" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C98" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B99" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C100" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C101" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C102" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>98</v>
+        <v>220</v>
       </c>
       <c r="B103" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C103" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>100</v>
+        <v>219</v>
       </c>
       <c r="B104" t="s">
-        <v>101</v>
+        <v>218</v>
       </c>
       <c r="C104" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="B105" t="s">
-        <v>103</v>
+        <v>216</v>
       </c>
       <c r="C105" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>105</v>
+        <v>215</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>214</v>
       </c>
       <c r="C106" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>107</v>
+        <v>213</v>
       </c>
       <c r="B107" t="s">
-        <v>108</v>
+        <v>212</v>
       </c>
       <c r="C107" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>211</v>
       </c>
       <c r="B108" t="s">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="C108" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>111</v>
+        <v>209</v>
       </c>
       <c r="B109" t="s">
-        <v>112</v>
+        <v>208</v>
       </c>
       <c r="C109" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="B110" t="s">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="C110" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B111" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C111" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B112" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C112" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B113" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C113" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B114" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C114" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="C115" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B116" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="C116" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B117" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C117" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B118" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C118" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B119" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C119" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B120" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C120" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="B121" t="s">
-        <v>255</v>
+        <v>527</v>
       </c>
       <c r="C121" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B122" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C122" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B123" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C123" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B124" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C124" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
@@ -3783,87 +3942,87 @@
         <v>248</v>
       </c>
       <c r="B125" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C125" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B126" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C126" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B127" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C127" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B128" t="s">
-        <v>241</v>
+        <v>469</v>
       </c>
       <c r="C128" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B129" t="s">
-        <v>652</v>
+        <v>256</v>
       </c>
       <c r="C129" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
+        <v>257</v>
+      </c>
+      <c r="B130" t="s">
         <v>258</v>
       </c>
-      <c r="B130" t="s">
-        <v>259</v>
-      </c>
       <c r="C130" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
+        <v>259</v>
+      </c>
+      <c r="B131" t="s">
         <v>260</v>
       </c>
-      <c r="B131" t="s">
-        <v>261</v>
-      </c>
       <c r="C131" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
+        <v>261</v>
+      </c>
+      <c r="B132" t="s">
         <v>262</v>
       </c>
-      <c r="B132" t="s">
-        <v>391</v>
-      </c>
       <c r="C132" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
@@ -3874,7 +4033,7 @@
         <v>264</v>
       </c>
       <c r="C133" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
@@ -3885,7 +4044,7 @@
         <v>266</v>
       </c>
       <c r="C134" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
@@ -3896,7 +4055,7 @@
         <v>268</v>
       </c>
       <c r="C135" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
@@ -3907,7 +4066,7 @@
         <v>270</v>
       </c>
       <c r="C136" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
@@ -3918,7 +4077,7 @@
         <v>272</v>
       </c>
       <c r="C137" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
@@ -3926,296 +4085,296 @@
         <v>273</v>
       </c>
       <c r="B138" t="s">
-        <v>559</v>
+        <v>274</v>
       </c>
       <c r="C138" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B139" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C139" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B140" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C140" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B141" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C141" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B142" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C142" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B143" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C143" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B144" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C144" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B145" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C145" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B146" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C146" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B147" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C147" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B148" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C148" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B149" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C149" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B150" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C150" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B151" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C151" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B152" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C152" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B153" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C153" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B154" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C154" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B155" t="s">
-        <v>653</v>
+        <v>309</v>
       </c>
       <c r="C155" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B156" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C156" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B157" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C157" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B158" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C158" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B159" t="s">
-        <v>315</v>
+        <v>528</v>
       </c>
       <c r="C159" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B160" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C160" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B161" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C161" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B162" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C162" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B163" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C163" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B164" t="s">
-        <v>325</v>
+        <v>287</v>
       </c>
       <c r="C164" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
@@ -4226,7 +4385,7 @@
         <v>327</v>
       </c>
       <c r="C165" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
@@ -4237,7 +4396,7 @@
         <v>329</v>
       </c>
       <c r="C166" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
@@ -4248,1173 +4407,1173 @@
         <v>331</v>
       </c>
       <c r="C167" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="B168" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C168" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B169" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="C169" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B170" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C170" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B171" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C171" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B172" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C172" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B173" t="s">
-        <v>654</v>
+        <v>336</v>
       </c>
       <c r="C173" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B174" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C174" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B175" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="C175" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B176" t="s">
-        <v>656</v>
+        <v>349</v>
       </c>
       <c r="C176" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B177" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="C177" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B178" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C178" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B179" t="s">
-        <v>307</v>
+        <v>353</v>
       </c>
       <c r="C179" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B180" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C180" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B181" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C181" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B182" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C182" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B183" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C183" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B184" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C184" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B185" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C185" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B186" t="s">
-        <v>655</v>
+        <v>368</v>
       </c>
       <c r="C186" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B187" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C187" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="B188" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="C188" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="B189" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C189" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>383</v>
+        <v>523</v>
       </c>
       <c r="B190" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C190" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B191" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C191" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B192" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C192" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>377</v>
+        <v>524</v>
       </c>
       <c r="B193" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C193" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B194" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C194" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B195" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="C195" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="B196" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="C196" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="B197" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="C197" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B198" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C198" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B199" t="s">
-        <v>449</v>
+        <v>389</v>
       </c>
       <c r="C199" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B200" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C200" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="B201" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C201" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B202" t="s">
         <v>398</v>
       </c>
       <c r="C202" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B203" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C203" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B204" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C204" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B205" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C205" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B206" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C206" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B207" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C207" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B208" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C208" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B209" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C209" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B210" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C210" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B211" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C211" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B212" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C212" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B213" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C213" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>648</v>
+        <v>422</v>
       </c>
       <c r="B214" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C214" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B215" t="s">
         <v>425</v>
       </c>
       <c r="C215" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B216" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C216" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>649</v>
+        <v>427</v>
       </c>
       <c r="B217" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C217" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="B218" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C218" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B219" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C219" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B220" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C220" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="B221" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C221" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="B222" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C222" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B223" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C223" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B224" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C224" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B225" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C225" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B226" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C226" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="B227" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="C227" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="B228" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="C228" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B229" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C229" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B230" t="s">
-        <v>453</v>
+        <v>529</v>
       </c>
       <c r="C230" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B231" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C231" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B232" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C232" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B233" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C233" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B234" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C234" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B235" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C235" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B236" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C236" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B237" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C237" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B238" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C238" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B239" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C239" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B240" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C240" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B241" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C241" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B242" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C242" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B243" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C243" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B244" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C244" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B245" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C245" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B246" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C246" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B247" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C247" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
+        <v>490</v>
+      </c>
+      <c r="B248" t="s">
         <v>491</v>
       </c>
-      <c r="B248" t="s">
-        <v>490</v>
-      </c>
       <c r="C248" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B249" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C249" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="B250" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="C250" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B251" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C251" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B252" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C252" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B253" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C253" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B254" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C254" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B255" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C255" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B256" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C256" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B257" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C257" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="B258" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="C258" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="B259" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="C259" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="B260" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="C260" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="B261" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C261" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B262" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C262" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B263" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C263" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B264" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C264" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="B265" t="s">
-        <v>514</v>
+        <v>621</v>
       </c>
       <c r="C265" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="B266" t="s">
-        <v>512</v>
+        <v>622</v>
       </c>
       <c r="C266" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="B267" t="s">
-        <v>510</v>
+        <v>623</v>
       </c>
       <c r="C267" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="B268" t="s">
-        <v>508</v>
+        <v>624</v>
       </c>
       <c r="C268" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B269" t="s">
-        <v>531</v>
+        <v>625</v>
       </c>
       <c r="C269" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B270" t="s">
-        <v>533</v>
+        <v>626</v>
       </c>
       <c r="C270" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B271" t="s">
-        <v>535</v>
+        <v>627</v>
       </c>
       <c r="C271" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B272" t="s">
-        <v>657</v>
+        <v>628</v>
       </c>
       <c r="C272" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B273" t="s">
-        <v>538</v>
+        <v>629</v>
       </c>
       <c r="C273" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
@@ -5422,612 +5581,909 @@
         <v>539</v>
       </c>
       <c r="B274" t="s">
-        <v>540</v>
+        <v>630</v>
       </c>
       <c r="C274" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B275" t="s">
-        <v>542</v>
+        <v>631</v>
       </c>
       <c r="C275" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B276" t="s">
-        <v>544</v>
+        <v>632</v>
       </c>
       <c r="C276" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B277" t="s">
-        <v>546</v>
+        <v>633</v>
       </c>
       <c r="C277" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B278" t="s">
-        <v>548</v>
+        <v>634</v>
       </c>
       <c r="C278" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="B279" t="s">
-        <v>550</v>
+        <v>635</v>
       </c>
       <c r="C279" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B280" t="s">
-        <v>552</v>
+        <v>636</v>
       </c>
       <c r="C280" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="B281" t="s">
-        <v>554</v>
+        <v>637</v>
       </c>
       <c r="C281" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="B282" t="s">
-        <v>556</v>
+        <v>638</v>
       </c>
       <c r="C282" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="B283" t="s">
-        <v>558</v>
+        <v>639</v>
       </c>
       <c r="C283" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="B284" t="s">
-        <v>561</v>
+        <v>640</v>
       </c>
       <c r="C284" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="B285" t="s">
-        <v>388</v>
+        <v>641</v>
       </c>
       <c r="C285" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="B286" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
       <c r="C286" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="B287" t="s">
-        <v>566</v>
+        <v>643</v>
       </c>
       <c r="C287" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="B288" t="s">
-        <v>568</v>
+        <v>644</v>
       </c>
       <c r="C288" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="B289" t="s">
-        <v>570</v>
+        <v>645</v>
       </c>
       <c r="C289" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="B290" t="s">
-        <v>572</v>
+        <v>646</v>
       </c>
       <c r="C290" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>573</v>
+        <v>556</v>
       </c>
       <c r="B291" t="s">
-        <v>574</v>
+        <v>647</v>
       </c>
       <c r="C291" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="B292" t="s">
-        <v>576</v>
+        <v>648</v>
       </c>
       <c r="C292" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>577</v>
+        <v>558</v>
       </c>
       <c r="B293" t="s">
-        <v>578</v>
+        <v>649</v>
       </c>
       <c r="C293" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>579</v>
+        <v>559</v>
       </c>
       <c r="B294" t="s">
-        <v>580</v>
+        <v>650</v>
       </c>
       <c r="C294" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="B295" t="s">
-        <v>582</v>
+        <v>651</v>
       </c>
       <c r="C295" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="B296" t="s">
-        <v>584</v>
+        <v>652</v>
       </c>
       <c r="C296" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>585</v>
+        <v>562</v>
       </c>
       <c r="B297" t="s">
-        <v>586</v>
+        <v>653</v>
       </c>
       <c r="C297" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="B298" t="s">
-        <v>588</v>
+        <v>654</v>
       </c>
       <c r="C298" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>589</v>
+        <v>564</v>
       </c>
       <c r="B299" t="s">
-        <v>590</v>
+        <v>655</v>
       </c>
       <c r="C299" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="B300" t="s">
-        <v>592</v>
+        <v>708</v>
       </c>
       <c r="C300" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="B301" t="s">
-        <v>594</v>
+        <v>656</v>
       </c>
       <c r="C301" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>595</v>
+        <v>567</v>
       </c>
       <c r="B302" t="s">
-        <v>596</v>
+        <v>657</v>
       </c>
       <c r="C302" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>597</v>
+        <v>568</v>
       </c>
       <c r="B303" t="s">
-        <v>602</v>
+        <v>658</v>
       </c>
       <c r="C303" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>598</v>
+        <v>569</v>
       </c>
       <c r="B304" t="s">
-        <v>603</v>
+        <v>707</v>
       </c>
       <c r="C304" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>599</v>
+        <v>570</v>
       </c>
       <c r="B305" t="s">
-        <v>604</v>
+        <v>659</v>
       </c>
       <c r="C305" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>600</v>
+        <v>571</v>
       </c>
       <c r="B306" t="s">
-        <v>605</v>
+        <v>660</v>
       </c>
       <c r="C306" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>601</v>
+        <v>572</v>
       </c>
       <c r="B307" t="s">
-        <v>606</v>
+        <v>661</v>
       </c>
       <c r="C307" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>607</v>
+        <v>573</v>
       </c>
       <c r="B308" t="s">
-        <v>608</v>
+        <v>662</v>
       </c>
       <c r="C308" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>609</v>
+        <v>574</v>
       </c>
       <c r="B309" t="s">
-        <v>610</v>
+        <v>663</v>
       </c>
       <c r="C309" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>611</v>
+        <v>575</v>
       </c>
       <c r="B310" t="s">
-        <v>612</v>
+        <v>664</v>
       </c>
       <c r="C310" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>613</v>
+        <v>576</v>
       </c>
       <c r="B311" t="s">
-        <v>614</v>
+        <v>665</v>
       </c>
       <c r="C311" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>615</v>
+        <v>577</v>
       </c>
       <c r="B312" t="s">
-        <v>616</v>
+        <v>666</v>
       </c>
       <c r="C312" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>617</v>
+        <v>578</v>
       </c>
       <c r="B313" t="s">
-        <v>618</v>
+        <v>667</v>
       </c>
       <c r="C313" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>619</v>
+        <v>579</v>
       </c>
       <c r="B314" t="s">
-        <v>620</v>
+        <v>668</v>
       </c>
       <c r="C314" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>621</v>
+        <v>580</v>
       </c>
       <c r="B315" t="s">
-        <v>622</v>
+        <v>669</v>
       </c>
       <c r="C315" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>623</v>
+        <v>581</v>
       </c>
       <c r="B316" t="s">
-        <v>624</v>
+        <v>670</v>
       </c>
       <c r="C316" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>625</v>
+        <v>582</v>
       </c>
       <c r="B317" t="s">
-        <v>626</v>
+        <v>671</v>
       </c>
       <c r="C317" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>627</v>
+        <v>583</v>
       </c>
       <c r="B318" t="s">
-        <v>628</v>
+        <v>672</v>
       </c>
       <c r="C318" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>629</v>
+        <v>584</v>
       </c>
       <c r="B319" t="s">
-        <v>630</v>
+        <v>673</v>
       </c>
       <c r="C319" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>631</v>
+        <v>585</v>
       </c>
       <c r="B320" t="s">
-        <v>632</v>
+        <v>674</v>
       </c>
       <c r="C320" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>633</v>
+        <v>586</v>
       </c>
       <c r="B321" t="s">
-        <v>634</v>
+        <v>675</v>
       </c>
       <c r="C321" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>635</v>
+        <v>587</v>
       </c>
       <c r="B322" t="s">
-        <v>636</v>
+        <v>676</v>
       </c>
       <c r="C322" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>637</v>
+        <v>588</v>
       </c>
       <c r="B323" t="s">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="C323" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>639</v>
+        <v>589</v>
       </c>
       <c r="B324" t="s">
-        <v>640</v>
+        <v>678</v>
       </c>
       <c r="C324" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>641</v>
+        <v>590</v>
       </c>
       <c r="B325" t="s">
-        <v>642</v>
+        <v>679</v>
       </c>
       <c r="C325" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>643</v>
+        <v>591</v>
       </c>
       <c r="B326" t="s">
-        <v>644</v>
+        <v>680</v>
       </c>
       <c r="C326" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>645</v>
+        <v>592</v>
       </c>
       <c r="B327" t="s">
-        <v>646</v>
+        <v>681</v>
       </c>
       <c r="C327" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>647</v>
+        <v>593</v>
       </c>
       <c r="B328" t="s">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="C328" t="s">
-        <v>205</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>594</v>
+      </c>
+      <c r="B329" t="s">
+        <v>683</v>
+      </c>
+      <c r="C329" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>595</v>
+      </c>
+      <c r="B330" t="s">
+        <v>684</v>
+      </c>
+      <c r="C330" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>596</v>
+      </c>
+      <c r="B331" t="s">
+        <v>685</v>
+      </c>
+      <c r="C331" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>597</v>
+      </c>
+      <c r="B332" t="s">
+        <v>686</v>
+      </c>
+      <c r="C332" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>598</v>
+      </c>
+      <c r="B333" t="s">
+        <v>687</v>
+      </c>
+      <c r="C333" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>599</v>
+      </c>
+      <c r="B334" t="s">
+        <v>688</v>
+      </c>
+      <c r="C334" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>600</v>
+      </c>
+      <c r="B335" t="s">
+        <v>689</v>
+      </c>
+      <c r="C335" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>601</v>
+      </c>
+      <c r="B336" t="s">
+        <v>690</v>
+      </c>
+      <c r="C336" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>602</v>
+      </c>
+      <c r="B337" t="s">
+        <v>691</v>
+      </c>
+      <c r="C337" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>603</v>
+      </c>
+      <c r="B338" t="s">
+        <v>692</v>
+      </c>
+      <c r="C338" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>604</v>
+      </c>
+      <c r="B339" t="s">
+        <v>693</v>
+      </c>
+      <c r="C339" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>605</v>
+      </c>
+      <c r="B340" t="s">
+        <v>694</v>
+      </c>
+      <c r="C340" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>606</v>
+      </c>
+      <c r="B341" t="s">
+        <v>695</v>
+      </c>
+      <c r="C341" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>607</v>
+      </c>
+      <c r="B342" t="s">
+        <v>696</v>
+      </c>
+      <c r="C342" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>608</v>
+      </c>
+      <c r="B343" t="s">
+        <v>697</v>
+      </c>
+      <c r="C343" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>609</v>
+      </c>
+      <c r="B344" t="s">
+        <v>698</v>
+      </c>
+      <c r="C344" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>610</v>
+      </c>
+      <c r="B345" t="s">
+        <v>709</v>
+      </c>
+      <c r="C345" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>611</v>
+      </c>
+      <c r="B346" t="s">
+        <v>699</v>
+      </c>
+      <c r="C346" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>612</v>
+      </c>
+      <c r="B347" t="s">
+        <v>700</v>
+      </c>
+      <c r="C347" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>613</v>
+      </c>
+      <c r="B348" t="s">
+        <v>701</v>
+      </c>
+      <c r="C348" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>614</v>
+      </c>
+      <c r="B349" t="s">
+        <v>702</v>
+      </c>
+      <c r="C349" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>615</v>
+      </c>
+      <c r="B350" t="s">
+        <v>696</v>
+      </c>
+      <c r="C350" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>616</v>
+      </c>
+      <c r="B351" t="s">
+        <v>703</v>
+      </c>
+      <c r="C351" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>617</v>
+      </c>
+      <c r="B352" t="s">
+        <v>704</v>
+      </c>
+      <c r="C352" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>618</v>
+      </c>
+      <c r="B353" t="s">
+        <v>705</v>
+      </c>
+      <c r="C353" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>619</v>
+      </c>
+      <c r="B354" t="s">
+        <v>706</v>
+      </c>
+      <c r="C354" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>620</v>
+      </c>
+      <c r="B355" t="s">
+        <v>710</v>
+      </c>
+      <c r="C355" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576 B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="B1:B264 B356:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/isla_t_npe-tech_co_nz/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1D30172-EC19-4FB2-80DA-675884CC5F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{F1D30172-EC19-4FB2-80DA-675884CC5F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D800A3C9-CCDE-47BC-9D26-3C41398573E0}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="679">
   <si>
     <t>Job</t>
   </si>
@@ -413,12 +413,6 @@
     <t>290D Dakins Road, Carterton</t>
   </si>
   <si>
-    <t>1083715 - 00056130 - DG Label</t>
-  </si>
-  <si>
-    <t>12 Plimsoll Street, Carterton</t>
-  </si>
-  <si>
     <t>1083714 - 00046993 - DG Label</t>
   </si>
   <si>
@@ -485,12 +479,6 @@
     <t>18 Moore Crescent, Carterton</t>
   </si>
   <si>
-    <t>1083533 - 00046992 - DG Label</t>
-  </si>
-  <si>
-    <t>9 Third Street, Masterton</t>
-  </si>
-  <si>
     <t>1083531 - 00049940 - DG Label</t>
   </si>
   <si>
@@ -503,12 +491,6 @@
     <t>45A Murphys Line, Featherston</t>
   </si>
   <si>
-    <t>1083528 - 00046079 - DG Label</t>
-  </si>
-  <si>
-    <t>15 Kākāriki Crescent, Carterton</t>
-  </si>
-  <si>
     <t>1083527 - 00043587 - DG Label</t>
   </si>
   <si>
@@ -563,24 +545,12 @@
     <t>78 Lake Domain Road, Featherston</t>
   </si>
   <si>
-    <t>1083513 - 00025964 - DG Label</t>
-  </si>
-  <si>
-    <t>21 Feist Street, Carterton</t>
-  </si>
-  <si>
     <t>1083512 - 00041933 - DG Label</t>
   </si>
   <si>
     <t>117 Chester Road, Carterton</t>
   </si>
   <si>
-    <t>1083511 - 00025515 - DG Label</t>
-  </si>
-  <si>
-    <t>20 Carrington Drive, Carterton</t>
-  </si>
-  <si>
     <t>1083509 - 00031620 - DG Label</t>
   </si>
   <si>
@@ -803,12 +773,6 @@
     <t>63 Otawa Drive, Carterton</t>
   </si>
   <si>
-    <t>1085460 - 00026995 - DG Label</t>
-  </si>
-  <si>
-    <t>73 Young Street, Whanganui East</t>
-  </si>
-  <si>
     <t>1085458 - 00044870 - DG Label</t>
   </si>
   <si>
@@ -869,12 +833,6 @@
     <t>49 Wards Line, Greytown</t>
   </si>
   <si>
-    <t>1085554 - 00062941 - DG Label</t>
-  </si>
-  <si>
-    <t>4 Boydfield Street, Whanganui East</t>
-  </si>
-  <si>
     <t>1085551 - 00062161 - DG Label</t>
   </si>
   <si>
@@ -887,12 +845,6 @@
     <t>180A Manchester Street, Feilding</t>
   </si>
   <si>
-    <t>1085548 - 00061326 - DG Label</t>
-  </si>
-  <si>
-    <t>19 Mill Grove, Clareville</t>
-  </si>
-  <si>
     <t>1085628 - 00042760 - DG Label</t>
   </si>
   <si>
@@ -911,12 +863,6 @@
     <t>154 Watershed Road, Bunnythorpe</t>
   </si>
   <si>
-    <t>1085622 - 00055340 - DG Label</t>
-  </si>
-  <si>
-    <t>41 Tayforth Road, Whanganui</t>
-  </si>
-  <si>
     <t>1085621 - 00052867 - DG Label</t>
   </si>
   <si>
@@ -941,12 +887,6 @@
     <t>85 Watt Street, Featherston</t>
   </si>
   <si>
-    <t>1085733 - 00031648 - DG Label</t>
-  </si>
-  <si>
-    <t>9 Fox Road, Springvale</t>
-  </si>
-  <si>
     <t>1085731 - 00029753 - DG Label</t>
   </si>
   <si>
@@ -1007,12 +947,6 @@
     <t>32 Harrison Street West, Featherston</t>
   </si>
   <si>
-    <t>1085716 - 00055342 - DG Label</t>
-  </si>
-  <si>
-    <t>52 Surrey Road, Springvale</t>
-  </si>
-  <si>
     <t>1085714 - 00048298 - DG Label</t>
   </si>
   <si>
@@ -1115,12 +1049,6 @@
     <t>38C Grove Road, Ashhurst</t>
   </si>
   <si>
-    <t>1086149 - 00062569 - DG Label</t>
-  </si>
-  <si>
-    <t>633 Turakina Valley Road, Turakina</t>
-  </si>
-  <si>
     <t>1086200 - 00055582 - DG Label</t>
   </si>
   <si>
@@ -1151,24 +1079,12 @@
     <t>38 Marybank Road, Marybank</t>
   </si>
   <si>
-    <t>1086285 - 00067399 - DG Label</t>
-  </si>
-  <si>
-    <t>24 Feist Street, Carterton</t>
-  </si>
-  <si>
     <t>1086240 - 00052127 - DG Label</t>
   </si>
   <si>
     <t>14 Oates Place, Greytown</t>
   </si>
   <si>
-    <t>1086239 - 00052061 - DG Label</t>
-  </si>
-  <si>
-    <t>26 Feist Street, Carterton</t>
-  </si>
-  <si>
     <t>1086237 - 00052158 - DG Label</t>
   </si>
   <si>
@@ -1343,12 +1259,6 @@
     <t>271 Scotts Road, Linton</t>
   </si>
   <si>
-    <t>1086967 - 00057376 - DG Label</t>
-  </si>
-  <si>
-    <t>31 Koromiko Road, Gonville</t>
-  </si>
-  <si>
     <t>1087124 - 00060146 - DG Label</t>
   </si>
   <si>
@@ -1361,12 +1271,6 @@
     <t>132 Winchester Street, Ashhurst</t>
   </si>
   <si>
-    <t>1087118 - 00065860 - DG Label</t>
-  </si>
-  <si>
-    <t>27 Mahoney Street, Whanganui East</t>
-  </si>
-  <si>
     <t>1087115 - 00056539 - DG Label</t>
   </si>
   <si>
@@ -1439,12 +1343,6 @@
     <t>14 Fitzherbert East Road, Aokautere</t>
   </si>
   <si>
-    <t>1087301 - 00043534 - DG Label</t>
-  </si>
-  <si>
-    <t>42 Harrison Street, Whanganui</t>
-  </si>
-  <si>
     <t>1087365 - 00065152 - DG Label</t>
   </si>
   <si>
@@ -1589,12 +1487,6 @@
     <t>330 Aokautere Drive, Aokautere</t>
   </si>
   <si>
-    <t>1087784 - 00063340 - DG Label</t>
-  </si>
-  <si>
-    <t>3 Kākāriki Crescent, Carterton</t>
-  </si>
-  <si>
     <t>1087783 - 00064721 - DG Label</t>
   </si>
   <si>
@@ -1919,18 +1811,6 @@
     <t>2 Barlow Road, Martinborough</t>
   </si>
   <si>
-    <t>1088588 - 00026057 - DG Label</t>
-  </si>
-  <si>
-    <t>45B Seafield Road, Whanganui</t>
-  </si>
-  <si>
-    <t>1088584 - 00053238 - DG Label</t>
-  </si>
-  <si>
-    <t>11 Poutini Street, Whanganui</t>
-  </si>
-  <si>
     <t>1088583 - 00066503 - DG Label</t>
   </si>
   <si>
@@ -2045,18 +1925,6 @@
     <t>136 Southdown Drive</t>
   </si>
   <si>
-    <t>1088334 - 00065862 - DG Label</t>
-  </si>
-  <si>
-    <t>1427 Whanganui River Road</t>
-  </si>
-  <si>
-    <t>1088333 - 00066000 - DG Label</t>
-  </si>
-  <si>
-    <t>Takahuri Block (aka #1021), Kaiwhaiki Road</t>
-  </si>
-  <si>
     <t>1088332 - 00065610 - DG Label</t>
   </si>
   <si>
@@ -2111,12 +1979,6 @@
     <t>397 Kairanga Bunnythorpe Road</t>
   </si>
   <si>
-    <t>1088311 - 00063050 - DG Label</t>
-  </si>
-  <si>
-    <t>264 Victoria Avenue, Whanganui</t>
-  </si>
-  <si>
     <t>1088307 - 00036744 - DG Label</t>
   </si>
   <si>
@@ -2154,12 +2016,6 @@
   </si>
   <si>
     <t>81 Western Line, Whanganui</t>
-  </si>
-  <si>
-    <t>1088240 - 00048022 - DG Label</t>
-  </si>
-  <si>
-    <t>1 196 Taupō Quay, Gonville</t>
   </si>
   <si>
     <t>1088239 - 00050670 - DG Label</t>
@@ -2268,7 +2124,37 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2619,7 +2505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C363"/>
+  <dimension ref="A1:C339"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -3339,7 +3225,7 @@
         <v>131</v>
       </c>
       <c r="C65" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -3361,7 +3247,7 @@
         <v>135</v>
       </c>
       <c r="C67" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -3405,7 +3291,7 @@
         <v>143</v>
       </c>
       <c r="C71" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -3416,7 +3302,7 @@
         <v>145</v>
       </c>
       <c r="C72" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -3427,7 +3313,7 @@
         <v>147</v>
       </c>
       <c r="C73" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -3438,7 +3324,7 @@
         <v>149</v>
       </c>
       <c r="C74" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -3460,7 +3346,7 @@
         <v>153</v>
       </c>
       <c r="C76" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -3526,7 +3412,7 @@
         <v>165</v>
       </c>
       <c r="C82" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -3537,7 +3423,7 @@
         <v>167</v>
       </c>
       <c r="C83" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -3570,7 +3456,7 @@
         <v>173</v>
       </c>
       <c r="C86" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -3581,7 +3467,7 @@
         <v>175</v>
       </c>
       <c r="C87" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -3592,7 +3478,7 @@
         <v>177</v>
       </c>
       <c r="C88" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -3603,7 +3489,7 @@
         <v>179</v>
       </c>
       <c r="C89" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -3614,7 +3500,7 @@
         <v>181</v>
       </c>
       <c r="C90" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -3625,7 +3511,7 @@
         <v>183</v>
       </c>
       <c r="C91" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -3636,7 +3522,7 @@
         <v>185</v>
       </c>
       <c r="C92" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -3647,7 +3533,7 @@
         <v>187</v>
       </c>
       <c r="C93" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -3658,7 +3544,7 @@
         <v>189</v>
       </c>
       <c r="C94" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -3669,7 +3555,7 @@
         <v>191</v>
       </c>
       <c r="C95" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -3691,7 +3577,7 @@
         <v>195</v>
       </c>
       <c r="C97" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -3702,7 +3588,7 @@
         <v>197</v>
       </c>
       <c r="C98" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -3713,7 +3599,7 @@
         <v>199</v>
       </c>
       <c r="C99" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -3724,7 +3610,7 @@
         <v>201</v>
       </c>
       <c r="C100" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -3746,7 +3632,7 @@
         <v>205</v>
       </c>
       <c r="C102" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -3757,7 +3643,7 @@
         <v>207</v>
       </c>
       <c r="C103" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -3801,7 +3687,7 @@
         <v>215</v>
       </c>
       <c r="C107" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
@@ -3812,7 +3698,7 @@
         <v>217</v>
       </c>
       <c r="C108" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -3823,7 +3709,7 @@
         <v>219</v>
       </c>
       <c r="C109" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -3911,7 +3797,7 @@
         <v>235</v>
       </c>
       <c r="C117" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -3933,7 +3819,7 @@
         <v>239</v>
       </c>
       <c r="C119" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -3955,7 +3841,7 @@
         <v>243</v>
       </c>
       <c r="C121" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -3977,7 +3863,7 @@
         <v>247</v>
       </c>
       <c r="C123" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -3999,7 +3885,7 @@
         <v>251</v>
       </c>
       <c r="C125" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -4010,7 +3896,7 @@
         <v>253</v>
       </c>
       <c r="C126" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -4032,7 +3918,7 @@
         <v>257</v>
       </c>
       <c r="C128" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
@@ -4043,7 +3929,7 @@
         <v>259</v>
       </c>
       <c r="C129" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
@@ -4065,7 +3951,7 @@
         <v>263</v>
       </c>
       <c r="C131" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -4087,7 +3973,7 @@
         <v>267</v>
       </c>
       <c r="C133" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
@@ -4109,7 +3995,7 @@
         <v>271</v>
       </c>
       <c r="C135" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
@@ -4131,7 +4017,7 @@
         <v>275</v>
       </c>
       <c r="C137" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -4153,7 +4039,7 @@
         <v>279</v>
       </c>
       <c r="C139" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -4164,7 +4050,7 @@
         <v>281</v>
       </c>
       <c r="C140" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
@@ -4230,7 +4116,7 @@
         <v>293</v>
       </c>
       <c r="C146" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
@@ -4241,7 +4127,7 @@
         <v>295</v>
       </c>
       <c r="C147" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
@@ -4263,7 +4149,7 @@
         <v>299</v>
       </c>
       <c r="C149" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
@@ -4274,7 +4160,7 @@
         <v>301</v>
       </c>
       <c r="C150" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
@@ -4318,7 +4204,7 @@
         <v>309</v>
       </c>
       <c r="C154" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
@@ -4362,7 +4248,7 @@
         <v>317</v>
       </c>
       <c r="C158" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -4373,7 +4259,7 @@
         <v>319</v>
       </c>
       <c r="C159" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
@@ -4395,7 +4281,7 @@
         <v>323</v>
       </c>
       <c r="C161" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
@@ -4417,7 +4303,7 @@
         <v>327</v>
       </c>
       <c r="C163" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
@@ -4439,7 +4325,7 @@
         <v>331</v>
       </c>
       <c r="C165" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -4472,7 +4358,7 @@
         <v>337</v>
       </c>
       <c r="C168" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -4483,7 +4369,7 @@
         <v>339</v>
       </c>
       <c r="C169" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -4516,7 +4402,7 @@
         <v>345</v>
       </c>
       <c r="C172" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
@@ -4538,7 +4424,7 @@
         <v>349</v>
       </c>
       <c r="C174" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
@@ -4549,7 +4435,7 @@
         <v>351</v>
       </c>
       <c r="C175" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
@@ -4571,7 +4457,7 @@
         <v>355</v>
       </c>
       <c r="C177" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
@@ -4582,7 +4468,7 @@
         <v>357</v>
       </c>
       <c r="C178" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
@@ -4604,7 +4490,7 @@
         <v>361</v>
       </c>
       <c r="C180" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -4648,7 +4534,7 @@
         <v>369</v>
       </c>
       <c r="C184" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
@@ -4659,7 +4545,7 @@
         <v>371</v>
       </c>
       <c r="C185" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
@@ -4670,7 +4556,7 @@
         <v>373</v>
       </c>
       <c r="C186" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
@@ -4703,7 +4589,7 @@
         <v>379</v>
       </c>
       <c r="C189" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
@@ -4714,7 +4600,7 @@
         <v>381</v>
       </c>
       <c r="C190" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
@@ -4736,7 +4622,7 @@
         <v>385</v>
       </c>
       <c r="C192" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
@@ -4747,7 +4633,7 @@
         <v>387</v>
       </c>
       <c r="C193" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
@@ -4824,7 +4710,7 @@
         <v>401</v>
       </c>
       <c r="C200" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
@@ -4835,7 +4721,7 @@
         <v>403</v>
       </c>
       <c r="C201" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
@@ -4857,7 +4743,7 @@
         <v>407</v>
       </c>
       <c r="C203" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
@@ -4868,7 +4754,7 @@
         <v>409</v>
       </c>
       <c r="C204" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
@@ -4879,7 +4765,7 @@
         <v>411</v>
       </c>
       <c r="C205" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
@@ -4912,7 +4798,7 @@
         <v>417</v>
       </c>
       <c r="C208" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
@@ -4945,7 +4831,7 @@
         <v>423</v>
       </c>
       <c r="C211" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
@@ -4967,7 +4853,7 @@
         <v>427</v>
       </c>
       <c r="C213" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
@@ -4978,7 +4864,7 @@
         <v>429</v>
       </c>
       <c r="C214" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
@@ -4989,7 +4875,7 @@
         <v>431</v>
       </c>
       <c r="C215" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
@@ -5011,7 +4897,7 @@
         <v>435</v>
       </c>
       <c r="C217" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
@@ -5044,7 +4930,7 @@
         <v>441</v>
       </c>
       <c r="C220" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
@@ -5066,7 +4952,7 @@
         <v>445</v>
       </c>
       <c r="C222" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
@@ -5099,7 +4985,7 @@
         <v>451</v>
       </c>
       <c r="C225" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
@@ -5121,7 +5007,7 @@
         <v>455</v>
       </c>
       <c r="C227" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
@@ -5132,7 +5018,7 @@
         <v>457</v>
       </c>
       <c r="C228" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
@@ -5143,7 +5029,7 @@
         <v>459</v>
       </c>
       <c r="C229" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
@@ -5165,7 +5051,7 @@
         <v>463</v>
       </c>
       <c r="C231" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
@@ -5220,7 +5106,7 @@
         <v>473</v>
       </c>
       <c r="C236" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
@@ -5242,7 +5128,7 @@
         <v>477</v>
       </c>
       <c r="C238" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
@@ -5253,7 +5139,7 @@
         <v>479</v>
       </c>
       <c r="C239" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
@@ -5264,7 +5150,7 @@
         <v>481</v>
       </c>
       <c r="C240" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
@@ -5275,7 +5161,7 @@
         <v>483</v>
       </c>
       <c r="C241" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
@@ -5286,7 +5172,7 @@
         <v>485</v>
       </c>
       <c r="C242" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
@@ -5297,7 +5183,7 @@
         <v>487</v>
       </c>
       <c r="C243" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
@@ -5319,7 +5205,7 @@
         <v>491</v>
       </c>
       <c r="C245" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
@@ -5341,7 +5227,7 @@
         <v>495</v>
       </c>
       <c r="C247" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
@@ -5407,7 +5293,7 @@
         <v>507</v>
       </c>
       <c r="C253" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
@@ -5451,7 +5337,7 @@
         <v>515</v>
       </c>
       <c r="C257" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
@@ -5462,7 +5348,7 @@
         <v>517</v>
       </c>
       <c r="C258" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
@@ -5495,7 +5381,7 @@
         <v>523</v>
       </c>
       <c r="C261" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
@@ -5506,7 +5392,7 @@
         <v>525</v>
       </c>
       <c r="C262" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
@@ -5517,7 +5403,7 @@
         <v>527</v>
       </c>
       <c r="C263" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
@@ -5550,7 +5436,7 @@
         <v>533</v>
       </c>
       <c r="C266" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
@@ -5561,7 +5447,7 @@
         <v>535</v>
       </c>
       <c r="C267" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
@@ -5583,7 +5469,7 @@
         <v>539</v>
       </c>
       <c r="C269" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
@@ -5594,7 +5480,7 @@
         <v>541</v>
       </c>
       <c r="C270" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
@@ -5616,7 +5502,7 @@
         <v>545</v>
       </c>
       <c r="C272" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
@@ -5627,7 +5513,7 @@
         <v>547</v>
       </c>
       <c r="C273" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
@@ -5638,7 +5524,7 @@
         <v>549</v>
       </c>
       <c r="C274" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
@@ -5682,7 +5568,7 @@
         <v>557</v>
       </c>
       <c r="C278" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
@@ -5693,7 +5579,7 @@
         <v>559</v>
       </c>
       <c r="C279" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
@@ -5704,7 +5590,7 @@
         <v>561</v>
       </c>
       <c r="C280" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
@@ -5726,7 +5612,7 @@
         <v>565</v>
       </c>
       <c r="C282" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
@@ -5737,7 +5623,7 @@
         <v>567</v>
       </c>
       <c r="C283" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
@@ -5759,7 +5645,7 @@
         <v>571</v>
       </c>
       <c r="C285" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
@@ -5770,7 +5656,7 @@
         <v>573</v>
       </c>
       <c r="C286" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
@@ -5792,7 +5678,7 @@
         <v>577</v>
       </c>
       <c r="C288" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
@@ -5803,7 +5689,7 @@
         <v>579</v>
       </c>
       <c r="C289" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
@@ -5814,7 +5700,7 @@
         <v>581</v>
       </c>
       <c r="C290" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
@@ -5825,7 +5711,7 @@
         <v>583</v>
       </c>
       <c r="C291" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
@@ -5836,7 +5722,7 @@
         <v>585</v>
       </c>
       <c r="C292" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
@@ -5858,7 +5744,7 @@
         <v>589</v>
       </c>
       <c r="C294" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
@@ -5880,7 +5766,7 @@
         <v>593</v>
       </c>
       <c r="C296" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
@@ -5902,7 +5788,7 @@
         <v>597</v>
       </c>
       <c r="C298" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
@@ -5913,7 +5799,7 @@
         <v>599</v>
       </c>
       <c r="C299" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
@@ -5935,7 +5821,7 @@
         <v>603</v>
       </c>
       <c r="C301" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
@@ -5946,7 +5832,7 @@
         <v>605</v>
       </c>
       <c r="C302" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
@@ -5957,7 +5843,7 @@
         <v>607</v>
       </c>
       <c r="C303" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
@@ -5968,7 +5854,7 @@
         <v>609</v>
       </c>
       <c r="C304" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.3">
@@ -6001,7 +5887,7 @@
         <v>615</v>
       </c>
       <c r="C307" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
@@ -6012,7 +5898,7 @@
         <v>617</v>
       </c>
       <c r="C308" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
@@ -6034,7 +5920,7 @@
         <v>621</v>
       </c>
       <c r="C310" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
@@ -6056,7 +5942,7 @@
         <v>625</v>
       </c>
       <c r="C312" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
@@ -6067,7 +5953,7 @@
         <v>627</v>
       </c>
       <c r="C313" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
@@ -6078,7 +5964,7 @@
         <v>629</v>
       </c>
       <c r="C314" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
@@ -6188,7 +6074,7 @@
         <v>649</v>
       </c>
       <c r="C324" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
@@ -6210,7 +6096,7 @@
         <v>653</v>
       </c>
       <c r="C326" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
@@ -6218,7 +6104,7 @@
         <v>654</v>
       </c>
       <c r="B327" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="C327" t="s">
         <v>5</v>
@@ -6226,10 +6112,10 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
+        <v>655</v>
+      </c>
+      <c r="B328" t="s">
         <v>656</v>
-      </c>
-      <c r="B328" t="s">
-        <v>657</v>
       </c>
       <c r="C328" t="s">
         <v>5</v>
@@ -6237,21 +6123,21 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
+        <v>657</v>
+      </c>
+      <c r="B329" t="s">
         <v>658</v>
       </c>
-      <c r="B329" t="s">
-        <v>659</v>
-      </c>
       <c r="C329" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
+        <v>659</v>
+      </c>
+      <c r="B330" t="s">
         <v>660</v>
-      </c>
-      <c r="B330" t="s">
-        <v>661</v>
       </c>
       <c r="C330" t="s">
         <v>10</v>
@@ -6259,10 +6145,10 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
+        <v>661</v>
+      </c>
+      <c r="B331" t="s">
         <v>662</v>
-      </c>
-      <c r="B331" t="s">
-        <v>663</v>
       </c>
       <c r="C331" t="s">
         <v>10</v>
@@ -6270,10 +6156,10 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="B332" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C332" t="s">
         <v>5</v>
@@ -6281,21 +6167,21 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="B333" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C333" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="B334" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C334" t="s">
         <v>5</v>
@@ -6303,21 +6189,21 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B335" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C335" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B336" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="C336" t="s">
         <v>10</v>
@@ -6325,10 +6211,10 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B337" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="C337" t="s">
         <v>10</v>
@@ -6336,10 +6222,10 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B338" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="C338" t="s">
         <v>10</v>
@@ -6350,283 +6236,22 @@
         <v>678</v>
       </c>
       <c r="B339" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="C339" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A340" t="s">
-        <v>680</v>
-      </c>
-      <c r="B340" t="s">
-        <v>681</v>
-      </c>
-      <c r="C340" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A341" t="s">
-        <v>682</v>
-      </c>
-      <c r="B341" t="s">
-        <v>683</v>
-      </c>
-      <c r="C341" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A342" t="s">
-        <v>684</v>
-      </c>
-      <c r="B342" t="s">
-        <v>685</v>
-      </c>
-      <c r="C342" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A343" t="s">
-        <v>686</v>
-      </c>
-      <c r="B343" t="s">
-        <v>687</v>
-      </c>
-      <c r="C343" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A344" t="s">
-        <v>688</v>
-      </c>
-      <c r="B344" t="s">
-        <v>689</v>
-      </c>
-      <c r="C344" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A345" t="s">
-        <v>690</v>
-      </c>
-      <c r="B345" t="s">
-        <v>691</v>
-      </c>
-      <c r="C345" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A346" t="s">
-        <v>692</v>
-      </c>
-      <c r="B346" t="s">
-        <v>693</v>
-      </c>
-      <c r="C346" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A347" t="s">
-        <v>694</v>
-      </c>
-      <c r="B347" t="s">
-        <v>695</v>
-      </c>
-      <c r="C347" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A348" t="s">
-        <v>696</v>
-      </c>
-      <c r="B348" t="s">
-        <v>697</v>
-      </c>
-      <c r="C348" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A349" t="s">
-        <v>698</v>
-      </c>
-      <c r="B349" t="s">
-        <v>699</v>
-      </c>
-      <c r="C349" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A350" t="s">
-        <v>700</v>
-      </c>
-      <c r="B350" t="s">
-        <v>685</v>
-      </c>
-      <c r="C350" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A351" t="s">
-        <v>701</v>
-      </c>
-      <c r="B351" t="s">
-        <v>702</v>
-      </c>
-      <c r="C351" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A352" t="s">
-        <v>703</v>
-      </c>
-      <c r="B352" t="s">
-        <v>704</v>
-      </c>
-      <c r="C352" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A353" t="s">
-        <v>705</v>
-      </c>
-      <c r="B353" t="s">
-        <v>706</v>
-      </c>
-      <c r="C353" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A354" t="s">
-        <v>707</v>
-      </c>
-      <c r="B354" t="s">
-        <v>708</v>
-      </c>
-      <c r="C354" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A355" t="s">
-        <v>709</v>
-      </c>
-      <c r="B355" t="s">
-        <v>710</v>
-      </c>
-      <c r="C355" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A356" t="s">
-        <v>719</v>
-      </c>
-      <c r="B356" t="s">
-        <v>711</v>
-      </c>
-      <c r="C356" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A357" t="s">
-        <v>720</v>
-      </c>
-      <c r="B357" t="s">
-        <v>712</v>
-      </c>
-      <c r="C357" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A358" t="s">
-        <v>721</v>
-      </c>
-      <c r="B358" t="s">
-        <v>713</v>
-      </c>
-      <c r="C358" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A359" t="s">
-        <v>722</v>
-      </c>
-      <c r="B359" t="s">
-        <v>714</v>
-      </c>
-      <c r="C359" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A360" t="s">
-        <v>723</v>
-      </c>
-      <c r="B360" t="s">
-        <v>715</v>
-      </c>
-      <c r="C360" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A361" t="s">
-        <v>724</v>
-      </c>
-      <c r="B361" t="s">
-        <v>716</v>
-      </c>
-      <c r="C361" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A362" t="s">
-        <v>725</v>
-      </c>
-      <c r="B362" t="s">
-        <v>717</v>
-      </c>
-      <c r="C362" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A363" t="s">
-        <v>726</v>
-      </c>
-      <c r="B363" t="s">
-        <v>718</v>
-      </c>
-      <c r="C363" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B264 B364:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  <conditionalFormatting sqref="B340:B1048576 B1:B246">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576 A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/isla_t_npe-tech_co_nz/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{F1D30172-EC19-4FB2-80DA-675884CC5F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D800A3C9-CCDE-47BC-9D26-3C41398573E0}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{F1D30172-EC19-4FB2-80DA-675884CC5F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7D4488-644D-4E43-B133-50BED84AD2BC}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="653">
   <si>
     <t>Job</t>
   </si>
@@ -170,12 +170,6 @@
     <t>45 Abraham Crescent, Milson</t>
   </si>
   <si>
-    <t>1082684 - 00052888 - DG Label</t>
-  </si>
-  <si>
-    <t>479 Ngaio Road, Halcombe</t>
-  </si>
-  <si>
     <t>1082681 - 00025645 - DG Label</t>
   </si>
   <si>
@@ -194,12 +188,6 @@
     <t>18 Ataahua Place, Featherston, 5710</t>
   </si>
   <si>
-    <t>1082671 - 00016526 - DG Label</t>
-  </si>
-  <si>
-    <t>728 Taonui Road</t>
-  </si>
-  <si>
     <t>1082666 - 00029367 - DG Label</t>
   </si>
   <si>
@@ -653,12 +641,6 @@
     <t>29 Rexwood Street, Carterton</t>
   </si>
   <si>
-    <t>1084702 - 00052539 - DG Label</t>
-  </si>
-  <si>
-    <t>296 Cambridge Avenue, Ashhurst</t>
-  </si>
-  <si>
     <t>1084701 - 00054540 - DG Label</t>
   </si>
   <si>
@@ -1007,12 +989,6 @@
     <t>2 Crawford Street, Featherston</t>
   </si>
   <si>
-    <t>1086015 - 00056955 - DG Label</t>
-  </si>
-  <si>
-    <t>41 Cracroft Drive, Putiki</t>
-  </si>
-  <si>
     <t>1086014 - 00062883 - DG Label</t>
   </si>
   <si>
@@ -1073,12 +1049,6 @@
     <t>88 Oxford Street, Ashhurst</t>
   </si>
   <si>
-    <t>1086288 - 00059442 - DG Label</t>
-  </si>
-  <si>
-    <t>38 Marybank Road, Marybank</t>
-  </si>
-  <si>
     <t>1086240 - 00052127 - DG Label</t>
   </si>
   <si>
@@ -1139,24 +1109,6 @@
     <t>508 Ballance Valley Road, Ballance</t>
   </si>
   <si>
-    <t>1086485 - 00066284 - DG Label</t>
-  </si>
-  <si>
-    <t>291 Kahuterawa Road, Linton</t>
-  </si>
-  <si>
-    <t>1086484 - 00065455 - DG Label</t>
-  </si>
-  <si>
-    <t>297 Fitzherbert East Road, Aokautere</t>
-  </si>
-  <si>
-    <t>1086483 - 00063913 - DG Label</t>
-  </si>
-  <si>
-    <t>1065 Rongotea Road, Rongotea</t>
-  </si>
-  <si>
     <t>1086478 - 00060479 - DG Label</t>
   </si>
   <si>
@@ -1169,12 +1121,6 @@
     <t>33 Harvest Lane, Newbury</t>
   </si>
   <si>
-    <t>1078322 - DG Labelling request - 00038395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4a wellesley st </t>
-  </si>
-  <si>
     <t>1086655 - 00064086 - DG Label</t>
   </si>
   <si>
@@ -1235,12 +1181,6 @@
     <t>4 Whio Avenue, Feilding</t>
   </si>
   <si>
-    <t>1086616 - 00061593 - DG Label</t>
-  </si>
-  <si>
-    <t>66 Wikitoria Road, Putiki</t>
-  </si>
-  <si>
     <t>1086615 - 00053909 - DG Label</t>
   </si>
   <si>
@@ -1451,18 +1391,6 @@
     <t>11 Tūere Place, Hokowhitu</t>
   </si>
   <si>
-    <t>1087797 - 00060025 - DG Label</t>
-  </si>
-  <si>
-    <t>20 Dickens Lane, Otamatea</t>
-  </si>
-  <si>
-    <t>1087795 - 00014068 - DG Label</t>
-  </si>
-  <si>
-    <t>77 Wikitoria Road, Whanganui Airport</t>
-  </si>
-  <si>
     <t>1087793 - 00064585 - DG Label</t>
   </si>
   <si>
@@ -2016,12 +1944,6 @@
   </si>
   <si>
     <t>81 Western Line, Whanganui</t>
-  </si>
-  <si>
-    <t>1088239 - 00050670 - DG Label</t>
-  </si>
-  <si>
-    <t>75a Marybank Road, Putiki</t>
   </si>
   <si>
     <t>1088226 - 00067692 - DG Label</t>
@@ -2124,27 +2046,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2505,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C339"/>
+  <dimension ref="A1:C326"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -2763,7 +2665,7 @@
         <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -2774,7 +2676,7 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -2818,7 +2720,7 @@
         <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -2840,7 +2742,7 @@
         <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -2848,7 +2750,7 @@
         <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -2856,10 +2758,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" t="s">
         <v>65</v>
-      </c>
-      <c r="B32" t="s">
-        <v>66</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -2867,13 +2769,13 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" t="s">
         <v>67</v>
       </c>
-      <c r="B33" t="s">
-        <v>66</v>
-      </c>
       <c r="C33" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -2895,7 +2797,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -2928,7 +2830,7 @@
         <v>77</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -2972,7 +2874,7 @@
         <v>85</v>
       </c>
       <c r="C42" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -2983,7 +2885,7 @@
         <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -3005,7 +2907,7 @@
         <v>91</v>
       </c>
       <c r="C45" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -3016,7 +2918,7 @@
         <v>93</v>
       </c>
       <c r="C46" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -3027,7 +2929,7 @@
         <v>95</v>
       </c>
       <c r="C47" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -3038,7 +2940,7 @@
         <v>97</v>
       </c>
       <c r="C48" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -3059,8 +2961,8 @@
       <c r="B50" t="s">
         <v>101</v>
       </c>
-      <c r="C50" t="s">
-        <v>5</v>
+      <c r="C50" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -3081,8 +2983,8 @@
       <c r="B52" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>10</v>
+      <c r="C52" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -3093,7 +2995,7 @@
         <v>107</v>
       </c>
       <c r="C53" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -3104,7 +3006,7 @@
         <v>109</v>
       </c>
       <c r="C54" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -3126,7 +3028,7 @@
         <v>113</v>
       </c>
       <c r="C56" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -3148,7 +3050,7 @@
         <v>117</v>
       </c>
       <c r="C58" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -3159,7 +3061,7 @@
         <v>119</v>
       </c>
       <c r="C59" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -3203,7 +3105,7 @@
         <v>127</v>
       </c>
       <c r="C63" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -3214,7 +3116,7 @@
         <v>129</v>
       </c>
       <c r="C64" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -3225,7 +3127,7 @@
         <v>131</v>
       </c>
       <c r="C65" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -3236,7 +3138,7 @@
         <v>133</v>
       </c>
       <c r="C66" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -3269,7 +3171,7 @@
         <v>139</v>
       </c>
       <c r="C69" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -3324,7 +3226,7 @@
         <v>149</v>
       </c>
       <c r="C74" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -3335,7 +3237,7 @@
         <v>151</v>
       </c>
       <c r="C75" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -3357,7 +3259,7 @@
         <v>155</v>
       </c>
       <c r="C77" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -3368,7 +3270,7 @@
         <v>157</v>
       </c>
       <c r="C78" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -3412,7 +3314,7 @@
         <v>165</v>
       </c>
       <c r="C82" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -3423,7 +3325,7 @@
         <v>167</v>
       </c>
       <c r="C83" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -3434,7 +3336,7 @@
         <v>169</v>
       </c>
       <c r="C84" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -3445,7 +3347,7 @@
         <v>171</v>
       </c>
       <c r="C85" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -3478,7 +3380,7 @@
         <v>177</v>
       </c>
       <c r="C88" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -3500,7 +3402,7 @@
         <v>181</v>
       </c>
       <c r="C90" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -3533,7 +3435,7 @@
         <v>187</v>
       </c>
       <c r="C93" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -3544,7 +3446,7 @@
         <v>189</v>
       </c>
       <c r="C94" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -3555,7 +3457,7 @@
         <v>191</v>
       </c>
       <c r="C95" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -3566,7 +3468,7 @@
         <v>193</v>
       </c>
       <c r="C96" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -3588,7 +3490,7 @@
         <v>197</v>
       </c>
       <c r="C98" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -3632,7 +3534,7 @@
         <v>205</v>
       </c>
       <c r="C102" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -3665,7 +3567,7 @@
         <v>211</v>
       </c>
       <c r="C105" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -3676,7 +3578,7 @@
         <v>213</v>
       </c>
       <c r="C106" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -3698,7 +3600,7 @@
         <v>217</v>
       </c>
       <c r="C108" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -3709,7 +3611,7 @@
         <v>219</v>
       </c>
       <c r="C109" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -3720,7 +3622,7 @@
         <v>221</v>
       </c>
       <c r="C110" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -3731,7 +3633,7 @@
         <v>223</v>
       </c>
       <c r="C111" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -3753,7 +3655,7 @@
         <v>227</v>
       </c>
       <c r="C113" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -3775,7 +3677,7 @@
         <v>231</v>
       </c>
       <c r="C115" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -3797,7 +3699,7 @@
         <v>235</v>
       </c>
       <c r="C117" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -3819,7 +3721,7 @@
         <v>239</v>
       </c>
       <c r="C119" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -3841,7 +3743,7 @@
         <v>243</v>
       </c>
       <c r="C121" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -3885,7 +3787,7 @@
         <v>251</v>
       </c>
       <c r="C125" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -3896,7 +3798,7 @@
         <v>253</v>
       </c>
       <c r="C126" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -3929,7 +3831,7 @@
         <v>259</v>
       </c>
       <c r="C129" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
@@ -3940,7 +3842,7 @@
         <v>261</v>
       </c>
       <c r="C130" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -3973,7 +3875,7 @@
         <v>267</v>
       </c>
       <c r="C133" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
@@ -3984,7 +3886,7 @@
         <v>269</v>
       </c>
       <c r="C134" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -4006,7 +3908,7 @@
         <v>273</v>
       </c>
       <c r="C136" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -4017,7 +3919,7 @@
         <v>275</v>
       </c>
       <c r="C137" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -4028,7 +3930,7 @@
         <v>277</v>
       </c>
       <c r="C138" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -4039,7 +3941,7 @@
         <v>279</v>
       </c>
       <c r="C139" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -4061,7 +3963,7 @@
         <v>283</v>
       </c>
       <c r="C141" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -4094,7 +3996,7 @@
         <v>289</v>
       </c>
       <c r="C144" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -4105,7 +4007,7 @@
         <v>291</v>
       </c>
       <c r="C145" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
@@ -4116,7 +4018,7 @@
         <v>293</v>
       </c>
       <c r="C146" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
@@ -4127,7 +4029,7 @@
         <v>295</v>
       </c>
       <c r="C147" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
@@ -4149,7 +4051,7 @@
         <v>299</v>
       </c>
       <c r="C149" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
@@ -4237,7 +4139,7 @@
         <v>315</v>
       </c>
       <c r="C157" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
@@ -4248,7 +4150,7 @@
         <v>317</v>
       </c>
       <c r="C158" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -4259,7 +4161,7 @@
         <v>319</v>
       </c>
       <c r="C159" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
@@ -4281,7 +4183,7 @@
         <v>323</v>
       </c>
       <c r="C161" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
@@ -4292,7 +4194,7 @@
         <v>325</v>
       </c>
       <c r="C162" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
@@ -4303,7 +4205,7 @@
         <v>327</v>
       </c>
       <c r="C163" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
@@ -4325,7 +4227,7 @@
         <v>331</v>
       </c>
       <c r="C165" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -4358,7 +4260,7 @@
         <v>337</v>
       </c>
       <c r="C168" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -4369,7 +4271,7 @@
         <v>339</v>
       </c>
       <c r="C169" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -4380,7 +4282,7 @@
         <v>341</v>
       </c>
       <c r="C170" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -4402,7 +4304,7 @@
         <v>345</v>
       </c>
       <c r="C172" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
@@ -4446,7 +4348,7 @@
         <v>353</v>
       </c>
       <c r="C176" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
@@ -4457,7 +4359,7 @@
         <v>355</v>
       </c>
       <c r="C177" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
@@ -4468,7 +4370,7 @@
         <v>357</v>
       </c>
       <c r="C178" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
@@ -4479,7 +4381,7 @@
         <v>359</v>
       </c>
       <c r="C179" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
@@ -4490,7 +4392,7 @@
         <v>361</v>
       </c>
       <c r="C180" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -4512,7 +4414,7 @@
         <v>365</v>
       </c>
       <c r="C182" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
@@ -4545,7 +4447,7 @@
         <v>371</v>
       </c>
       <c r="C185" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
@@ -4556,7 +4458,7 @@
         <v>373</v>
       </c>
       <c r="C186" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
@@ -4567,7 +4469,7 @@
         <v>375</v>
       </c>
       <c r="C187" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
@@ -4589,7 +4491,7 @@
         <v>379</v>
       </c>
       <c r="C189" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
@@ -4611,7 +4513,7 @@
         <v>383</v>
       </c>
       <c r="C191" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
@@ -4644,7 +4546,7 @@
         <v>389</v>
       </c>
       <c r="C194" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
@@ -4655,7 +4557,7 @@
         <v>391</v>
       </c>
       <c r="C195" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
@@ -4677,7 +4579,7 @@
         <v>395</v>
       </c>
       <c r="C197" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
@@ -4688,7 +4590,7 @@
         <v>397</v>
       </c>
       <c r="C198" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
@@ -4699,7 +4601,7 @@
         <v>399</v>
       </c>
       <c r="C199" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
@@ -4710,7 +4612,7 @@
         <v>401</v>
       </c>
       <c r="C200" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
@@ -4721,7 +4623,7 @@
         <v>403</v>
       </c>
       <c r="C201" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
@@ -4732,7 +4634,7 @@
         <v>405</v>
       </c>
       <c r="C202" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
@@ -4765,7 +4667,7 @@
         <v>411</v>
       </c>
       <c r="C205" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
@@ -4798,7 +4700,7 @@
         <v>417</v>
       </c>
       <c r="C208" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
@@ -4809,7 +4711,7 @@
         <v>419</v>
       </c>
       <c r="C209" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
@@ -4820,7 +4722,7 @@
         <v>421</v>
       </c>
       <c r="C210" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
@@ -4831,7 +4733,7 @@
         <v>423</v>
       </c>
       <c r="C211" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
@@ -4875,7 +4777,7 @@
         <v>431</v>
       </c>
       <c r="C215" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
@@ -4897,7 +4799,7 @@
         <v>435</v>
       </c>
       <c r="C217" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
@@ -4908,7 +4810,7 @@
         <v>437</v>
       </c>
       <c r="C218" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
@@ -4930,7 +4832,7 @@
         <v>441</v>
       </c>
       <c r="C220" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
@@ -4952,7 +4854,7 @@
         <v>445</v>
       </c>
       <c r="C222" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
@@ -4974,7 +4876,7 @@
         <v>449</v>
       </c>
       <c r="C224" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
@@ -4985,7 +4887,7 @@
         <v>451</v>
       </c>
       <c r="C225" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
@@ -4996,7 +4898,7 @@
         <v>453</v>
       </c>
       <c r="C226" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
@@ -5029,7 +4931,7 @@
         <v>459</v>
       </c>
       <c r="C229" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
@@ -5040,7 +4942,7 @@
         <v>461</v>
       </c>
       <c r="C230" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
@@ -5051,7 +4953,7 @@
         <v>463</v>
       </c>
       <c r="C231" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
@@ -5084,7 +4986,7 @@
         <v>469</v>
       </c>
       <c r="C234" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
@@ -5106,7 +5008,7 @@
         <v>473</v>
       </c>
       <c r="C236" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
@@ -5117,7 +5019,7 @@
         <v>475</v>
       </c>
       <c r="C237" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
@@ -5139,7 +5041,7 @@
         <v>479</v>
       </c>
       <c r="C239" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
@@ -5150,7 +5052,7 @@
         <v>481</v>
       </c>
       <c r="C240" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
@@ -5161,7 +5063,7 @@
         <v>483</v>
       </c>
       <c r="C241" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
@@ -5238,7 +5140,7 @@
         <v>497</v>
       </c>
       <c r="C248" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
@@ -5271,7 +5173,7 @@
         <v>503</v>
       </c>
       <c r="C251" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
@@ -5282,7 +5184,7 @@
         <v>505</v>
       </c>
       <c r="C252" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
@@ -5293,7 +5195,7 @@
         <v>507</v>
       </c>
       <c r="C253" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
@@ -5326,7 +5228,7 @@
         <v>513</v>
       </c>
       <c r="C256" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
@@ -5337,7 +5239,7 @@
         <v>515</v>
       </c>
       <c r="C257" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
@@ -5359,7 +5261,7 @@
         <v>519</v>
       </c>
       <c r="C259" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
@@ -5370,7 +5272,7 @@
         <v>521</v>
       </c>
       <c r="C260" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
@@ -5403,7 +5305,7 @@
         <v>527</v>
       </c>
       <c r="C263" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
@@ -5436,7 +5338,7 @@
         <v>533</v>
       </c>
       <c r="C266" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
@@ -5458,7 +5360,7 @@
         <v>537</v>
       </c>
       <c r="C268" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
@@ -5480,7 +5382,7 @@
         <v>541</v>
       </c>
       <c r="C270" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
@@ -5502,7 +5404,7 @@
         <v>545</v>
       </c>
       <c r="C272" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
@@ -5524,7 +5426,7 @@
         <v>549</v>
       </c>
       <c r="C274" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
@@ -5535,7 +5437,7 @@
         <v>551</v>
       </c>
       <c r="C275" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
@@ -5546,7 +5448,7 @@
         <v>553</v>
       </c>
       <c r="C276" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
@@ -5568,7 +5470,7 @@
         <v>557</v>
       </c>
       <c r="C278" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
@@ -5601,7 +5503,7 @@
         <v>563</v>
       </c>
       <c r="C281" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
@@ -5623,7 +5525,7 @@
         <v>567</v>
       </c>
       <c r="C283" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
@@ -5645,7 +5547,7 @@
         <v>571</v>
       </c>
       <c r="C285" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
@@ -5656,7 +5558,7 @@
         <v>573</v>
       </c>
       <c r="C286" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
@@ -5667,7 +5569,7 @@
         <v>575</v>
       </c>
       <c r="C287" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
@@ -5700,7 +5602,7 @@
         <v>581</v>
       </c>
       <c r="C290" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
@@ -5722,7 +5624,7 @@
         <v>585</v>
       </c>
       <c r="C292" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
@@ -5733,7 +5635,7 @@
         <v>587</v>
       </c>
       <c r="C293" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
@@ -5755,7 +5657,7 @@
         <v>591</v>
       </c>
       <c r="C295" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
@@ -5766,7 +5668,7 @@
         <v>593</v>
       </c>
       <c r="C296" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
@@ -5810,7 +5712,7 @@
         <v>601</v>
       </c>
       <c r="C300" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
@@ -5821,7 +5723,7 @@
         <v>603</v>
       </c>
       <c r="C301" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
@@ -5832,7 +5734,7 @@
         <v>605</v>
       </c>
       <c r="C302" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
@@ -5865,7 +5767,7 @@
         <v>611</v>
       </c>
       <c r="C305" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
@@ -5887,7 +5789,7 @@
         <v>615</v>
       </c>
       <c r="C307" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
@@ -5898,7 +5800,7 @@
         <v>617</v>
       </c>
       <c r="C308" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
@@ -5920,7 +5822,7 @@
         <v>621</v>
       </c>
       <c r="C310" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
@@ -5964,7 +5866,7 @@
         <v>629</v>
       </c>
       <c r="C314" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
@@ -5972,40 +5874,40 @@
         <v>630</v>
       </c>
       <c r="B315" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="C315" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
+        <v>631</v>
+      </c>
+      <c r="B316" t="s">
         <v>632</v>
       </c>
-      <c r="B316" t="s">
-        <v>633</v>
-      </c>
       <c r="C316" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
+        <v>633</v>
+      </c>
+      <c r="B317" t="s">
         <v>634</v>
       </c>
-      <c r="B317" t="s">
-        <v>635</v>
-      </c>
       <c r="C317" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
+        <v>635</v>
+      </c>
+      <c r="B318" t="s">
         <v>636</v>
-      </c>
-      <c r="B318" t="s">
-        <v>637</v>
       </c>
       <c r="C318" t="s">
         <v>10</v>
@@ -6013,21 +5915,21 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="B319" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C319" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="B320" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C320" t="s">
         <v>10</v>
@@ -6035,32 +5937,32 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B321" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C321" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B322" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="C322" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B323" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C323" t="s">
         <v>10</v>
@@ -6068,24 +5970,24 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B324" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="C324" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B325" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="C325" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
@@ -6093,152 +5995,9 @@
         <v>652</v>
       </c>
       <c r="B326" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="C326" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A327" t="s">
-        <v>654</v>
-      </c>
-      <c r="B327" t="s">
-        <v>641</v>
-      </c>
-      <c r="C327" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A328" t="s">
-        <v>655</v>
-      </c>
-      <c r="B328" t="s">
-        <v>656</v>
-      </c>
-      <c r="C328" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A329" t="s">
-        <v>657</v>
-      </c>
-      <c r="B329" t="s">
-        <v>658</v>
-      </c>
-      <c r="C329" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A330" t="s">
-        <v>659</v>
-      </c>
-      <c r="B330" t="s">
-        <v>660</v>
-      </c>
-      <c r="C330" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A331" t="s">
-        <v>661</v>
-      </c>
-      <c r="B331" t="s">
-        <v>662</v>
-      </c>
-      <c r="C331" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A332" t="s">
-        <v>671</v>
-      </c>
-      <c r="B332" t="s">
-        <v>663</v>
-      </c>
-      <c r="C332" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A333" t="s">
-        <v>672</v>
-      </c>
-      <c r="B333" t="s">
-        <v>664</v>
-      </c>
-      <c r="C333" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A334" t="s">
-        <v>673</v>
-      </c>
-      <c r="B334" t="s">
-        <v>665</v>
-      </c>
-      <c r="C334" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A335" t="s">
-        <v>674</v>
-      </c>
-      <c r="B335" t="s">
-        <v>666</v>
-      </c>
-      <c r="C335" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A336" t="s">
-        <v>675</v>
-      </c>
-      <c r="B336" t="s">
-        <v>667</v>
-      </c>
-      <c r="C336" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A337" t="s">
-        <v>676</v>
-      </c>
-      <c r="B337" t="s">
-        <v>668</v>
-      </c>
-      <c r="C337" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A338" t="s">
-        <v>677</v>
-      </c>
-      <c r="B338" t="s">
-        <v>669</v>
-      </c>
-      <c r="C338" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A339" t="s">
-        <v>678</v>
-      </c>
-      <c r="B339" t="s">
-        <v>670</v>
-      </c>
-      <c r="C339" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6247,11 +6006,11 @@
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B340:B1048576 B1:B246">
+  <conditionalFormatting sqref="B327:B1048576 B1:B234">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576 A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/isla_t_npe-tech_co_nz/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{F1D30172-EC19-4FB2-80DA-675884CC5F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7D4488-644D-4E43-B133-50BED84AD2BC}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{F1D30172-EC19-4FB2-80DA-675884CC5F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D41C491A-828C-48F9-AB9F-4817404DCD4A}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="567">
   <si>
     <t>Job</t>
   </si>
@@ -116,12 +116,6 @@
     <t>70B DUBLIN STREET , MARTINBOROUGH, 5711</t>
   </si>
   <si>
-    <t>1082527 - 00052277 - DG Label - 0000065056CP68A</t>
-  </si>
-  <si>
-    <t>180B PHARAZYN ROAD, FEILDING, 4777</t>
-  </si>
-  <si>
     <t>1082526 - 00044306 - DG Label - 1000605858PCC99</t>
   </si>
   <si>
@@ -152,24 +146,12 @@
     <t>39 Craigmillar Street, Solway, Masterton</t>
   </si>
   <si>
-    <t>1082792 - 00051464 - DG Label</t>
-  </si>
-  <si>
-    <t>506 Longbush Road, Hinakura</t>
-  </si>
-  <si>
     <t>1082791 - 00042426 - DG Label</t>
   </si>
   <si>
     <t>56 FREDERICK ST, CARTERTON</t>
   </si>
   <si>
-    <t>1082687 - 00058152 - DG Label</t>
-  </si>
-  <si>
-    <t>45 Abraham Crescent, Milson</t>
-  </si>
-  <si>
     <t>1082681 - 00025645 - DG Label</t>
   </si>
   <si>
@@ -182,12 +164,6 @@
     <t>2562 Homewood Road, Masterton</t>
   </si>
   <si>
-    <t>1082679 - 00027851 - DG Label</t>
-  </si>
-  <si>
-    <t>18 Ataahua Place, Featherston, 5710</t>
-  </si>
-  <si>
     <t>1082666 - 00029367 - DG Label</t>
   </si>
   <si>
@@ -206,12 +182,6 @@
     <t>Junction Road, Halcombe</t>
   </si>
   <si>
-    <t>1082641 - 00032322 - DG Label</t>
-  </si>
-  <si>
-    <t>Nga Waka Winery, Martinborough</t>
-  </si>
-  <si>
     <t>1082309 - 00027982 - DG Label</t>
   </si>
   <si>
@@ -245,12 +215,6 @@
     <t>95 Mingaroa Road, Halcombe</t>
   </si>
   <si>
-    <t>1082157 - 00045590 - DG Label</t>
-  </si>
-  <si>
-    <t>83 Ngahere Park Road, Palmerston North</t>
-  </si>
-  <si>
     <t>1082153 - 00045468 - DG Label</t>
   </si>
   <si>
@@ -323,30 +287,6 @@
     <t>143 Watershed Road, Bunnythorpe</t>
   </si>
   <si>
-    <t>1084466 - 00057025 - DG Label</t>
-  </si>
-  <si>
-    <t>231 Valley Views, Palmerston North</t>
-  </si>
-  <si>
-    <t>1084464 - 00050442 - DG Label</t>
-  </si>
-  <si>
-    <t>99A Lees Pakaraka Road, Masterton</t>
-  </si>
-  <si>
-    <t>1084461 - 00050984 - DG Label</t>
-  </si>
-  <si>
-    <t>80 West Street, Greytown</t>
-  </si>
-  <si>
-    <t>1084171 - 00014163 - DG Label</t>
-  </si>
-  <si>
-    <t>89 Dublin Street, Martinborough</t>
-  </si>
-  <si>
     <t>1084156 - 00027186 - DG Label</t>
   </si>
   <si>
@@ -365,18 +305,6 @@
     <t>1727 State Highway 2</t>
   </si>
   <si>
-    <t>1084056 - 00054197 - DG Label</t>
-  </si>
-  <si>
-    <t>57 White Rock Road, Martinborough</t>
-  </si>
-  <si>
-    <t>1084055 - 00021842 - DG Label</t>
-  </si>
-  <si>
-    <t>16 Madden Place, Masterton</t>
-  </si>
-  <si>
     <t>1083912 - 00050108 - DG Label</t>
   </si>
   <si>
@@ -479,18 +407,6 @@
     <t>45A Murphys Line, Featherston</t>
   </si>
   <si>
-    <t>1083527 - 00043587 - DG Label</t>
-  </si>
-  <si>
-    <t>46A Main Street, Greytown</t>
-  </si>
-  <si>
-    <t>1083524 - 00043172 - DG Label</t>
-  </si>
-  <si>
-    <t>431C Te Kopi Road, Te Whiti</t>
-  </si>
-  <si>
     <t>1083521 - 00043163 - DG Label</t>
   </si>
   <si>
@@ -575,18 +491,6 @@
     <t>16 Parkers Road, Carterton</t>
   </si>
   <si>
-    <t>1083186 - 00051708 - DG Label</t>
-  </si>
-  <si>
-    <t>346 State Highway 1, Foxton</t>
-  </si>
-  <si>
-    <t>1083182 - 00055894 - DG Label</t>
-  </si>
-  <si>
-    <t>22 South Street, Feilding</t>
-  </si>
-  <si>
     <t>1083036 - 00050431 - DG Label</t>
   </si>
   <si>
@@ -719,12 +623,6 @@
     <t>1244A Rangitikei Line, Kauwhata</t>
   </si>
   <si>
-    <t>1085378 - 00050724 - DG Label</t>
-  </si>
-  <si>
-    <t>51 Southdown Drive, Martinborough, Hillside, Martinborough</t>
-  </si>
-  <si>
     <t>1085376 - 00064756 - DG Label</t>
   </si>
   <si>
@@ -755,12 +653,6 @@
     <t>63 Otawa Drive, Carterton</t>
   </si>
   <si>
-    <t>1085458 - 00044870 - DG Label</t>
-  </si>
-  <si>
-    <t>70 Duddings Line, Tauwharenīkau 5771</t>
-  </si>
-  <si>
     <t>1085533 - 00050342 - DG Label</t>
   </si>
   <si>
@@ -917,12 +809,6 @@
     <t>14 Spelman Court, Ashhurst</t>
   </si>
   <si>
-    <t>1085718 - 00025360 - DG Label</t>
-  </si>
-  <si>
-    <t>65 Hartwell Drive, Kelvin Grove, Palmerston North 4470</t>
-  </si>
-  <si>
     <t>1085717 - 00057960 - DG Label</t>
   </si>
   <si>
@@ -1091,12 +977,6 @@
     <t>260 High Street South, Carterton</t>
   </si>
   <si>
-    <t>1078481 - DG Labelling request - 00037578</t>
-  </si>
-  <si>
-    <t>574 Masterton Castlepoint Road, Masterton</t>
-  </si>
-  <si>
     <t>1086425 - 00067416 - DG Label</t>
   </si>
   <si>
@@ -1175,12 +1055,6 @@
     <t>1580 State Highway 3, Awahuri</t>
   </si>
   <si>
-    <t>1086631 - 00050566 - DG Label</t>
-  </si>
-  <si>
-    <t>4 Whio Avenue, Feilding</t>
-  </si>
-  <si>
     <t>1086615 - 00053909 - DG Label</t>
   </si>
   <si>
@@ -1223,12 +1097,6 @@
     <t>52 Cross Creek Road, Western Lake</t>
   </si>
   <si>
-    <t>1087147 - 00040396 - DG Label</t>
-  </si>
-  <si>
-    <t>208 John F Kennedy Drive, Milson</t>
-  </si>
-  <si>
     <t>1087141 - 00065202 - DG Label</t>
   </si>
   <si>
@@ -1265,12 +1133,6 @@
     <t>408 Albert Street, Hokowhitu</t>
   </si>
   <si>
-    <t>1087274 - 00055245 - DG Label</t>
-  </si>
-  <si>
-    <t>219A Hinakura Road, Martinborough 5784</t>
-  </si>
-  <si>
     <t>1087269 - 00052068 - DG Label</t>
   </si>
   <si>
@@ -1319,12 +1181,6 @@
     <t>52 Clyde Crescent, Roslyn</t>
   </si>
   <si>
-    <t>1087498 - 00064089 - DG Label</t>
-  </si>
-  <si>
-    <t>18 Pukeko Road, Bunnythorpe</t>
-  </si>
-  <si>
     <t>1087492 - 00059113 - DG Label</t>
   </si>
   <si>
@@ -1385,12 +1241,6 @@
     <t>286 Hewitts Road, Linton</t>
   </si>
   <si>
-    <t>1087619 - 00060420 - DG Label</t>
-  </si>
-  <si>
-    <t>11 Tūere Place, Hokowhitu</t>
-  </si>
-  <si>
     <t>1087793 - 00064585 - DG Label</t>
   </si>
   <si>
@@ -1415,24 +1265,12 @@
     <t>330 Aokautere Drive, Aokautere</t>
   </si>
   <si>
-    <t>1087783 - 00064721 - DG Label</t>
-  </si>
-  <si>
-    <t>22 Galea Grove, Kelvin Grove</t>
-  </si>
-  <si>
     <t>1087782 - 00062531 - DG Label</t>
   </si>
   <si>
     <t>291 Grey Street, Palmerston North</t>
   </si>
   <si>
-    <t>1087781 - 00064110 - DG Label</t>
-  </si>
-  <si>
-    <t>103 Freedom Drive, Kelvin Grove</t>
-  </si>
-  <si>
     <t>1087780 - 00065105 - DG Label</t>
   </si>
   <si>
@@ -1529,24 +1367,12 @@
     <t>138 Reid Line West, Feilding</t>
   </si>
   <si>
-    <t>1088874 - 00057954 - DG Label</t>
-  </si>
-  <si>
-    <t>57 Exeter Crescent, Whanganui</t>
-  </si>
-  <si>
     <t>1088820 - 00025077 - DG Label</t>
   </si>
   <si>
     <t>953C Kaiwhata Road, Carterton</t>
   </si>
   <si>
-    <t>1088819 - 00053582 - DG Label</t>
-  </si>
-  <si>
-    <t>30 Pickwick Road, Otamatea</t>
-  </si>
-  <si>
     <t>1088817 - 00064077 - DG Label</t>
   </si>
   <si>
@@ -1637,12 +1463,6 @@
     <t>38 Cracroft Drive, Putiki</t>
   </si>
   <si>
-    <t>1088768 - 00067149 - DG Label</t>
-  </si>
-  <si>
-    <t>15 Oaklea Avenue, Marton</t>
-  </si>
-  <si>
     <t>1088766 - 00065178 - DG Label</t>
   </si>
   <si>
@@ -1661,18 +1481,6 @@
     <t>774 Kimbolton Road</t>
   </si>
   <si>
-    <t>1088737 - 00067725 - DG Label</t>
-  </si>
-  <si>
-    <t>19 Woodland Grove, Feilding</t>
-  </si>
-  <si>
-    <t>1088734 - 00067456 - DG Label</t>
-  </si>
-  <si>
-    <t>344 Blueskin Road</t>
-  </si>
-  <si>
     <t>1088729 - 00068423 - DG Label</t>
   </si>
   <si>
@@ -1685,30 +1493,12 @@
     <t>90D Paierau Road</t>
   </si>
   <si>
-    <t>1088725 - 00070510 - DG Label</t>
-  </si>
-  <si>
-    <t>264 High Street South, Carterton</t>
-  </si>
-  <si>
-    <t>1088724 - 00064099 - DG Label</t>
-  </si>
-  <si>
-    <t>14 Carlisle Street, Milson</t>
-  </si>
-  <si>
     <t>1088723 - 00064106 - DG Label</t>
   </si>
   <si>
     <t>52 Featherston Street</t>
   </si>
   <si>
-    <t>1088721 - 00057186 - DG Label</t>
-  </si>
-  <si>
-    <t>240C Blueskin Road</t>
-  </si>
-  <si>
     <t>1088681 - 00071920 - DG Label</t>
   </si>
   <si>
@@ -1763,12 +1553,6 @@
     <t>1A Carrington Drive, Carterton</t>
   </si>
   <si>
-    <t>1088574 - 00068534 - DG Label </t>
-  </si>
-  <si>
-    <t>45 Pokerekere Crescent, Kelvin Grove</t>
-  </si>
-  <si>
     <t>1088571 - 00068782 - DG Label</t>
   </si>
   <si>
@@ -1829,12 +1613,6 @@
     <t>2 Garrity Lane</t>
   </si>
   <si>
-    <t>1088341 - 00056617 - DG Label</t>
-  </si>
-  <si>
-    <t>27 Hartwell Drive</t>
-  </si>
-  <si>
     <t>1088340 - 00062870 - DG Label</t>
   </si>
   <si>
@@ -1865,12 +1643,6 @@
     <t>323 Bainesse Road</t>
   </si>
   <si>
-    <t>1088322 - 00053961 - DG Label</t>
-  </si>
-  <si>
-    <t>33 Ashford Avenue, Hokowhitu</t>
-  </si>
-  <si>
     <t>1088321 - 00053962 - DG Label</t>
   </si>
   <si>
@@ -1946,18 +1718,9 @@
     <t>81 Western Line, Whanganui</t>
   </si>
   <si>
-    <t>1088226 - 00067692 - DG Label</t>
-  </si>
-  <si>
-    <t>103 Warwick Street,</t>
-  </si>
-  <si>
     <t>10 Eringa Road, Carterton</t>
   </si>
   <si>
-    <t>16 Miles Place, Awapuni</t>
-  </si>
-  <si>
     <t>278 State Highway 3, Marybank</t>
   </si>
   <si>
@@ -1967,21 +1730,9 @@
     <t>262 Campbell Road, Brunswick</t>
   </si>
   <si>
-    <t>44 Pokerekere Crescent, Kelvin Grove</t>
-  </si>
-  <si>
-    <t>1 Gibraltar Way, Fitzherbert</t>
-  </si>
-  <si>
-    <t>151 Valley Views, Fitzherbert</t>
-  </si>
-  <si>
     <t>1089058 - 00062808 - DG Label</t>
   </si>
   <si>
-    <t>1089057 - 00073170 - DG Label</t>
-  </si>
-  <si>
     <t>1089055 - 00072880 - DG Label</t>
   </si>
   <si>
@@ -1989,15 +1740,6 @@
   </si>
   <si>
     <t>1089052 - 00055446 - DG Label</t>
-  </si>
-  <si>
-    <t>1089032 - 00066953 - DG Label</t>
-  </si>
-  <si>
-    <t>1089030 - 00063564 - DG Label</t>
-  </si>
-  <si>
-    <t>1089027 - 00065910 - DG Label</t>
   </si>
 </sst>
 </file>
@@ -2039,14 +1781,163 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2407,7 +2298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C326"/>
+  <dimension ref="A1:C283"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -2544,7 +2435,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -2566,7 +2457,7 @@
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -2577,7 +2468,7 @@
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -2599,7 +2490,7 @@
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2632,7 +2523,7 @@
         <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -2695,7 +2586,7 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -2703,10 +2594,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
         <v>55</v>
-      </c>
-      <c r="B27" t="s">
-        <v>56</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -2714,10 +2605,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
         <v>57</v>
-      </c>
-      <c r="B28" t="s">
-        <v>58</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
@@ -2725,10 +2616,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" t="s">
         <v>59</v>
-      </c>
-      <c r="B29" t="s">
-        <v>60</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -2736,10 +2627,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
         <v>61</v>
-      </c>
-      <c r="B30" t="s">
-        <v>62</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -2747,10 +2638,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" t="s">
         <v>63</v>
-      </c>
-      <c r="B31" t="s">
-        <v>62</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -2764,7 +2655,7 @@
         <v>65</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -2775,7 +2666,7 @@
         <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -2786,7 +2677,7 @@
         <v>69</v>
       </c>
       <c r="C34" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -2819,7 +2710,7 @@
         <v>75</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -2830,7 +2721,7 @@
         <v>77</v>
       </c>
       <c r="C38" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -2863,7 +2754,7 @@
         <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -2885,7 +2776,7 @@
         <v>87</v>
       </c>
       <c r="C43" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -2940,7 +2831,7 @@
         <v>97</v>
       </c>
       <c r="C48" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -2961,7 +2852,7 @@
       <c r="B50" t="s">
         <v>101</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2973,7 +2864,7 @@
         <v>103</v>
       </c>
       <c r="C51" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -2995,7 +2886,7 @@
         <v>107</v>
       </c>
       <c r="C53" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -3017,7 +2908,7 @@
         <v>111</v>
       </c>
       <c r="C55" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -3028,7 +2919,7 @@
         <v>113</v>
       </c>
       <c r="C56" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -3061,7 +2952,7 @@
         <v>119</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -3094,7 +2985,7 @@
         <v>125</v>
       </c>
       <c r="C62" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -3116,7 +3007,7 @@
         <v>129</v>
       </c>
       <c r="C64" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -3127,7 +3018,7 @@
         <v>131</v>
       </c>
       <c r="C65" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -3149,7 +3040,7 @@
         <v>135</v>
       </c>
       <c r="C67" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -3160,7 +3051,7 @@
         <v>137</v>
       </c>
       <c r="C68" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -3171,7 +3062,7 @@
         <v>139</v>
       </c>
       <c r="C69" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -3237,7 +3128,7 @@
         <v>151</v>
       </c>
       <c r="C75" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -3248,7 +3139,7 @@
         <v>153</v>
       </c>
       <c r="C76" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -3259,7 +3150,7 @@
         <v>155</v>
       </c>
       <c r="C77" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -3270,7 +3161,7 @@
         <v>157</v>
       </c>
       <c r="C78" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -3325,7 +3216,7 @@
         <v>167</v>
       </c>
       <c r="C83" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -3336,7 +3227,7 @@
         <v>169</v>
       </c>
       <c r="C84" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -3358,7 +3249,7 @@
         <v>173</v>
       </c>
       <c r="C86" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -3391,7 +3282,7 @@
         <v>179</v>
       </c>
       <c r="C89" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -3424,7 +3315,7 @@
         <v>185</v>
       </c>
       <c r="C92" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -3435,7 +3326,7 @@
         <v>187</v>
       </c>
       <c r="C93" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -3446,7 +3337,7 @@
         <v>189</v>
       </c>
       <c r="C94" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -3457,7 +3348,7 @@
         <v>191</v>
       </c>
       <c r="C95" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -3468,7 +3359,7 @@
         <v>193</v>
       </c>
       <c r="C96" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -3479,7 +3370,7 @@
         <v>195</v>
       </c>
       <c r="C97" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -3490,7 +3381,7 @@
         <v>197</v>
       </c>
       <c r="C98" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -3523,7 +3414,7 @@
         <v>203</v>
       </c>
       <c r="C101" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -3556,7 +3447,7 @@
         <v>209</v>
       </c>
       <c r="C104" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -3567,7 +3458,7 @@
         <v>211</v>
       </c>
       <c r="C105" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
@@ -3578,7 +3469,7 @@
         <v>213</v>
       </c>
       <c r="C106" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -3600,7 +3491,7 @@
         <v>217</v>
       </c>
       <c r="C108" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
@@ -3622,7 +3513,7 @@
         <v>221</v>
       </c>
       <c r="C110" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -3633,7 +3524,7 @@
         <v>223</v>
       </c>
       <c r="C111" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -3644,7 +3535,7 @@
         <v>225</v>
       </c>
       <c r="C112" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -3666,7 +3557,7 @@
         <v>229</v>
       </c>
       <c r="C114" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -3677,7 +3568,7 @@
         <v>231</v>
       </c>
       <c r="C115" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -3688,7 +3579,7 @@
         <v>233</v>
       </c>
       <c r="C116" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -3721,7 +3612,7 @@
         <v>239</v>
       </c>
       <c r="C119" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -3732,7 +3623,7 @@
         <v>241</v>
       </c>
       <c r="C120" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -3754,7 +3645,7 @@
         <v>245</v>
       </c>
       <c r="C122" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
@@ -3809,7 +3700,7 @@
         <v>255</v>
       </c>
       <c r="C127" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -3831,7 +3722,7 @@
         <v>259</v>
       </c>
       <c r="C129" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
@@ -3842,7 +3733,7 @@
         <v>261</v>
       </c>
       <c r="C130" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -3864,7 +3755,7 @@
         <v>265</v>
       </c>
       <c r="C132" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -3886,7 +3777,7 @@
         <v>269</v>
       </c>
       <c r="C134" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -3897,7 +3788,7 @@
         <v>271</v>
       </c>
       <c r="C135" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
@@ -3908,7 +3799,7 @@
         <v>273</v>
       </c>
       <c r="C136" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -3930,7 +3821,7 @@
         <v>277</v>
       </c>
       <c r="C138" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -3941,7 +3832,7 @@
         <v>279</v>
       </c>
       <c r="C139" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -3952,7 +3843,7 @@
         <v>281</v>
       </c>
       <c r="C140" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
@@ -3996,7 +3887,7 @@
         <v>289</v>
       </c>
       <c r="C144" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -4007,7 +3898,7 @@
         <v>291</v>
       </c>
       <c r="C145" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
@@ -4040,7 +3931,7 @@
         <v>297</v>
       </c>
       <c r="C148" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
@@ -4051,7 +3942,7 @@
         <v>299</v>
       </c>
       <c r="C149" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
@@ -4095,7 +3986,7 @@
         <v>307</v>
       </c>
       <c r="C153" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
@@ -4128,7 +4019,7 @@
         <v>313</v>
       </c>
       <c r="C156" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
@@ -4150,7 +4041,7 @@
         <v>317</v>
       </c>
       <c r="C158" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -4183,7 +4074,7 @@
         <v>323</v>
       </c>
       <c r="C161" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
@@ -4194,7 +4085,7 @@
         <v>325</v>
       </c>
       <c r="C162" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
@@ -4216,7 +4107,7 @@
         <v>329</v>
       </c>
       <c r="C164" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
@@ -4238,7 +4129,7 @@
         <v>333</v>
       </c>
       <c r="C166" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
@@ -4260,7 +4151,7 @@
         <v>337</v>
       </c>
       <c r="C168" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -4271,7 +4162,7 @@
         <v>339</v>
       </c>
       <c r="C169" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -4282,7 +4173,7 @@
         <v>341</v>
       </c>
       <c r="C170" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -4315,7 +4206,7 @@
         <v>347</v>
       </c>
       <c r="C173" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
@@ -4337,7 +4228,7 @@
         <v>351</v>
       </c>
       <c r="C175" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
@@ -4348,7 +4239,7 @@
         <v>353</v>
       </c>
       <c r="C176" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
@@ -4359,7 +4250,7 @@
         <v>355</v>
       </c>
       <c r="C177" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
@@ -4392,7 +4283,7 @@
         <v>361</v>
       </c>
       <c r="C180" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -4458,7 +4349,7 @@
         <v>373</v>
       </c>
       <c r="C186" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
@@ -4469,7 +4360,7 @@
         <v>375</v>
       </c>
       <c r="C187" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
@@ -4502,7 +4393,7 @@
         <v>381</v>
       </c>
       <c r="C190" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
@@ -4535,7 +4426,7 @@
         <v>387</v>
       </c>
       <c r="C193" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
@@ -4579,7 +4470,7 @@
         <v>395</v>
       </c>
       <c r="C197" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
@@ -4612,7 +4503,7 @@
         <v>401</v>
       </c>
       <c r="C200" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
@@ -4634,7 +4525,7 @@
         <v>405</v>
       </c>
       <c r="C202" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
@@ -4645,7 +4536,7 @@
         <v>407</v>
       </c>
       <c r="C203" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
@@ -4656,7 +4547,7 @@
         <v>409</v>
       </c>
       <c r="C204" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
@@ -4667,7 +4558,7 @@
         <v>411</v>
       </c>
       <c r="C205" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
@@ -4678,7 +4569,7 @@
         <v>413</v>
       </c>
       <c r="C206" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
@@ -4689,7 +4580,7 @@
         <v>415</v>
       </c>
       <c r="C207" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
@@ -4722,7 +4613,7 @@
         <v>421</v>
       </c>
       <c r="C210" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
@@ -4733,7 +4624,7 @@
         <v>423</v>
       </c>
       <c r="C211" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
@@ -4777,7 +4668,7 @@
         <v>431</v>
       </c>
       <c r="C215" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
@@ -4788,7 +4679,7 @@
         <v>433</v>
       </c>
       <c r="C216" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
@@ -4810,7 +4701,7 @@
         <v>437</v>
       </c>
       <c r="C218" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
@@ -4832,7 +4723,7 @@
         <v>441</v>
       </c>
       <c r="C220" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
@@ -4865,7 +4756,7 @@
         <v>447</v>
       </c>
       <c r="C223" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
@@ -4909,7 +4800,7 @@
         <v>455</v>
       </c>
       <c r="C227" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
@@ -4931,7 +4822,7 @@
         <v>459</v>
       </c>
       <c r="C229" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
@@ -4942,7 +4833,7 @@
         <v>461</v>
       </c>
       <c r="C230" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
@@ -4953,7 +4844,7 @@
         <v>463</v>
       </c>
       <c r="C231" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
@@ -4986,7 +4877,7 @@
         <v>469</v>
       </c>
       <c r="C234" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
@@ -4997,7 +4888,7 @@
         <v>471</v>
       </c>
       <c r="C235" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
@@ -5008,7 +4899,7 @@
         <v>473</v>
       </c>
       <c r="C236" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
@@ -5019,7 +4910,7 @@
         <v>475</v>
       </c>
       <c r="C237" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
@@ -5030,7 +4921,7 @@
         <v>477</v>
       </c>
       <c r="C238" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
@@ -5041,7 +4932,7 @@
         <v>479</v>
       </c>
       <c r="C239" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
@@ -5096,7 +4987,7 @@
         <v>489</v>
       </c>
       <c r="C244" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
@@ -5107,7 +4998,7 @@
         <v>491</v>
       </c>
       <c r="C245" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
@@ -5118,7 +5009,7 @@
         <v>493</v>
       </c>
       <c r="C246" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
@@ -5151,7 +5042,7 @@
         <v>499</v>
       </c>
       <c r="C249" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
@@ -5173,7 +5064,7 @@
         <v>503</v>
       </c>
       <c r="C251" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
@@ -5184,7 +5075,7 @@
         <v>505</v>
       </c>
       <c r="C252" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
@@ -5206,7 +5097,7 @@
         <v>509</v>
       </c>
       <c r="C254" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
@@ -5250,7 +5141,7 @@
         <v>517</v>
       </c>
       <c r="C258" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
@@ -5283,7 +5174,7 @@
         <v>523</v>
       </c>
       <c r="C261" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
@@ -5305,7 +5196,7 @@
         <v>527</v>
       </c>
       <c r="C263" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
@@ -5338,7 +5229,7 @@
         <v>533</v>
       </c>
       <c r="C266" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
@@ -5360,7 +5251,7 @@
         <v>537</v>
       </c>
       <c r="C268" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
@@ -5371,7 +5262,7 @@
         <v>539</v>
       </c>
       <c r="C269" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
@@ -5393,7 +5284,7 @@
         <v>543</v>
       </c>
       <c r="C271" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
@@ -5404,7 +5295,7 @@
         <v>545</v>
       </c>
       <c r="C272" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
@@ -5415,7 +5306,7 @@
         <v>547</v>
       </c>
       <c r="C273" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
@@ -5448,7 +5339,7 @@
         <v>553</v>
       </c>
       <c r="C276" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
@@ -5456,40 +5347,40 @@
         <v>554</v>
       </c>
       <c r="B277" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="C277" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
+        <v>555</v>
+      </c>
+      <c r="B278" t="s">
         <v>556</v>
       </c>
-      <c r="B278" t="s">
-        <v>557</v>
-      </c>
       <c r="C278" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
+        <v>557</v>
+      </c>
+      <c r="B279" t="s">
         <v>558</v>
       </c>
-      <c r="B279" t="s">
-        <v>559</v>
-      </c>
       <c r="C279" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B280" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C280" t="s">
         <v>5</v>
@@ -5497,21 +5388,21 @@
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B281" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C281" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B282" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C282" t="s">
         <v>10</v>
@@ -5522,495 +5413,29 @@
         <v>566</v>
       </c>
       <c r="B283" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C283" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A284" t="s">
-        <v>568</v>
-      </c>
-      <c r="B284" t="s">
-        <v>569</v>
-      </c>
-      <c r="C284" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A285" t="s">
-        <v>570</v>
-      </c>
-      <c r="B285" t="s">
-        <v>571</v>
-      </c>
-      <c r="C285" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A286" t="s">
-        <v>572</v>
-      </c>
-      <c r="B286" t="s">
-        <v>573</v>
-      </c>
-      <c r="C286" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A287" t="s">
-        <v>574</v>
-      </c>
-      <c r="B287" t="s">
-        <v>575</v>
-      </c>
-      <c r="C287" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A288" t="s">
-        <v>576</v>
-      </c>
-      <c r="B288" t="s">
-        <v>577</v>
-      </c>
-      <c r="C288" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A289" t="s">
-        <v>578</v>
-      </c>
-      <c r="B289" t="s">
-        <v>579</v>
-      </c>
-      <c r="C289" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A290" t="s">
-        <v>580</v>
-      </c>
-      <c r="B290" t="s">
-        <v>581</v>
-      </c>
-      <c r="C290" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A291" t="s">
-        <v>582</v>
-      </c>
-      <c r="B291" t="s">
-        <v>583</v>
-      </c>
-      <c r="C291" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
-        <v>584</v>
-      </c>
-      <c r="B292" t="s">
-        <v>585</v>
-      </c>
-      <c r="C292" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A293" t="s">
-        <v>586</v>
-      </c>
-      <c r="B293" t="s">
-        <v>587</v>
-      </c>
-      <c r="C293" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A294" t="s">
-        <v>588</v>
-      </c>
-      <c r="B294" t="s">
-        <v>589</v>
-      </c>
-      <c r="C294" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A295" t="s">
-        <v>590</v>
-      </c>
-      <c r="B295" t="s">
-        <v>591</v>
-      </c>
-      <c r="C295" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A296" t="s">
-        <v>592</v>
-      </c>
-      <c r="B296" t="s">
-        <v>593</v>
-      </c>
-      <c r="C296" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A297" t="s">
-        <v>594</v>
-      </c>
-      <c r="B297" t="s">
-        <v>595</v>
-      </c>
-      <c r="C297" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A298" t="s">
-        <v>596</v>
-      </c>
-      <c r="B298" t="s">
-        <v>597</v>
-      </c>
-      <c r="C298" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A299" t="s">
-        <v>598</v>
-      </c>
-      <c r="B299" t="s">
-        <v>599</v>
-      </c>
-      <c r="C299" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A300" t="s">
-        <v>600</v>
-      </c>
-      <c r="B300" t="s">
-        <v>601</v>
-      </c>
-      <c r="C300" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A301" t="s">
-        <v>602</v>
-      </c>
-      <c r="B301" t="s">
-        <v>603</v>
-      </c>
-      <c r="C301" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A302" t="s">
-        <v>604</v>
-      </c>
-      <c r="B302" t="s">
-        <v>605</v>
-      </c>
-      <c r="C302" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A303" t="s">
-        <v>606</v>
-      </c>
-      <c r="B303" t="s">
-        <v>607</v>
-      </c>
-      <c r="C303" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
-        <v>608</v>
-      </c>
-      <c r="B304" t="s">
-        <v>609</v>
-      </c>
-      <c r="C304" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A305" t="s">
-        <v>610</v>
-      </c>
-      <c r="B305" t="s">
-        <v>611</v>
-      </c>
-      <c r="C305" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A306" t="s">
-        <v>612</v>
-      </c>
-      <c r="B306" t="s">
-        <v>613</v>
-      </c>
-      <c r="C306" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A307" t="s">
-        <v>614</v>
-      </c>
-      <c r="B307" t="s">
-        <v>615</v>
-      </c>
-      <c r="C307" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A308" t="s">
-        <v>616</v>
-      </c>
-      <c r="B308" t="s">
-        <v>617</v>
-      </c>
-      <c r="C308" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A309" t="s">
-        <v>618</v>
-      </c>
-      <c r="B309" t="s">
-        <v>619</v>
-      </c>
-      <c r="C309" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A310" t="s">
-        <v>620</v>
-      </c>
-      <c r="B310" t="s">
-        <v>621</v>
-      </c>
-      <c r="C310" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A311" t="s">
-        <v>622</v>
-      </c>
-      <c r="B311" t="s">
-        <v>623</v>
-      </c>
-      <c r="C311" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A312" t="s">
-        <v>624</v>
-      </c>
-      <c r="B312" t="s">
-        <v>625</v>
-      </c>
-      <c r="C312" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A313" t="s">
-        <v>626</v>
-      </c>
-      <c r="B313" t="s">
-        <v>627</v>
-      </c>
-      <c r="C313" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A314" t="s">
-        <v>628</v>
-      </c>
-      <c r="B314" t="s">
-        <v>629</v>
-      </c>
-      <c r="C314" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A315" t="s">
-        <v>630</v>
-      </c>
-      <c r="B315" t="s">
-        <v>617</v>
-      </c>
-      <c r="C315" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A316" t="s">
-        <v>631</v>
-      </c>
-      <c r="B316" t="s">
-        <v>632</v>
-      </c>
-      <c r="C316" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A317" t="s">
-        <v>633</v>
-      </c>
-      <c r="B317" t="s">
-        <v>634</v>
-      </c>
-      <c r="C317" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A318" t="s">
-        <v>635</v>
-      </c>
-      <c r="B318" t="s">
-        <v>636</v>
-      </c>
-      <c r="C318" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A319" t="s">
-        <v>645</v>
-      </c>
-      <c r="B319" t="s">
-        <v>637</v>
-      </c>
-      <c r="C319" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A320" t="s">
-        <v>646</v>
-      </c>
-      <c r="B320" t="s">
-        <v>638</v>
-      </c>
-      <c r="C320" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A321" t="s">
-        <v>647</v>
-      </c>
-      <c r="B321" t="s">
-        <v>639</v>
-      </c>
-      <c r="C321" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A322" t="s">
-        <v>648</v>
-      </c>
-      <c r="B322" t="s">
-        <v>640</v>
-      </c>
-      <c r="C322" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A323" t="s">
-        <v>649</v>
-      </c>
-      <c r="B323" t="s">
-        <v>641</v>
-      </c>
-      <c r="C323" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A324" t="s">
-        <v>650</v>
-      </c>
-      <c r="B324" t="s">
-        <v>642</v>
-      </c>
-      <c r="C324" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A325" t="s">
-        <v>651</v>
-      </c>
-      <c r="B325" t="s">
-        <v>643</v>
-      </c>
-      <c r="C325" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A326" t="s">
-        <v>652</v>
-      </c>
-      <c r="B326" t="s">
-        <v>644</v>
-      </c>
-      <c r="C326" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B327:B1048576 B1:B234">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  <conditionalFormatting sqref="B284:B1048576 B1:B207">
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M16">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/isla_t_npe-tech_co_nz/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{F1D30172-EC19-4FB2-80DA-675884CC5F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D41C491A-828C-48F9-AB9F-4817404DCD4A}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="8_{F1D30172-EC19-4FB2-80DA-675884CC5F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66A9526D-723E-4471-AC52-4106EC91FC7B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="655">
   <si>
     <t>Job</t>
   </si>
@@ -200,9 +200,6 @@
     <t>23 Fry Road, Halcombe</t>
   </si>
   <si>
-    <t>1082300 - 00046363 - DG Label</t>
-  </si>
-  <si>
     <t>1082166 - 00052136 - DG Label</t>
   </si>
   <si>
@@ -863,9 +860,6 @@
     <t>2623 Pohangina Road, Pohangina</t>
   </si>
   <si>
-    <t>1086017 - 00064085 - DG Label</t>
-  </si>
-  <si>
     <t>41 Watt Street, Featherston</t>
   </si>
   <si>
@@ -1703,9 +1697,6 @@
     <t>24 Ameku Road, Raetihi</t>
   </si>
   <si>
-    <t>1088302 - 00071638 - DG Label</t>
-  </si>
-  <si>
     <t>1088252 - 00024700 - DG Label</t>
   </si>
   <si>
@@ -1740,6 +1731,279 @@
   </si>
   <si>
     <t>1089052 - 00055446 - DG Label</t>
+  </si>
+  <si>
+    <t>1089540 - 00064926 - DG Label</t>
+  </si>
+  <si>
+    <t>239 Queen Street, Masterton</t>
+  </si>
+  <si>
+    <t>1089539 - 00040744 - DG Label</t>
+  </si>
+  <si>
+    <t>211A Trickers Road, Bulls</t>
+  </si>
+  <si>
+    <t>1089538 - 00065866 - DG Label</t>
+  </si>
+  <si>
+    <t>84B Peakes Road, Springvale</t>
+  </si>
+  <si>
+    <t>1089535 - 00075757 - DG Label</t>
+  </si>
+  <si>
+    <t>1089532 - 00065312 - DG Label</t>
+  </si>
+  <si>
+    <t>269 Hoihere Road</t>
+  </si>
+  <si>
+    <t>1089531 - 00059962 - DG Label</t>
+  </si>
+  <si>
+    <t>161 State Highway 56, Highbury</t>
+  </si>
+  <si>
+    <t>1089528 - 00056947 - DG Label</t>
+  </si>
+  <si>
+    <t>43 Waireka Road, Whanganui</t>
+  </si>
+  <si>
+    <t>1089527 - 00063401 - DG Label</t>
+  </si>
+  <si>
+    <t>1827 State Highway 2, Greytown</t>
+  </si>
+  <si>
+    <t>1089525 - 00068465 - DG Label</t>
+  </si>
+  <si>
+    <t>13 Blue Pacific Parade, Riversdale</t>
+  </si>
+  <si>
+    <t>1089418 - 00071363 - DG Label</t>
+  </si>
+  <si>
+    <t>7 Hewson Lane, Greytown</t>
+  </si>
+  <si>
+    <t>1089417 - 00064852 - DG Label</t>
+  </si>
+  <si>
+    <t>184 Glenmorven Road, Morrisons Bush</t>
+  </si>
+  <si>
+    <t>1089416 - 00067545 - DG Label</t>
+  </si>
+  <si>
+    <t>2774 Lake Ferry Road, Pirinoa</t>
+  </si>
+  <si>
+    <t>1089414 - 00035193 - DG Label</t>
+  </si>
+  <si>
+    <t>286 Dry River Road, Dyerville</t>
+  </si>
+  <si>
+    <t>1089413 - 00072763 - DG Label</t>
+  </si>
+  <si>
+    <t>30 Johnston Street, Featherston</t>
+  </si>
+  <si>
+    <t>1089412 - 00074175 - DG Label</t>
+  </si>
+  <si>
+    <t>20A Denbigh Street, Feilding</t>
+  </si>
+  <si>
+    <t>1089410 - 00026221 - DG Label</t>
+  </si>
+  <si>
+    <t>11 Centennial Drive, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1089409 - 00071408 - DG Label</t>
+  </si>
+  <si>
+    <t>10 Long Melford Road, Awapuni</t>
+  </si>
+  <si>
+    <t>1089407 - 00072966 - DG Label</t>
+  </si>
+  <si>
+    <t>5 MacFarlane Drive, Bunnythorpe</t>
+  </si>
+  <si>
+    <t>1089405 - 00025616 - DG Label</t>
+  </si>
+  <si>
+    <t>420A Kahutara Road</t>
+  </si>
+  <si>
+    <t>1089402 - 00059394 - DG Label</t>
+  </si>
+  <si>
+    <t>48 Geraldine Crescent, Cloverlea</t>
+  </si>
+  <si>
+    <t>1089292 - 00071022 - DG Label</t>
+  </si>
+  <si>
+    <t>42 Grey Street, Marton</t>
+  </si>
+  <si>
+    <t>1089291 - 00067569 - DG Label</t>
+  </si>
+  <si>
+    <t>60 Parsons Street, Whanganui</t>
+  </si>
+  <si>
+    <t>1089289 - 00054176 - DG Label</t>
+  </si>
+  <si>
+    <t>53A Belmont Road, Whanganui</t>
+  </si>
+  <si>
+    <t>1089288 - 00064333 - DG Label</t>
+  </si>
+  <si>
+    <t>85 Rugby Street, Awapuni</t>
+  </si>
+  <si>
+    <t>1089287 - 00058537 - DG Label</t>
+  </si>
+  <si>
+    <t>11 Belmont Place, Terrace End</t>
+  </si>
+  <si>
+    <t>1089286 - 00065591 - DG Label</t>
+  </si>
+  <si>
+    <t>28 Willow Lane, Martinborough</t>
+  </si>
+  <si>
+    <t>1089285 - 00074566 - DG Label</t>
+  </si>
+  <si>
+    <t>124 Hughes Line, Carterton</t>
+  </si>
+  <si>
+    <t>1089284 - 00067688 - DG Label</t>
+  </si>
+  <si>
+    <t>48 West Road, Paihiatua</t>
+  </si>
+  <si>
+    <t>1088737 - 00067725 - DG Label</t>
+  </si>
+  <si>
+    <t>19 Woodland Grove</t>
+  </si>
+  <si>
+    <t>1088725 - 00070510 - DG Label</t>
+  </si>
+  <si>
+    <t>264 High Street South</t>
+  </si>
+  <si>
+    <t>1088226 - 00067692 - DG Label</t>
+  </si>
+  <si>
+    <t>1087274 - 00055245 - DG Label</t>
+  </si>
+  <si>
+    <t>219a Hinekura Road, Hinakura</t>
+  </si>
+  <si>
+    <t>1085718 - 00025360 - DG Label</t>
+  </si>
+  <si>
+    <t>65 Hartwell Drive, Bunnythorpe</t>
+  </si>
+  <si>
+    <t>1085458 - 00044870 - DG Label</t>
+  </si>
+  <si>
+    <t>70B Duddings Line, Featherston</t>
+  </si>
+  <si>
+    <t>1085378 - 00050724 - DG Label</t>
+  </si>
+  <si>
+    <t>51A Southdown Drive, Martinborough</t>
+  </si>
+  <si>
+    <t>1084464 - 00050442 - DG Label</t>
+  </si>
+  <si>
+    <t>99A Lees Pakaraka Road</t>
+  </si>
+  <si>
+    <t>1084461 - 00050984 - DG Label</t>
+  </si>
+  <si>
+    <t>80 West Street</t>
+  </si>
+  <si>
+    <t>1084171 - 00014163 - DG Label</t>
+  </si>
+  <si>
+    <t>89 Dublin Street</t>
+  </si>
+  <si>
+    <t>1084056 - 00054197 - DG Label</t>
+  </si>
+  <si>
+    <t>65 Awhea Road</t>
+  </si>
+  <si>
+    <t>1084055 - 00021842 - DG Label</t>
+  </si>
+  <si>
+    <t>16 Madden Place</t>
+  </si>
+  <si>
+    <t>1083527 - 00043587 - DG Label</t>
+  </si>
+  <si>
+    <t>46A Main Street, Greytowm</t>
+  </si>
+  <si>
+    <t>1083524 - 00043172 - DG Label</t>
+  </si>
+  <si>
+    <t>431C Te Kopi Road, Masterton</t>
+  </si>
+  <si>
+    <t>1082792 - 00051464 - DG Label</t>
+  </si>
+  <si>
+    <t>506 Longbush Road, Masterton</t>
+  </si>
+  <si>
+    <t>1082679 - 00027851 - DG Label</t>
+  </si>
+  <si>
+    <t>18 Ataahua Place, Featherston</t>
+  </si>
+  <si>
+    <t>1082641 - 00032322 - DG Label</t>
+  </si>
+  <si>
+    <t>Nga Waka Winery</t>
+  </si>
+  <si>
+    <t>1078481 - DG Labelling request - 00037578</t>
+  </si>
+  <si>
+    <t>Masterton Castlepoint Road</t>
+  </si>
+  <si>
+    <t>103 Warwick Street</t>
   </si>
 </sst>
 </file>
@@ -1787,7 +2051,127 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="30">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2298,7 +2682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C283"/>
+  <dimension ref="A1:C326"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -2586,7 +2970,7 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -2594,32 +2978,32 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -2627,10 +3011,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -2638,54 +3022,54 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -2693,32 +3077,32 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -2726,21 +3110,21 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
@@ -2748,21 +3132,21 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -2770,10 +3154,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -2781,10 +3165,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -2792,21 +3176,21 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
         <v>10</v>
@@ -2814,10 +3198,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
         <v>10</v>
@@ -2825,10 +3209,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C48" t="s">
         <v>10</v>
@@ -2836,10 +3220,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C49" t="s">
         <v>10</v>
@@ -2847,21 +3231,21 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -2869,21 +3253,21 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C52" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C53" t="s">
         <v>10</v>
@@ -2891,10 +3275,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C54" t="s">
         <v>10</v>
@@ -2902,10 +3286,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B55" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
@@ -2913,54 +3297,54 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B56" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C56" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C57" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B58" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B59" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C59" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C60" t="s">
         <v>10</v>
@@ -2968,21 +3352,21 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C61" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B62" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -2990,54 +3374,54 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B63" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C63" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C64" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C65" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B66" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C66" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B67" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
@@ -3045,21 +3429,21 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B68" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C68" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B69" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C69" t="s">
         <v>10</v>
@@ -3067,43 +3451,43 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B70" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C70" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B71" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C71" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B72" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C72" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B73" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C73" t="s">
         <v>5</v>
@@ -3111,10 +3495,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B74" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
@@ -3122,21 +3506,21 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B75" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C75" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B76" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
@@ -3144,21 +3528,21 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B77" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C77" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B78" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C78" t="s">
         <v>5</v>
@@ -3166,32 +3550,32 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B79" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C79" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B80" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C80" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B81" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
@@ -3199,10 +3583,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B82" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C82" t="s">
         <v>5</v>
@@ -3210,10 +3594,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B83" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C83" t="s">
         <v>5</v>
@@ -3221,10 +3605,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B84" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C84" t="s">
         <v>5</v>
@@ -3232,10 +3616,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
         <v>5</v>
@@ -3243,10 +3627,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B86" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
@@ -3254,10 +3638,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B87" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C87" t="s">
         <v>5</v>
@@ -3265,21 +3649,21 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C88" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B89" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C89" t="s">
         <v>10</v>
@@ -3287,21 +3671,21 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B90" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C90" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B91" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C91" t="s">
         <v>5</v>
@@ -3309,10 +3693,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B92" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
@@ -3320,21 +3704,21 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C93" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B94" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C94" t="s">
         <v>10</v>
@@ -3342,32 +3726,32 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B95" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C95" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B96" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C96" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B97" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C97" t="s">
         <v>10</v>
@@ -3375,21 +3759,21 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B98" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C98" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B99" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C99" t="s">
         <v>5</v>
@@ -3397,32 +3781,32 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B100" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C100" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B101" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C101" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B102" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C102" t="s">
         <v>5</v>
@@ -3430,32 +3814,32 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B103" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C103" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B104" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C104" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B105" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C105" t="s">
         <v>5</v>
@@ -3463,10 +3847,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B106" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C106" t="s">
         <v>5</v>
@@ -3474,32 +3858,32 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B107" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C107" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B108" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C108" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B109" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C109" t="s">
         <v>5</v>
@@ -3507,10 +3891,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B110" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C110" t="s">
         <v>5</v>
@@ -3518,32 +3902,32 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B111" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C111" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B112" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C112" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B113" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C113" t="s">
         <v>5</v>
@@ -3551,10 +3935,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B114" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C114" t="s">
         <v>5</v>
@@ -3562,76 +3946,76 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B115" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C115" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B116" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C116" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B117" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C117" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B118" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C118" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B119" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C119" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B120" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C120" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B121" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C121" t="s">
         <v>5</v>
@@ -3639,10 +4023,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B122" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -3650,10 +4034,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B123" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C123" t="s">
         <v>5</v>
@@ -3661,10 +4045,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B124" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C124" t="s">
         <v>5</v>
@@ -3672,21 +4056,21 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B125" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C125" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B126" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C126" t="s">
         <v>10</v>
@@ -3694,43 +4078,43 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B127" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C127" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B128" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C128" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B129" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C129" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B130" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C130" t="s">
         <v>5</v>
@@ -3738,32 +4122,32 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B131" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C131" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B132" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C132" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B133" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C133" t="s">
         <v>5</v>
@@ -3771,32 +4155,32 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B134" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C134" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B135" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C135" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B136" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C136" t="s">
         <v>5</v>
@@ -3804,54 +4188,54 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B137" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C137" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B138" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C138" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B139" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C139" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B140" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C140" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B141" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C141" t="s">
         <v>5</v>
@@ -3859,10 +4243,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B142" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C142" t="s">
         <v>5</v>
@@ -3870,10 +4254,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B143" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C143" t="s">
         <v>5</v>
@@ -3881,21 +4265,21 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B144" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C144" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B145" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C145" t="s">
         <v>5</v>
@@ -3903,32 +4287,32 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B146" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C146" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B147" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C147" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B148" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C148" t="s">
         <v>5</v>
@@ -3936,10 +4320,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B149" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C149" t="s">
         <v>10</v>
@@ -3947,10 +4331,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B150" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C150" t="s">
         <v>5</v>
@@ -3958,10 +4342,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B151" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C151" t="s">
         <v>10</v>
@@ -3969,32 +4353,32 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B152" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C152" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B153" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C153" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B154" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C154" t="s">
         <v>10</v>
@@ -4002,10 +4386,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B155" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C155" t="s">
         <v>5</v>
@@ -4013,32 +4397,32 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B156" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C156" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B157" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C157" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B158" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C158" t="s">
         <v>5</v>
@@ -4046,10 +4430,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B159" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C159" t="s">
         <v>10</v>
@@ -4057,32 +4441,32 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B160" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C160" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B161" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C161" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B162" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C162" t="s">
         <v>10</v>
@@ -4090,21 +4474,21 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B163" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C163" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B164" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C164" t="s">
         <v>10</v>
@@ -4112,43 +4496,43 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B165" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C165" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B166" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C166" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B167" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C167" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B168" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C168" t="s">
         <v>5</v>
@@ -4156,32 +4540,32 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B169" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C169" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B170" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C170" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B171" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C171" t="s">
         <v>5</v>
@@ -4189,21 +4573,21 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B172" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C172" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B173" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C173" t="s">
         <v>5</v>
@@ -4211,10 +4595,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B174" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C174" t="s">
         <v>5</v>
@@ -4222,21 +4606,21 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B175" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C175" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B176" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C176" t="s">
         <v>5</v>
@@ -4244,10 +4628,10 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B177" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C177" t="s">
         <v>10</v>
@@ -4255,21 +4639,21 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C178" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B179" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C179" t="s">
         <v>10</v>
@@ -4277,10 +4661,10 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B180" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C180" t="s">
         <v>10</v>
@@ -4288,21 +4672,21 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B181" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C181" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B182" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C182" t="s">
         <v>10</v>
@@ -4310,32 +4694,32 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B183" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C183" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B184" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C184" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B185" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C185" t="s">
         <v>10</v>
@@ -4343,10 +4727,10 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B186" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C186" t="s">
         <v>5</v>
@@ -4354,10 +4738,10 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B187" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C187" t="s">
         <v>10</v>
@@ -4365,10 +4749,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B188" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C188" t="s">
         <v>5</v>
@@ -4376,21 +4760,21 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B189" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C189" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B190" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C190" t="s">
         <v>5</v>
@@ -4398,10 +4782,10 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B191" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C191" t="s">
         <v>5</v>
@@ -4409,10 +4793,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B192" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C192" t="s">
         <v>5</v>
@@ -4420,10 +4804,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B193" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C193" t="s">
         <v>5</v>
@@ -4431,10 +4815,10 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B194" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C194" t="s">
         <v>5</v>
@@ -4442,10 +4826,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B195" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C195" t="s">
         <v>5</v>
@@ -4453,10 +4837,10 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B196" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C196" t="s">
         <v>5</v>
@@ -4464,32 +4848,32 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B197" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C197" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B198" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C198" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B199" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C199" t="s">
         <v>10</v>
@@ -4497,43 +4881,43 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B200" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C200" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B201" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C201" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B202" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C202" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B203" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C203" t="s">
         <v>5</v>
@@ -4541,10 +4925,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B204" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C204" t="s">
         <v>10</v>
@@ -4552,10 +4936,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B205" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C205" t="s">
         <v>5</v>
@@ -4563,10 +4947,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B206" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C206" t="s">
         <v>10</v>
@@ -4574,10 +4958,10 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B207" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C207" t="s">
         <v>5</v>
@@ -4585,43 +4969,43 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B208" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C208" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B209" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C209" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B210" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C210" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B211" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C211" t="s">
         <v>10</v>
@@ -4629,21 +5013,21 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B212" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C212" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B213" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C213" t="s">
         <v>10</v>
@@ -4651,32 +5035,32 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B214" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C214" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B215" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C215" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B216" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C216" t="s">
         <v>10</v>
@@ -4684,10 +5068,10 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B217" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C217" t="s">
         <v>5</v>
@@ -4695,10 +5079,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B218" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C218" t="s">
         <v>10</v>
@@ -4706,10 +5090,10 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B219" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C219" t="s">
         <v>5</v>
@@ -4717,21 +5101,21 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B220" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C220" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B221" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C221" t="s">
         <v>5</v>
@@ -4739,32 +5123,32 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B222" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C222" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B223" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C223" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B224" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C224" t="s">
         <v>10</v>
@@ -4772,10 +5156,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B225" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C225" t="s">
         <v>10</v>
@@ -4783,32 +5167,32 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B226" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C226" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B227" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C227" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B228" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C228" t="s">
         <v>5</v>
@@ -4816,10 +5200,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B229" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C229" t="s">
         <v>5</v>
@@ -4827,10 +5211,10 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B230" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C230" t="s">
         <v>5</v>
@@ -4838,43 +5222,43 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B231" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C231" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B232" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C232" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B233" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C233" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B234" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C234" t="s">
         <v>10</v>
@@ -4882,54 +5266,54 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B235" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C235" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B236" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C236" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B237" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C237" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B238" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C238" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B239" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C239" t="s">
         <v>5</v>
@@ -4937,10 +5321,10 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B240" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C240" t="s">
         <v>10</v>
@@ -4948,21 +5332,21 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B241" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C241" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B242" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C242" t="s">
         <v>10</v>
@@ -4970,21 +5354,21 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B243" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C243" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B244" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C244" t="s">
         <v>10</v>
@@ -4992,21 +5376,21 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B245" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C245" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B246" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C246" t="s">
         <v>10</v>
@@ -5014,10 +5398,10 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B247" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C247" t="s">
         <v>10</v>
@@ -5025,10 +5409,10 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B248" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C248" t="s">
         <v>10</v>
@@ -5036,10 +5420,10 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B249" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C249" t="s">
         <v>10</v>
@@ -5047,10 +5431,10 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B250" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C250" t="s">
         <v>10</v>
@@ -5058,10 +5442,10 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B251" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C251" t="s">
         <v>10</v>
@@ -5069,21 +5453,21 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B252" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C252" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B253" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C253" t="s">
         <v>10</v>
@@ -5091,32 +5475,32 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B254" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C254" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B255" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C255" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B256" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C256" t="s">
         <v>10</v>
@@ -5124,10 +5508,10 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B257" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C257" t="s">
         <v>5</v>
@@ -5135,87 +5519,87 @@
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B258" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C258" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B259" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C259" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B260" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C260" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B261" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C261" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B262" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C262" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B263" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C263" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B264" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C264" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B265" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C265" t="s">
         <v>10</v>
@@ -5223,10 +5607,10 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B266" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C266" t="s">
         <v>10</v>
@@ -5234,10 +5618,10 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B267" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C267" t="s">
         <v>10</v>
@@ -5245,10 +5629,10 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B268" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C268" t="s">
         <v>10</v>
@@ -5256,10 +5640,10 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B269" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C269" t="s">
         <v>10</v>
@@ -5267,21 +5651,21 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B270" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C270" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B271" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C271" t="s">
         <v>10</v>
@@ -5289,10 +5673,10 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B272" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C272" t="s">
         <v>5</v>
@@ -5300,21 +5684,21 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B273" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C273" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B274" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C274" t="s">
         <v>5</v>
@@ -5322,10 +5706,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B275" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C275" t="s">
         <v>5</v>
@@ -5333,10 +5717,10 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B276" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C276" t="s">
         <v>5</v>
@@ -5344,10 +5728,10 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B277" t="s">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="C277" t="s">
         <v>5</v>
@@ -5355,10 +5739,10 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B278" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C278" t="s">
         <v>5</v>
@@ -5366,13 +5750,13 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B279" t="s">
         <v>558</v>
       </c>
       <c r="C279" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
@@ -5383,7 +5767,7 @@
         <v>559</v>
       </c>
       <c r="C280" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
@@ -5391,18 +5775,18 @@
         <v>564</v>
       </c>
       <c r="B281" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C281" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B282" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="C282" t="s">
         <v>10</v>
@@ -5410,32 +5794,512 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B283" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="C283" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>570</v>
+      </c>
+      <c r="B284" t="s">
+        <v>273</v>
+      </c>
+      <c r="C284" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>571</v>
+      </c>
+      <c r="B285" t="s">
+        <v>572</v>
+      </c>
+      <c r="C285" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>573</v>
+      </c>
+      <c r="B286" t="s">
+        <v>574</v>
+      </c>
+      <c r="C286" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>575</v>
+      </c>
+      <c r="B287" t="s">
+        <v>576</v>
+      </c>
+      <c r="C287" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>577</v>
+      </c>
+      <c r="B288" t="s">
+        <v>578</v>
+      </c>
+      <c r="C288" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>579</v>
+      </c>
+      <c r="B289" t="s">
+        <v>580</v>
+      </c>
+      <c r="C289" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>581</v>
+      </c>
+      <c r="B290" t="s">
+        <v>582</v>
+      </c>
+      <c r="C290" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>583</v>
+      </c>
+      <c r="B291" t="s">
+        <v>584</v>
+      </c>
+      <c r="C291" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>585</v>
+      </c>
+      <c r="B292" t="s">
+        <v>586</v>
+      </c>
+      <c r="C292" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>587</v>
+      </c>
+      <c r="B293" t="s">
+        <v>588</v>
+      </c>
+      <c r="C293" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>589</v>
+      </c>
+      <c r="B294" t="s">
+        <v>590</v>
+      </c>
+      <c r="C294" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>591</v>
+      </c>
+      <c r="B295" t="s">
+        <v>592</v>
+      </c>
+      <c r="C295" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>593</v>
+      </c>
+      <c r="B296" t="s">
+        <v>594</v>
+      </c>
+      <c r="C296" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>595</v>
+      </c>
+      <c r="B297" t="s">
+        <v>596</v>
+      </c>
+      <c r="C297" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>597</v>
+      </c>
+      <c r="B298" t="s">
+        <v>598</v>
+      </c>
+      <c r="C298" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>599</v>
+      </c>
+      <c r="B299" t="s">
+        <v>600</v>
+      </c>
+      <c r="C299" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>601</v>
+      </c>
+      <c r="B300" t="s">
+        <v>602</v>
+      </c>
+      <c r="C300" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>603</v>
+      </c>
+      <c r="B301" t="s">
+        <v>604</v>
+      </c>
+      <c r="C301" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>605</v>
+      </c>
+      <c r="B302" t="s">
+        <v>606</v>
+      </c>
+      <c r="C302" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>607</v>
+      </c>
+      <c r="B303" t="s">
+        <v>608</v>
+      </c>
+      <c r="C303" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>609</v>
+      </c>
+      <c r="B304" t="s">
+        <v>610</v>
+      </c>
+      <c r="C304" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>611</v>
+      </c>
+      <c r="B305" t="s">
+        <v>612</v>
+      </c>
+      <c r="C305" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>613</v>
+      </c>
+      <c r="B306" t="s">
+        <v>614</v>
+      </c>
+      <c r="C306" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>615</v>
+      </c>
+      <c r="B307" t="s">
+        <v>616</v>
+      </c>
+      <c r="C307" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>617</v>
+      </c>
+      <c r="B308" t="s">
+        <v>618</v>
+      </c>
+      <c r="C308" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>619</v>
+      </c>
+      <c r="B309" t="s">
+        <v>620</v>
+      </c>
+      <c r="C309" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>621</v>
+      </c>
+      <c r="B310" t="s">
+        <v>622</v>
+      </c>
+      <c r="C310" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>652</v>
+      </c>
+      <c r="B311" t="s">
+        <v>653</v>
+      </c>
+      <c r="C311" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>650</v>
+      </c>
+      <c r="B312" t="s">
+        <v>651</v>
+      </c>
+      <c r="C312" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>648</v>
+      </c>
+      <c r="B313" t="s">
+        <v>649</v>
+      </c>
+      <c r="C313" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>646</v>
+      </c>
+      <c r="B314" t="s">
+        <v>647</v>
+      </c>
+      <c r="C314" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>642</v>
+      </c>
+      <c r="B315" t="s">
+        <v>643</v>
+      </c>
+      <c r="C315" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>644</v>
+      </c>
+      <c r="B316" t="s">
+        <v>645</v>
+      </c>
+      <c r="C316" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>638</v>
+      </c>
+      <c r="B317" t="s">
+        <v>639</v>
+      </c>
+      <c r="C317" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>640</v>
+      </c>
+      <c r="B318" t="s">
+        <v>641</v>
+      </c>
+      <c r="C318" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>632</v>
+      </c>
+      <c r="B319" t="s">
+        <v>633</v>
+      </c>
+      <c r="C319" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>634</v>
+      </c>
+      <c r="B320" t="s">
+        <v>635</v>
+      </c>
+      <c r="C320" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>636</v>
+      </c>
+      <c r="B321" t="s">
+        <v>637</v>
+      </c>
+      <c r="C321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>630</v>
+      </c>
+      <c r="B322" t="s">
+        <v>631</v>
+      </c>
+      <c r="C322" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>628</v>
+      </c>
+      <c r="B323" t="s">
+        <v>629</v>
+      </c>
+      <c r="C323" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>626</v>
+      </c>
+      <c r="B324" t="s">
+        <v>627</v>
+      </c>
+      <c r="C324" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>624</v>
+      </c>
+      <c r="B325" t="s">
+        <v>625</v>
+      </c>
+      <c r="C325" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>623</v>
+      </c>
+      <c r="B326" t="s">
+        <v>654</v>
+      </c>
+      <c r="C326" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+  <conditionalFormatting sqref="A327:A1048576 A1:A280">
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B284:B1048576 B1:B207">
-    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+  <conditionalFormatting sqref="B327:B1048576 B1:B280">
+    <cfRule type="duplicateValues" dxfId="5" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M16">
+  <conditionalFormatting sqref="B327:B1048576 B1:B205">
+    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16">
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I21">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
